--- a/STOK RANK/Rank Dealer/RANK BHG.xlsx
+++ b/STOK RANK/Rank Dealer/RANK BHG.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\DASHBOARD RANK STOK\data\Rank Dealer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36379D2A-321A-4618-BE1E-88571837CF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C59A240-377A-4226-A5D1-13C971DAA4BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B751393D-4C32-4D4C-AA97-AA7CC129AC75}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="286">
   <si>
     <t>Sum of Qty</t>
   </si>
@@ -194,9 +194,6 @@
     <t>42711KVB931</t>
   </si>
   <si>
-    <t>31919K25602</t>
-  </si>
-  <si>
     <t>33100K1AN01</t>
   </si>
   <si>
@@ -248,9 +245,6 @@
     <t>42711K2SN01</t>
   </si>
   <si>
-    <t>31926KRM841</t>
-  </si>
-  <si>
     <t>ALF6301RS</t>
   </si>
   <si>
@@ -299,9 +293,6 @@
     <t>64223K1AN01</t>
   </si>
   <si>
-    <t>AHB6201RS</t>
-  </si>
-  <si>
     <t>22011KWN900</t>
   </si>
   <si>
@@ -470,9 +461,6 @@
     <t>64431K2FN00YK</t>
   </si>
   <si>
-    <t>12191KZR600</t>
-  </si>
-  <si>
     <t>81134K2FN00YB</t>
   </si>
   <si>
@@ -533,9 +521,6 @@
     <t>17210KZR600</t>
   </si>
   <si>
-    <t>33100K2VN31</t>
-  </si>
-  <si>
     <t>64421K2FN00YJ</t>
   </si>
   <si>
@@ -563,9 +548,6 @@
     <t>81141K2FN80ZG</t>
   </si>
   <si>
-    <t>45150K93N01</t>
-  </si>
-  <si>
     <t>83620K56N00RSW</t>
   </si>
   <si>
@@ -620,9 +602,6 @@
     <t>64223K2FN80</t>
   </si>
   <si>
-    <t>33110K81N01</t>
-  </si>
-  <si>
     <t>64301K1AN80MFB</t>
   </si>
   <si>
@@ -638,9 +617,6 @@
     <t>12191GGC900</t>
   </si>
   <si>
-    <t>33400K81N01</t>
-  </si>
-  <si>
     <t>64301K81N00RSW</t>
   </si>
   <si>
@@ -710,18 +686,12 @@
     <t>81110K0JN00</t>
   </si>
   <si>
-    <t>33452K1AN01</t>
-  </si>
-  <si>
     <t>81131K2VN30ZM</t>
   </si>
   <si>
     <t>33452K1AN81</t>
   </si>
   <si>
-    <t>81141K16A40RSW</t>
-  </si>
-  <si>
     <t>53207K2FN00RSW</t>
   </si>
   <si>
@@ -828,6 +798,102 @@
   </si>
   <si>
     <t>kode part</t>
+  </si>
+  <si>
+    <t>1C70070EJ01</t>
+  </si>
+  <si>
+    <t>51490KGH902</t>
+  </si>
+  <si>
+    <t>88211K93N00ZE</t>
+  </si>
+  <si>
+    <t>61100K15920ZA</t>
+  </si>
+  <si>
+    <t>22535KVB900</t>
+  </si>
+  <si>
+    <t>81142K2FN00ZX</t>
+  </si>
+  <si>
+    <t>64301K2FN00YA</t>
+  </si>
+  <si>
+    <t>45351K93N01</t>
+  </si>
+  <si>
+    <t>64310K2FN00ZC</t>
+  </si>
+  <si>
+    <t>81141K2FN00ZN</t>
+  </si>
+  <si>
+    <t>16700K16305</t>
+  </si>
+  <si>
+    <t>3501AK93N00</t>
+  </si>
+  <si>
+    <t>52400K81N11</t>
+  </si>
+  <si>
+    <t>64221K45N40</t>
+  </si>
+  <si>
+    <t>64241K45NA0</t>
+  </si>
+  <si>
+    <t>17220KZR600</t>
+  </si>
+  <si>
+    <t>64421K2FN00ZJ</t>
+  </si>
+  <si>
+    <t>64431K2FN00ZE</t>
+  </si>
+  <si>
+    <t>61100K2FN00YB</t>
+  </si>
+  <si>
+    <t>80105K1AN00ZA</t>
+  </si>
+  <si>
+    <t>64201K2FN00ZJ</t>
+  </si>
+  <si>
+    <t>64202K2FN00ZJ</t>
+  </si>
+  <si>
+    <t>64211K45N40ZB</t>
+  </si>
+  <si>
+    <t>64223K0JN00</t>
+  </si>
+  <si>
+    <t>33110K03N31</t>
+  </si>
+  <si>
+    <t>33400K45NA1</t>
+  </si>
+  <si>
+    <t>61313K45N40</t>
+  </si>
+  <si>
+    <t>64330K45N40</t>
+  </si>
+  <si>
+    <t>64231K45N40</t>
+  </si>
+  <si>
+    <t>88211K93N00ZD</t>
+  </si>
+  <si>
+    <t>64271K45N40</t>
+  </si>
+  <si>
+    <t>06455KREK01</t>
   </si>
 </sst>
 </file>
@@ -889,13 +955,13 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -911,13 +977,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C03BE401-9C1F-4F8C-A0F0-B1258C79C616}" name="rankparts" displayName="rankparts" ref="A1:F255" totalsRowShown="0">
-  <autoFilter ref="A1:F255" xr:uid="{C03BE401-9C1F-4F8C-A0F0-B1258C79C616}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C03BE401-9C1F-4F8C-A0F0-B1258C79C616}" name="rankparts" displayName="rankparts" ref="A1:F277" totalsRowShown="0">
+  <autoFilter ref="A1:F277" xr:uid="{C03BE401-9C1F-4F8C-A0F0-B1258C79C616}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{EC489C37-CEDC-4675-8D70-1D331AA94B51}" name="kode part" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{EC489C37-CEDC-4675-8D70-1D331AA94B51}" name="kode part" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{36D6B850-0C62-4808-8CA4-A3ADDE283157}" name="Sum of Qty"/>
-    <tableColumn id="3" xr3:uid="{6AF7942C-7A8B-42A4-8893-BB3A0B0BA8DB}" name="AVG 12 Bulan" dataDxfId="2" dataCellStyle="Comma"/>
-    <tableColumn id="4" xr3:uid="{A19099EB-09D4-453B-B335-8C8E31A09221}" name="Akumulasi AVG 12 Bulan" dataDxfId="1" dataCellStyle="Comma"/>
+    <tableColumn id="3" xr3:uid="{6AF7942C-7A8B-42A4-8893-BB3A0B0BA8DB}" name="AVG 12 Bulan" dataDxfId="1" dataCellStyle="Comma"/>
+    <tableColumn id="4" xr3:uid="{A19099EB-09D4-453B-B335-8C8E31A09221}" name="Akumulasi AVG 12 Bulan" dataDxfId="0" dataCellStyle="Comma"/>
     <tableColumn id="5" xr3:uid="{47EFE725-CDB5-45AD-BDA0-B6DCB63EE85D}" name="Cont % Akumulasi" dataCellStyle="Percent"/>
     <tableColumn id="6" xr3:uid="{37C8619E-0B0F-4647-86AB-979865F93ADA}" name="Rank"/>
   </tableColumns>
@@ -1242,7 +1308,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10CE7CC1-6D2C-42F4-9AE1-2E1B51ED5CAA}">
-  <dimension ref="A1:F255"/>
+  <dimension ref="A1:F277"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" style="3" bestFit="1" customWidth="1"/>
@@ -1254,7 +1320,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1277,16 +1343,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>150</v>
+        <v>196</v>
       </c>
       <c r="C2" s="1">
-        <v>25</v>
+        <v>32.666666666666664</v>
       </c>
       <c r="D2" s="1">
-        <v>25</v>
+        <v>32.666666666666664</v>
       </c>
       <c r="E2" s="2">
-        <v>0.10026737967914483</v>
+        <v>0.11893203883495056</v>
       </c>
       <c r="F2" t="s">
         <v>6</v>
@@ -1303,10 +1369,10 @@
         <v>15.666666666666666</v>
       </c>
       <c r="D3" s="1">
-        <v>40.666666666666664</v>
+        <v>48.333333333333329</v>
       </c>
       <c r="E3" s="2">
-        <v>0.16310160427807557</v>
+        <v>0.17597087378640644</v>
       </c>
       <c r="F3" t="s">
         <v>6</v>
@@ -1314,19 +1380,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C4" s="1">
-        <v>12.166666666666666</v>
+        <v>12.5</v>
       </c>
       <c r="D4" s="1">
-        <v>52.833333333333329</v>
+        <v>60.833333333333329</v>
       </c>
       <c r="E4" s="2">
-        <v>0.21189839572192604</v>
+        <v>0.22148058252427016</v>
       </c>
       <c r="F4" t="s">
         <v>6</v>
@@ -1334,19 +1400,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C5" s="1">
-        <v>11.333333333333334</v>
+        <v>12.5</v>
       </c>
       <c r="D5" s="1">
-        <v>64.166666666666657</v>
+        <v>73.333333333333329</v>
       </c>
       <c r="E5" s="2">
-        <v>0.25735294117647167</v>
+        <v>0.26699029126213392</v>
       </c>
       <c r="F5" t="s">
         <v>6</v>
@@ -1357,16 +1423,16 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C6" s="1">
-        <v>11.333333333333334</v>
+        <v>12.166666666666666</v>
       </c>
       <c r="D6" s="1">
-        <v>75.499999999999986</v>
+        <v>85.5</v>
       </c>
       <c r="E6" s="2">
-        <v>0.30280748663101731</v>
+        <v>0.31128640776698796</v>
       </c>
       <c r="F6" t="s">
         <v>6</v>
@@ -1374,19 +1440,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C7" s="1">
-        <v>9.3333333333333339</v>
+        <v>11.333333333333334</v>
       </c>
       <c r="D7" s="1">
-        <v>84.833333333333314</v>
+        <v>96.833333333333329</v>
       </c>
       <c r="E7" s="2">
-        <v>0.34024064171123136</v>
+        <v>0.35254854368931771</v>
       </c>
       <c r="F7" t="s">
         <v>6</v>
@@ -1394,19 +1460,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B8">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C8" s="1">
-        <v>9.1666666666666661</v>
+        <v>10.166666666666666</v>
       </c>
       <c r="D8" s="1">
-        <v>93.999999999999986</v>
+        <v>107</v>
       </c>
       <c r="E8" s="2">
-        <v>0.37700534759358451</v>
+        <v>0.38956310679611356</v>
       </c>
       <c r="F8" t="s">
         <v>6</v>
@@ -1417,16 +1483,16 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C9" s="1">
-        <v>9</v>
+        <v>8.3333333333333339</v>
       </c>
       <c r="D9" s="1">
-        <v>102.99999999999999</v>
+        <v>115.33333333333333</v>
       </c>
       <c r="E9" s="2">
-        <v>0.41310160427807663</v>
+        <v>0.41990291262135604</v>
       </c>
       <c r="F9" t="s">
         <v>6</v>
@@ -1434,19 +1500,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B10">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C10" s="1">
-        <v>7.833333333333333</v>
+        <v>8.1666666666666661</v>
       </c>
       <c r="D10" s="1">
-        <v>110.83333333333331</v>
+        <v>123.5</v>
       </c>
       <c r="E10" s="2">
-        <v>0.44451871657754199</v>
+        <v>0.4496359223300937</v>
       </c>
       <c r="F10" t="s">
         <v>6</v>
@@ -1454,19 +1520,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C11" s="1">
-        <v>6.833333333333333</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="D11" s="1">
-        <v>117.66666666666664</v>
+        <v>130.83333333333334</v>
       </c>
       <c r="E11" s="2">
-        <v>0.47192513368984157</v>
+        <v>0.47633495145630711</v>
       </c>
       <c r="F11" t="s">
         <v>6</v>
@@ -1477,16 +1543,16 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1">
-        <v>4.666666666666667</v>
+        <v>5.5</v>
       </c>
       <c r="D12" s="1">
-        <v>122.33333333333331</v>
+        <v>136.33333333333334</v>
       </c>
       <c r="E12" s="2">
-        <v>0.4906417112299486</v>
+        <v>0.49635922330096716</v>
       </c>
       <c r="F12" t="s">
         <v>6</v>
@@ -1494,7 +1560,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>25</v>
@@ -1503,10 +1569,10 @@
         <v>4.166666666666667</v>
       </c>
       <c r="D13" s="1">
-        <v>126.49999999999999</v>
+        <v>140.5</v>
       </c>
       <c r="E13" s="2">
-        <v>0.50735294117647278</v>
+        <v>0.51152912621358837</v>
       </c>
       <c r="F13" t="s">
         <v>6</v>
@@ -1523,10 +1589,10 @@
         <v>3.8333333333333335</v>
       </c>
       <c r="D14" s="1">
-        <v>130.33333333333331</v>
+        <v>144.33333333333334</v>
       </c>
       <c r="E14" s="2">
-        <v>0.52272727272727493</v>
+        <v>0.52548543689319993</v>
       </c>
       <c r="F14" t="s">
         <v>6</v>
@@ -1534,19 +1600,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" s="1">
-        <v>3.6666666666666665</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="D15" s="1">
-        <v>133.99999999999997</v>
+        <v>148.16666666666669</v>
       </c>
       <c r="E15" s="2">
-        <v>0.53743315508021616</v>
+        <v>0.53944174757281149</v>
       </c>
       <c r="F15" t="s">
         <v>6</v>
@@ -1554,7 +1620,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B16">
         <v>22</v>
@@ -1563,10 +1629,10 @@
         <v>3.6666666666666665</v>
       </c>
       <c r="D16" s="1">
-        <v>137.66666666666663</v>
+        <v>151.83333333333334</v>
       </c>
       <c r="E16" s="2">
-        <v>0.5521390374331574</v>
+        <v>0.55279126213591823</v>
       </c>
       <c r="F16" t="s">
         <v>6</v>
@@ -1577,16 +1643,16 @@
         <v>21</v>
       </c>
       <c r="B17">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C17" s="1">
-        <v>3.5</v>
+        <v>3.1666666666666665</v>
       </c>
       <c r="D17" s="1">
-        <v>141.16666666666663</v>
+        <v>155</v>
       </c>
       <c r="E17" s="2">
-        <v>0.56617647058823761</v>
+        <v>0.56432038834951037</v>
       </c>
       <c r="F17" t="s">
         <v>6</v>
@@ -1594,7 +1660,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="B18">
         <v>18</v>
@@ -1603,10 +1669,10 @@
         <v>3</v>
       </c>
       <c r="D18" s="1">
-        <v>144.16666666666663</v>
+        <v>158</v>
       </c>
       <c r="E18" s="2">
-        <v>0.57820855614973499</v>
+        <v>0.57524271844659758</v>
       </c>
       <c r="F18" t="s">
         <v>6</v>
@@ -1614,19 +1680,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" s="1">
-        <v>2.8333333333333335</v>
+        <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>146.99999999999997</v>
+        <v>161</v>
       </c>
       <c r="E19" s="2">
-        <v>0.58957219251337145</v>
+        <v>0.5861650485436849</v>
       </c>
       <c r="F19" t="s">
         <v>6</v>
@@ -1634,19 +1700,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B20">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C20" s="1">
-        <v>2.6666666666666665</v>
+        <v>3</v>
       </c>
       <c r="D20" s="1">
-        <v>149.66666666666663</v>
+        <v>164</v>
       </c>
       <c r="E20" s="2">
-        <v>0.6002673796791469</v>
+        <v>0.59708737864077222</v>
       </c>
       <c r="F20" t="s">
         <v>6</v>
@@ -1654,19 +1720,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B21">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C21" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D21" s="1">
-        <v>152.16666666666663</v>
+        <v>167</v>
       </c>
       <c r="E21" s="2">
-        <v>0.61029411764706132</v>
+        <v>0.60800970873785953</v>
       </c>
       <c r="F21" t="s">
         <v>6</v>
@@ -1674,19 +1740,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B22">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1">
-        <v>2.3333333333333335</v>
+        <v>2.8333333333333335</v>
       </c>
       <c r="D22" s="1">
-        <v>154.49999999999997</v>
+        <v>169.83333333333334</v>
       </c>
       <c r="E22" s="2">
-        <v>0.61965240641711494</v>
+        <v>0.61832524271844203</v>
       </c>
       <c r="F22" t="s">
         <v>6</v>
@@ -1694,19 +1760,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B23">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C23" s="1">
-        <v>2.3333333333333335</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="D23" s="1">
-        <v>156.83333333333331</v>
+        <v>172.5</v>
       </c>
       <c r="E23" s="2">
-        <v>0.62901069518716846</v>
+        <v>0.62803398058251958</v>
       </c>
       <c r="F23" t="s">
         <v>6</v>
@@ -1714,19 +1780,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B24">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C24" s="1">
-        <v>2.3333333333333335</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="D24" s="1">
-        <v>159.16666666666666</v>
+        <v>175.16666666666666</v>
       </c>
       <c r="E24" s="2">
-        <v>0.63836898395722208</v>
+        <v>0.63774271844659713</v>
       </c>
       <c r="F24" t="s">
         <v>6</v>
@@ -1734,19 +1800,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B25">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C25" s="1">
-        <v>2.1666666666666665</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="D25" s="1">
-        <v>161.33333333333331</v>
+        <v>177.83333333333331</v>
       </c>
       <c r="E25" s="2">
-        <v>0.64705882352941457</v>
+        <v>0.64745145631067469</v>
       </c>
       <c r="F25" t="s">
         <v>6</v>
@@ -1754,19 +1820,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B26">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D26" s="1">
-        <v>163.33333333333331</v>
+        <v>180.33333333333331</v>
       </c>
       <c r="E26" s="2">
-        <v>0.65508021390374616</v>
+        <v>0.65655339805824742</v>
       </c>
       <c r="F26" t="s">
         <v>6</v>
@@ -1777,16 +1843,16 @@
         <v>31</v>
       </c>
       <c r="B27">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D27" s="1">
-        <v>165.33333333333331</v>
+        <v>182.83333333333331</v>
       </c>
       <c r="E27" s="2">
-        <v>0.66310160427807774</v>
+        <v>0.66565533980582015</v>
       </c>
       <c r="F27" t="s">
         <v>6</v>
@@ -1794,19 +1860,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B28">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C28" s="1">
-        <v>2</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="D28" s="1">
-        <v>167.33333333333331</v>
+        <v>185.16666666666666</v>
       </c>
       <c r="E28" s="2">
-        <v>0.67112299465240932</v>
+        <v>0.67415048543688805</v>
       </c>
       <c r="F28" t="s">
         <v>6</v>
@@ -1814,19 +1880,19 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B29">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C29" s="1">
-        <v>1.8333333333333333</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="D29" s="1">
-        <v>169.16666666666666</v>
+        <v>187.5</v>
       </c>
       <c r="E29" s="2">
-        <v>0.67847593582887999</v>
+        <v>0.68264563106795606</v>
       </c>
       <c r="F29" t="s">
         <v>6</v>
@@ -1834,19 +1900,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C30" s="1">
-        <v>1.8333333333333333</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="D30" s="1">
-        <v>171</v>
+        <v>189.83333333333334</v>
       </c>
       <c r="E30" s="2">
-        <v>0.68582887700535067</v>
+        <v>0.69114077669902396</v>
       </c>
       <c r="F30" t="s">
         <v>6</v>
@@ -1854,19 +1920,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B31">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C31" s="1">
-        <v>1.8333333333333333</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="D31" s="1">
-        <v>172.83333333333334</v>
+        <v>192.16666666666669</v>
       </c>
       <c r="E31" s="2">
-        <v>0.69318181818182123</v>
+        <v>0.69963592233009186</v>
       </c>
       <c r="F31" t="s">
         <v>6</v>
@@ -1874,19 +1940,19 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B32">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C32" s="1">
-        <v>1.8333333333333333</v>
+        <v>2.1666666666666665</v>
       </c>
       <c r="D32" s="1">
-        <v>174.66666666666669</v>
+        <v>194.33333333333334</v>
       </c>
       <c r="E32" s="2">
-        <v>0.7005347593582919</v>
+        <v>0.70752427184465494</v>
       </c>
       <c r="F32" t="s">
         <v>6</v>
@@ -1894,19 +1960,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="B33">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C33" s="1">
-        <v>1.8333333333333333</v>
+        <v>2</v>
       </c>
       <c r="D33" s="1">
-        <v>176.50000000000003</v>
+        <v>196.33333333333334</v>
       </c>
       <c r="E33" s="2">
-        <v>0.70788770053476258</v>
+        <v>0.71480582524271308</v>
       </c>
       <c r="F33" t="s">
         <v>6</v>
@@ -1914,19 +1980,19 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B34">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C34" s="1">
-        <v>1.6666666666666667</v>
+        <v>2</v>
       </c>
       <c r="D34" s="1">
-        <v>178.16666666666669</v>
+        <v>198.33333333333334</v>
       </c>
       <c r="E34" s="2">
-        <v>0.71457219251337223</v>
+        <v>0.72208737864077133</v>
       </c>
       <c r="F34" t="s">
         <v>6</v>
@@ -1934,19 +2000,19 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B35">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C35" s="1">
-        <v>1.6666666666666667</v>
+        <v>2</v>
       </c>
       <c r="D35" s="1">
-        <v>179.83333333333334</v>
+        <v>200.33333333333334</v>
       </c>
       <c r="E35" s="2">
-        <v>0.72125668449198188</v>
+        <v>0.72936893203882947</v>
       </c>
       <c r="F35" t="s">
         <v>6</v>
@@ -1954,19 +2020,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B36">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="1">
-        <v>1.6666666666666667</v>
+        <v>1.8333333333333333</v>
       </c>
       <c r="D36" s="1">
-        <v>181.5</v>
+        <v>202.16666666666669</v>
       </c>
       <c r="E36" s="2">
-        <v>0.72794117647059142</v>
+        <v>0.73604368932038289</v>
       </c>
       <c r="F36" t="s">
         <v>6</v>
@@ -1974,7 +2040,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B37">
         <v>10</v>
@@ -1983,10 +2049,10 @@
         <v>1.6666666666666667</v>
       </c>
       <c r="D37" s="1">
-        <v>183.16666666666666</v>
+        <v>203.83333333333334</v>
       </c>
       <c r="E37" s="2">
-        <v>0.73462566844920107</v>
+        <v>0.74211165048543137</v>
       </c>
       <c r="F37" t="s">
         <v>6</v>
@@ -1994,7 +2060,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B38">
         <v>10</v>
@@ -2003,10 +2069,10 @@
         <v>1.6666666666666667</v>
       </c>
       <c r="D38" s="1">
-        <v>184.83333333333331</v>
+        <v>205.5</v>
       </c>
       <c r="E38" s="2">
-        <v>0.74131016042781073</v>
+        <v>0.74817961165047986</v>
       </c>
       <c r="F38" t="s">
         <v>6</v>
@@ -2014,19 +2080,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C39" s="1">
-        <v>1.5</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="D39" s="1">
-        <v>186.33333333333331</v>
+        <v>207.16666666666666</v>
       </c>
       <c r="E39" s="2">
-        <v>0.74732620320855936</v>
+        <v>0.75424757281552823</v>
       </c>
       <c r="F39" t="s">
         <v>6</v>
@@ -2034,7 +2100,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B40">
         <v>9</v>
@@ -2043,10 +2109,10 @@
         <v>1.5</v>
       </c>
       <c r="D40" s="1">
-        <v>187.83333333333331</v>
+        <v>208.66666666666666</v>
       </c>
       <c r="E40" s="2">
-        <v>0.7533422459893081</v>
+        <v>0.75970873786407189</v>
       </c>
       <c r="F40" t="s">
         <v>6</v>
@@ -2054,7 +2120,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B41">
         <v>8</v>
@@ -2063,10 +2129,10 @@
         <v>1.3333333333333333</v>
       </c>
       <c r="D41" s="1">
-        <v>189.16666666666666</v>
+        <v>210</v>
       </c>
       <c r="E41" s="2">
-        <v>0.75868983957219582</v>
+        <v>0.76456310679611073</v>
       </c>
       <c r="F41" t="s">
         <v>6</v>
@@ -2074,19 +2140,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C42" s="1">
-        <v>1.1666666666666667</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="D42" s="1">
-        <v>190.33333333333331</v>
+        <v>211.33333333333334</v>
       </c>
       <c r="E42" s="2">
-        <v>0.76336898395722252</v>
+        <v>0.76941747572814956</v>
       </c>
       <c r="F42" t="s">
         <v>6</v>
@@ -2094,19 +2160,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C43" s="1">
-        <v>1.1666666666666667</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="D43" s="1">
-        <v>191.49999999999997</v>
+        <v>212.66666666666669</v>
       </c>
       <c r="E43" s="2">
-        <v>0.76804812834224923</v>
+        <v>0.77427184466018839</v>
       </c>
       <c r="F43" t="s">
         <v>6</v>
@@ -2114,19 +2180,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C44" s="1">
-        <v>1.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="D44" s="1">
-        <v>192.66666666666663</v>
+        <v>213.66666666666669</v>
       </c>
       <c r="E44" s="2">
-        <v>0.77272727272727593</v>
+        <v>0.77791262135921757</v>
       </c>
       <c r="F44" t="s">
         <v>6</v>
@@ -2134,19 +2200,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C45" s="1">
-        <v>1.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="D45" s="1">
-        <v>193.83333333333329</v>
+        <v>214.66666666666669</v>
       </c>
       <c r="E45" s="2">
-        <v>0.77740641711230274</v>
+        <v>0.78155339805824664</v>
       </c>
       <c r="F45" t="s">
         <v>6</v>
@@ -2154,19 +2220,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B46">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46" s="1">
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D46" s="1">
-        <v>194.83333333333329</v>
+        <v>215.50000000000003</v>
       </c>
       <c r="E46" s="2">
-        <v>0.78141711229946853</v>
+        <v>0.78458737864077088</v>
       </c>
       <c r="F46" t="s">
         <v>6</v>
@@ -2174,19 +2240,19 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C47" s="1">
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D47" s="1">
-        <v>195.83333333333329</v>
+        <v>216.33333333333337</v>
       </c>
       <c r="E47" s="2">
-        <v>0.78542780748663432</v>
+        <v>0.78762135922329524</v>
       </c>
       <c r="F47" t="s">
         <v>6</v>
@@ -2194,7 +2260,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B48">
         <v>5</v>
@@ -2203,10 +2269,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D48" s="1">
-        <v>196.66666666666663</v>
+        <v>217.16666666666671</v>
       </c>
       <c r="E48" s="2">
-        <v>0.7887700534759392</v>
+        <v>0.79065533980581948</v>
       </c>
       <c r="F48" t="s">
         <v>6</v>
@@ -2214,7 +2280,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B49">
         <v>5</v>
@@ -2223,10 +2289,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D49" s="1">
-        <v>197.49999999999997</v>
+        <v>218.00000000000006</v>
       </c>
       <c r="E49" s="2">
-        <v>0.79211229946524397</v>
+        <v>0.79368932038834372</v>
       </c>
       <c r="F49" t="s">
         <v>6</v>
@@ -2234,7 +2300,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B50">
         <v>5</v>
@@ -2243,10 +2309,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D50" s="1">
-        <v>198.33333333333331</v>
+        <v>218.8333333333334</v>
       </c>
       <c r="E50" s="2">
-        <v>0.79545454545454886</v>
+        <v>0.79672330097086808</v>
       </c>
       <c r="F50" t="s">
         <v>6</v>
@@ -2254,7 +2320,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B51">
         <v>4</v>
@@ -2263,10 +2329,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D51" s="1">
-        <v>198.99999999999997</v>
+        <v>219.50000000000006</v>
       </c>
       <c r="E51" s="2">
-        <v>0.79812834224599272</v>
+        <v>0.79915048543688738</v>
       </c>
       <c r="F51" t="s">
         <v>6</v>
@@ -2274,7 +2340,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B52">
         <v>4</v>
@@ -2283,10 +2349,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D52" s="1">
-        <v>199.66666666666663</v>
+        <v>220.16666666666671</v>
       </c>
       <c r="E52" s="2">
-        <v>0.80080213903743658</v>
+        <v>0.8015776699029068</v>
       </c>
       <c r="F52" t="s">
         <v>6</v>
@@ -2294,7 +2360,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B53">
         <v>4</v>
@@ -2303,10 +2369,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D53" s="1">
-        <v>200.33333333333329</v>
+        <v>220.83333333333337</v>
       </c>
       <c r="E53" s="2">
-        <v>0.80347593582888033</v>
+        <v>0.8040048543689261</v>
       </c>
       <c r="F53" t="s">
         <v>6</v>
@@ -2314,7 +2380,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B54">
         <v>4</v>
@@ -2323,10 +2389,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D54" s="1">
-        <v>200.99999999999994</v>
+        <v>221.50000000000003</v>
       </c>
       <c r="E54" s="2">
-        <v>0.80614973262032419</v>
+        <v>0.80643203883494552</v>
       </c>
       <c r="F54" t="s">
         <v>6</v>
@@ -2334,7 +2400,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B55">
         <v>4</v>
@@ -2343,10 +2409,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D55" s="1">
-        <v>201.6666666666666</v>
+        <v>222.16666666666669</v>
       </c>
       <c r="E55" s="2">
-        <v>0.80882352941176805</v>
+        <v>0.80885922330096482</v>
       </c>
       <c r="F55" t="s">
         <v>6</v>
@@ -2363,10 +2429,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D56" s="1">
-        <v>202.33333333333326</v>
+        <v>222.83333333333334</v>
       </c>
       <c r="E56" s="2">
-        <v>0.8114973262032118</v>
+        <v>0.81128640776698424</v>
       </c>
       <c r="F56" t="s">
         <v>6</v>
@@ -2374,7 +2440,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B57">
         <v>4</v>
@@ -2383,10 +2449,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D57" s="1">
-        <v>202.99999999999991</v>
+        <v>223.5</v>
       </c>
       <c r="E57" s="2">
-        <v>0.81417112299465566</v>
+        <v>0.81371359223300355</v>
       </c>
       <c r="F57" t="s">
         <v>6</v>
@@ -2394,7 +2460,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="B58">
         <v>4</v>
@@ -2403,10 +2469,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D58" s="1">
-        <v>203.66666666666657</v>
+        <v>224.16666666666666</v>
       </c>
       <c r="E58" s="2">
-        <v>0.81684491978609952</v>
+        <v>0.81614077669902296</v>
       </c>
       <c r="F58" t="s">
         <v>6</v>
@@ -2414,7 +2480,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B59">
         <v>4</v>
@@ -2423,10 +2489,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D59" s="1">
-        <v>204.33333333333323</v>
+        <v>224.83333333333331</v>
       </c>
       <c r="E59" s="2">
-        <v>0.81951871657754327</v>
+        <v>0.81856796116504227</v>
       </c>
       <c r="F59" t="s">
         <v>6</v>
@@ -2434,19 +2500,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C60" s="1">
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D60" s="1">
-        <v>204.83333333333323</v>
+        <v>225.49999999999997</v>
       </c>
       <c r="E60" s="2">
-        <v>0.82152406417112622</v>
+        <v>0.82099514563106168</v>
       </c>
       <c r="F60" t="s">
         <v>6</v>
@@ -2454,19 +2520,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C61" s="1">
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D61" s="1">
-        <v>205.33333333333323</v>
+        <v>226.16666666666663</v>
       </c>
       <c r="E61" s="2">
-        <v>0.82352941176470906</v>
+        <v>0.8234223300970811</v>
       </c>
       <c r="F61" t="s">
         <v>6</v>
@@ -2474,19 +2540,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C62" s="1">
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D62" s="1">
-        <v>205.83333333333323</v>
+        <v>226.83333333333329</v>
       </c>
       <c r="E62" s="2">
-        <v>0.82553475935829201</v>
+        <v>0.82584951456310041</v>
       </c>
       <c r="F62" t="s">
         <v>6</v>
@@ -2494,7 +2560,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B63">
         <v>3</v>
@@ -2503,10 +2569,10 @@
         <v>0.5</v>
       </c>
       <c r="D63" s="1">
-        <v>206.33333333333323</v>
+        <v>227.33333333333329</v>
       </c>
       <c r="E63" s="2">
-        <v>0.82754010695187485</v>
+        <v>0.827669902912615</v>
       </c>
       <c r="F63" t="s">
         <v>6</v>
@@ -2514,7 +2580,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="B64">
         <v>3</v>
@@ -2523,10 +2589,10 @@
         <v>0.5</v>
       </c>
       <c r="D64" s="1">
-        <v>206.83333333333323</v>
+        <v>227.83333333333329</v>
       </c>
       <c r="E64" s="2">
-        <v>0.82954545454545781</v>
+        <v>0.82949029126212948</v>
       </c>
       <c r="F64" t="s">
         <v>6</v>
@@ -2534,7 +2600,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="B65">
         <v>3</v>
@@ -2543,10 +2609,10 @@
         <v>0.5</v>
       </c>
       <c r="D65" s="1">
-        <v>207.33333333333323</v>
+        <v>228.33333333333329</v>
       </c>
       <c r="E65" s="2">
-        <v>0.83155080213904065</v>
+        <v>0.83131067961164407</v>
       </c>
       <c r="F65" t="s">
         <v>6</v>
@@ -2554,7 +2620,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B66">
         <v>3</v>
@@ -2563,10 +2629,10 @@
         <v>0.5</v>
       </c>
       <c r="D66" s="1">
-        <v>207.83333333333323</v>
+        <v>228.83333333333329</v>
       </c>
       <c r="E66" s="2">
-        <v>0.8335561497326236</v>
+        <v>0.83313106796115866</v>
       </c>
       <c r="F66" t="s">
         <v>6</v>
@@ -2574,7 +2640,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="B67">
         <v>3</v>
@@ -2583,10 +2649,10 @@
         <v>0.5</v>
       </c>
       <c r="D67" s="1">
-        <v>208.33333333333323</v>
+        <v>229.33333333333329</v>
       </c>
       <c r="E67" s="2">
-        <v>0.83556149732620644</v>
+        <v>0.83495145631067313</v>
       </c>
       <c r="F67" t="s">
         <v>6</v>
@@ -2594,7 +2660,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B68">
         <v>3</v>
@@ -2603,10 +2669,10 @@
         <v>0.5</v>
       </c>
       <c r="D68" s="1">
-        <v>208.83333333333323</v>
+        <v>229.83333333333329</v>
       </c>
       <c r="E68" s="2">
-        <v>0.83756684491978939</v>
+        <v>0.83677184466018772</v>
       </c>
       <c r="F68" t="s">
         <v>6</v>
@@ -2614,7 +2680,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B69">
         <v>3</v>
@@ -2623,10 +2689,10 @@
         <v>0.5</v>
       </c>
       <c r="D69" s="1">
-        <v>209.33333333333323</v>
+        <v>230.33333333333329</v>
       </c>
       <c r="E69" s="2">
-        <v>0.83957219251337223</v>
+        <v>0.83859223300970231</v>
       </c>
       <c r="F69" t="s">
         <v>6</v>
@@ -2634,7 +2700,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>75</v>
+        <v>221</v>
       </c>
       <c r="B70">
         <v>3</v>
@@ -2643,10 +2709,10 @@
         <v>0.5</v>
       </c>
       <c r="D70" s="1">
-        <v>209.83333333333323</v>
+        <v>230.83333333333329</v>
       </c>
       <c r="E70" s="2">
-        <v>0.84157754010695518</v>
+        <v>0.84041262135921679</v>
       </c>
       <c r="F70" t="s">
         <v>6</v>
@@ -2654,7 +2720,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B71">
         <v>3</v>
@@ -2663,10 +2729,10 @@
         <v>0.5</v>
       </c>
       <c r="D71" s="1">
-        <v>210.33333333333323</v>
+        <v>231.33333333333329</v>
       </c>
       <c r="E71" s="2">
-        <v>0.84358288770053802</v>
+        <v>0.84223300970873138</v>
       </c>
       <c r="F71" t="s">
         <v>6</v>
@@ -2683,10 +2749,10 @@
         <v>0.5</v>
       </c>
       <c r="D72" s="1">
-        <v>210.83333333333323</v>
+        <v>231.83333333333329</v>
       </c>
       <c r="E72" s="2">
-        <v>0.84558823529412097</v>
+        <v>0.84405339805824586</v>
       </c>
       <c r="F72" t="s">
         <v>6</v>
@@ -2694,7 +2760,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B73">
         <v>3</v>
@@ -2703,10 +2769,10 @@
         <v>0.5</v>
       </c>
       <c r="D73" s="1">
-        <v>211.33333333333323</v>
+        <v>232.33333333333329</v>
       </c>
       <c r="E73" s="2">
-        <v>0.84759358288770381</v>
+        <v>0.84587378640776045</v>
       </c>
       <c r="F73" t="s">
         <v>6</v>
@@ -2714,7 +2780,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B74">
         <v>3</v>
@@ -2723,10 +2789,10 @@
         <v>0.5</v>
       </c>
       <c r="D74" s="1">
-        <v>211.83333333333323</v>
+        <v>232.83333333333329</v>
       </c>
       <c r="E74" s="2">
-        <v>0.84959893048128676</v>
+        <v>0.84769417475727504</v>
       </c>
       <c r="F74" t="s">
         <v>6</v>
@@ -2734,7 +2800,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B75">
         <v>3</v>
@@ -2743,10 +2809,10 @@
         <v>0.5</v>
       </c>
       <c r="D75" s="1">
-        <v>212.33333333333323</v>
+        <v>233.33333333333329</v>
       </c>
       <c r="E75" s="2">
-        <v>0.8516042780748696</v>
+        <v>0.84951456310678952</v>
       </c>
       <c r="F75" t="s">
         <v>6</v>
@@ -2754,19 +2820,19 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C76" s="1">
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D76" s="1">
-        <v>212.83333333333323</v>
+        <v>233.66666666666663</v>
       </c>
       <c r="E76" s="2">
-        <v>0.85360962566845255</v>
+        <v>0.85072815533979929</v>
       </c>
       <c r="F76" t="s">
         <v>6</v>
@@ -2774,19 +2840,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C77" s="1">
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D77" s="1">
-        <v>213.33333333333323</v>
+        <v>233.99999999999997</v>
       </c>
       <c r="E77" s="2">
-        <v>0.85561497326203539</v>
+        <v>0.85194174757280905</v>
       </c>
       <c r="F77" t="s">
         <v>6</v>
@@ -2794,19 +2860,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>84</v>
+        <v>189</v>
       </c>
       <c r="B78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C78" s="1">
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D78" s="1">
-        <v>213.83333333333323</v>
+        <v>234.33333333333331</v>
       </c>
       <c r="E78" s="2">
-        <v>0.85762032085561835</v>
+        <v>0.85315533980581881</v>
       </c>
       <c r="F78" t="s">
         <v>6</v>
@@ -2814,7 +2880,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -2823,10 +2889,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D79" s="1">
-        <v>214.16666666666657</v>
+        <v>234.66666666666666</v>
       </c>
       <c r="E79" s="2">
-        <v>0.85895721925134028</v>
+        <v>0.85436893203882847</v>
       </c>
       <c r="F79" t="s">
         <v>6</v>
@@ -2834,7 +2900,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -2843,10 +2909,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D80" s="1">
-        <v>214.49999999999991</v>
+        <v>235</v>
       </c>
       <c r="E80" s="2">
-        <v>0.86029411764706232</v>
+        <v>0.85558252427183823</v>
       </c>
       <c r="F80" t="s">
         <v>6</v>
@@ -2854,7 +2920,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -2863,10 +2929,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D81" s="1">
-        <v>214.83333333333326</v>
+        <v>235.33333333333334</v>
       </c>
       <c r="E81" s="2">
-        <v>0.86163101604278425</v>
+        <v>0.85679611650484799</v>
       </c>
       <c r="F81" t="s">
         <v>6</v>
@@ -2874,7 +2940,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>88</v>
+        <v>254</v>
       </c>
       <c r="B82">
         <v>2</v>
@@ -2883,10 +2949,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D82" s="1">
-        <v>215.1666666666666</v>
+        <v>235.66666666666669</v>
       </c>
       <c r="E82" s="2">
-        <v>0.86296791443850618</v>
+        <v>0.85800970873785765</v>
       </c>
       <c r="F82" t="s">
         <v>6</v>
@@ -2894,7 +2960,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>89</v>
+        <v>139</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -2903,10 +2969,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D83" s="1">
-        <v>215.49999999999994</v>
+        <v>236.00000000000003</v>
       </c>
       <c r="E83" s="2">
-        <v>0.86430481283422822</v>
+        <v>0.85922330097086741</v>
       </c>
       <c r="F83" t="s">
         <v>6</v>
@@ -2914,7 +2980,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="B84">
         <v>2</v>
@@ -2923,10 +2989,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D84" s="1">
-        <v>215.83333333333329</v>
+        <v>236.33333333333337</v>
       </c>
       <c r="E84" s="2">
-        <v>0.86564171122995015</v>
+        <v>0.86043689320387717</v>
       </c>
       <c r="F84" t="s">
         <v>6</v>
@@ -2934,7 +3000,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B85">
         <v>2</v>
@@ -2943,10 +3009,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D85" s="1">
-        <v>216.16666666666663</v>
+        <v>236.66666666666671</v>
       </c>
       <c r="E85" s="2">
-        <v>0.86697860962567208</v>
+        <v>0.86165048543688694</v>
       </c>
       <c r="F85" t="s">
         <v>6</v>
@@ -2954,7 +3020,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -2963,10 +3029,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D86" s="1">
-        <v>216.49999999999997</v>
+        <v>237.00000000000006</v>
       </c>
       <c r="E86" s="2">
-        <v>0.86831550802139412</v>
+        <v>0.86286407766989659</v>
       </c>
       <c r="F86" t="s">
         <v>6</v>
@@ -2974,7 +3040,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>93</v>
+        <v>199</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -2983,10 +3049,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D87" s="1">
-        <v>216.83333333333331</v>
+        <v>237.3333333333334</v>
       </c>
       <c r="E87" s="2">
-        <v>0.86965240641711605</v>
+        <v>0.86407766990290635</v>
       </c>
       <c r="F87" t="s">
         <v>6</v>
@@ -2994,7 +3060,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>94</v>
+        <v>215</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -3003,10 +3069,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D88" s="1">
-        <v>217.16666666666666</v>
+        <v>237.66666666666674</v>
       </c>
       <c r="E88" s="2">
-        <v>0.87098930481283798</v>
+        <v>0.86529126213591612</v>
       </c>
       <c r="F88" t="s">
         <v>6</v>
@@ -3014,7 +3080,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>95</v>
+        <v>255</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -3023,10 +3089,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D89" s="1">
-        <v>217.5</v>
+        <v>238.00000000000009</v>
       </c>
       <c r="E89" s="2">
-        <v>0.87232620320856002</v>
+        <v>0.86650485436892588</v>
       </c>
       <c r="F89" t="s">
         <v>6</v>
@@ -3034,7 +3100,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>96</v>
+        <v>256</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -3043,10 +3109,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D90" s="1">
-        <v>217.83333333333334</v>
+        <v>238.33333333333343</v>
       </c>
       <c r="E90" s="2">
-        <v>0.87366310160428196</v>
+        <v>0.86771844660193553</v>
       </c>
       <c r="F90" t="s">
         <v>6</v>
@@ -3054,7 +3120,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>97</v>
+        <v>184</v>
       </c>
       <c r="B91">
         <v>2</v>
@@ -3063,10 +3129,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D91" s="1">
-        <v>218.16666666666669</v>
+        <v>238.66666666666677</v>
       </c>
       <c r="E91" s="2">
-        <v>0.87500000000000389</v>
+        <v>0.8689320388349453</v>
       </c>
       <c r="F91" t="s">
         <v>6</v>
@@ -3074,7 +3140,7 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -3083,10 +3149,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D92" s="1">
-        <v>218.50000000000003</v>
+        <v>239.00000000000011</v>
       </c>
       <c r="E92" s="2">
-        <v>0.87633689839572593</v>
+        <v>0.87014563106795506</v>
       </c>
       <c r="F92" t="s">
         <v>6</v>
@@ -3094,7 +3160,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -3103,10 +3169,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D93" s="1">
-        <v>218.83333333333337</v>
+        <v>239.33333333333346</v>
       </c>
       <c r="E93" s="2">
-        <v>0.87767379679144786</v>
+        <v>0.87135922330096482</v>
       </c>
       <c r="F93" t="s">
         <v>6</v>
@@ -3114,7 +3180,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="B94">
         <v>2</v>
@@ -3123,10 +3189,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D94" s="1">
-        <v>219.16666666666671</v>
+        <v>239.6666666666668</v>
       </c>
       <c r="E94" s="2">
-        <v>0.87901069518716979</v>
+        <v>0.87257281553397448</v>
       </c>
       <c r="F94" t="s">
         <v>6</v>
@@ -3134,7 +3200,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="B95">
         <v>2</v>
@@ -3143,10 +3209,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D95" s="1">
-        <v>219.50000000000006</v>
+        <v>240.00000000000014</v>
       </c>
       <c r="E95" s="2">
-        <v>0.88034759358289183</v>
+        <v>0.87378640776698424</v>
       </c>
       <c r="F95" t="s">
         <v>6</v>
@@ -3154,7 +3220,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>102</v>
+        <v>193</v>
       </c>
       <c r="B96">
         <v>2</v>
@@ -3163,10 +3229,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D96" s="1">
-        <v>219.8333333333334</v>
+        <v>240.33333333333348</v>
       </c>
       <c r="E96" s="2">
-        <v>0.88168449197861376</v>
+        <v>0.874999999999994</v>
       </c>
       <c r="F96" t="s">
         <v>6</v>
@@ -3174,7 +3240,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B97">
         <v>2</v>
@@ -3183,10 +3249,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D97" s="1">
-        <v>220.16666666666674</v>
+        <v>240.66666666666683</v>
       </c>
       <c r="E97" s="2">
-        <v>0.8830213903743358</v>
+        <v>0.87621359223300366</v>
       </c>
       <c r="F97" t="s">
         <v>6</v>
@@ -3194,7 +3260,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>104</v>
+        <v>195</v>
       </c>
       <c r="B98">
         <v>2</v>
@@ -3203,10 +3269,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D98" s="1">
-        <v>220.50000000000009</v>
+        <v>241.00000000000017</v>
       </c>
       <c r="E98" s="2">
-        <v>0.88435828877005773</v>
+        <v>0.87742718446601342</v>
       </c>
       <c r="F98" t="s">
         <v>6</v>
@@ -3214,7 +3280,7 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>105</v>
+        <v>194</v>
       </c>
       <c r="B99">
         <v>2</v>
@@ -3223,10 +3289,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D99" s="1">
-        <v>220.83333333333343</v>
+        <v>241.33333333333351</v>
       </c>
       <c r="E99" s="2">
-        <v>0.88569518716577966</v>
+        <v>0.87864077669902318</v>
       </c>
       <c r="F99" t="s">
         <v>6</v>
@@ -3234,7 +3300,7 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="B100">
         <v>2</v>
@@ -3243,10 +3309,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D100" s="1">
-        <v>221.16666666666677</v>
+        <v>241.66666666666686</v>
       </c>
       <c r="E100" s="2">
-        <v>0.8870320855615017</v>
+        <v>0.87985436893203295</v>
       </c>
       <c r="F100" t="s">
         <v>6</v>
@@ -3254,7 +3320,7 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B101">
         <v>2</v>
@@ -3263,10 +3329,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D101" s="1">
-        <v>221.50000000000011</v>
+        <v>242.0000000000002</v>
       </c>
       <c r="E101" s="2">
-        <v>0.88836898395722363</v>
+        <v>0.8810679611650426</v>
       </c>
       <c r="F101" t="s">
         <v>6</v>
@@ -3274,7 +3340,7 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="B102">
         <v>2</v>
@@ -3283,10 +3349,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D102" s="1">
-        <v>221.83333333333346</v>
+        <v>242.33333333333354</v>
       </c>
       <c r="E102" s="2">
-        <v>0.88970588235294557</v>
+        <v>0.88228155339805237</v>
       </c>
       <c r="F102" t="s">
         <v>6</v>
@@ -3294,7 +3360,7 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B103">
         <v>2</v>
@@ -3303,10 +3369,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D103" s="1">
-        <v>222.1666666666668</v>
+        <v>242.66666666666688</v>
       </c>
       <c r="E103" s="2">
-        <v>0.89104278074866761</v>
+        <v>0.88349514563106213</v>
       </c>
       <c r="F103" t="s">
         <v>6</v>
@@ -3323,10 +3389,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D104" s="1">
-        <v>222.50000000000014</v>
+        <v>243.00000000000023</v>
       </c>
       <c r="E104" s="2">
-        <v>0.89237967914438954</v>
+        <v>0.88470873786407189</v>
       </c>
       <c r="F104" t="s">
         <v>6</v>
@@ -3334,7 +3400,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="B105">
         <v>2</v>
@@ -3343,10 +3409,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D105" s="1">
-        <v>222.83333333333348</v>
+        <v>243.33333333333357</v>
       </c>
       <c r="E105" s="2">
-        <v>0.89371657754011147</v>
+        <v>0.88592233009708155</v>
       </c>
       <c r="F105" t="s">
         <v>6</v>
@@ -3354,7 +3420,7 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>112</v>
+        <v>214</v>
       </c>
       <c r="B106">
         <v>2</v>
@@ -3363,10 +3429,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D106" s="1">
-        <v>223.16666666666683</v>
+        <v>243.66666666666691</v>
       </c>
       <c r="E106" s="2">
-        <v>0.89505347593583351</v>
+        <v>0.88713592233009131</v>
       </c>
       <c r="F106" t="s">
         <v>6</v>
@@ -3374,7 +3440,7 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="B107">
         <v>2</v>
@@ -3383,10 +3449,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D107" s="1">
-        <v>223.50000000000017</v>
+        <v>244.00000000000026</v>
       </c>
       <c r="E107" s="2">
-        <v>0.89639037433155544</v>
+        <v>0.88834951456310107</v>
       </c>
       <c r="F107" t="s">
         <v>6</v>
@@ -3394,7 +3460,7 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B108">
         <v>2</v>
@@ -3403,10 +3469,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D108" s="1">
-        <v>223.83333333333351</v>
+        <v>244.3333333333336</v>
       </c>
       <c r="E108" s="2">
-        <v>0.89772727272727737</v>
+        <v>0.88956310679611084</v>
       </c>
       <c r="F108" t="s">
         <v>6</v>
@@ -3414,7 +3480,7 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>115</v>
+        <v>242</v>
       </c>
       <c r="B109">
         <v>2</v>
@@ -3423,10 +3489,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D109" s="1">
-        <v>224.16666666666686</v>
+        <v>244.66666666666694</v>
       </c>
       <c r="E109" s="2">
-        <v>0.89906417112299941</v>
+        <v>0.89077669902912049</v>
       </c>
       <c r="F109" t="s">
         <v>6</v>
@@ -3434,7 +3500,7 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B110">
         <v>2</v>
@@ -3443,18 +3509,18 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D110" s="1">
-        <v>224.5000000000002</v>
+        <v>245.00000000000028</v>
       </c>
       <c r="E110" s="2">
-        <v>0.90040106951872134</v>
+        <v>0.89199029126213025</v>
       </c>
       <c r="F110" t="s">
-        <v>45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="B111">
         <v>2</v>
@@ -3463,18 +3529,18 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D111" s="1">
-        <v>224.83333333333354</v>
+        <v>245.33333333333363</v>
       </c>
       <c r="E111" s="2">
-        <v>0.90173796791444327</v>
+        <v>0.89320388349514002</v>
       </c>
       <c r="F111" t="s">
-        <v>45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B112">
         <v>2</v>
@@ -3483,18 +3549,18 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D112" s="1">
-        <v>225.16666666666688</v>
+        <v>245.66666666666697</v>
       </c>
       <c r="E112" s="2">
-        <v>0.90307486631016531</v>
+        <v>0.89441747572814967</v>
       </c>
       <c r="F112" t="s">
-        <v>45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="B113">
         <v>2</v>
@@ -3503,18 +3569,18 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D113" s="1">
-        <v>225.50000000000023</v>
+        <v>246.00000000000031</v>
       </c>
       <c r="E113" s="2">
-        <v>0.90441176470588724</v>
+        <v>0.89563106796115943</v>
       </c>
       <c r="F113" t="s">
-        <v>45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="B114">
         <v>2</v>
@@ -3523,70 +3589,70 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D114" s="1">
-        <v>225.83333333333357</v>
+        <v>246.33333333333366</v>
       </c>
       <c r="E114" s="2">
-        <v>0.90574866310160917</v>
+        <v>0.8968446601941692</v>
       </c>
       <c r="F114" t="s">
-        <v>45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>121</v>
+        <v>174</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C115" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D115" s="1">
-        <v>226.00000000000023</v>
+        <v>246.666666666667</v>
       </c>
       <c r="E115" s="2">
-        <v>0.9064171122994702</v>
+        <v>0.89805825242717896</v>
       </c>
       <c r="F115" t="s">
-        <v>45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C116" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D116" s="1">
-        <v>226.16666666666688</v>
+        <v>247.00000000000034</v>
       </c>
       <c r="E116" s="2">
-        <v>0.90708556149733111</v>
+        <v>0.89927184466018861</v>
       </c>
       <c r="F116" t="s">
-        <v>45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C117" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D117" s="1">
-        <v>226.33333333333354</v>
+        <v>247.33333333333368</v>
       </c>
       <c r="E117" s="2">
-        <v>0.90775401069519202</v>
+        <v>0.90048543689319838</v>
       </c>
       <c r="F117" t="s">
         <v>45</v>
@@ -3594,19 +3660,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C118" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D118" s="1">
-        <v>226.5000000000002</v>
+        <v>247.66666666666703</v>
       </c>
       <c r="E118" s="2">
-        <v>0.90842245989305292</v>
+        <v>0.90169902912620814</v>
       </c>
       <c r="F118" t="s">
         <v>45</v>
@@ -3614,19 +3680,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C119" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D119" s="1">
-        <v>226.66666666666686</v>
+        <v>248.00000000000037</v>
       </c>
       <c r="E119" s="2">
-        <v>0.90909090909091383</v>
+        <v>0.9029126213592179</v>
       </c>
       <c r="F119" t="s">
         <v>45</v>
@@ -3634,19 +3700,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C120" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D120" s="1">
-        <v>226.83333333333351</v>
+        <v>248.33333333333371</v>
       </c>
       <c r="E120" s="2">
-        <v>0.90975935828877474</v>
+        <v>0.90412621359222756</v>
       </c>
       <c r="F120" t="s">
         <v>45</v>
@@ -3654,19 +3720,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>127</v>
+        <v>67</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C121" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D121" s="1">
-        <v>227.00000000000017</v>
+        <v>248.66666666666706</v>
       </c>
       <c r="E121" s="2">
-        <v>0.91042780748663577</v>
+        <v>0.90533980582523732</v>
       </c>
       <c r="F121" t="s">
         <v>45</v>
@@ -3674,7 +3740,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>128</v>
+        <v>230</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -3683,10 +3749,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D122" s="1">
-        <v>227.16666666666683</v>
+        <v>248.83333333333371</v>
       </c>
       <c r="E122" s="2">
-        <v>0.91109625668449667</v>
+        <v>0.90594660194174215</v>
       </c>
       <c r="F122" t="s">
         <v>45</v>
@@ -3694,7 +3760,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -3703,10 +3769,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D123" s="1">
-        <v>227.33333333333348</v>
+        <v>249.00000000000037</v>
       </c>
       <c r="E123" s="2">
-        <v>0.91176470588235758</v>
+        <v>0.90655339805824697</v>
       </c>
       <c r="F123" t="s">
         <v>45</v>
@@ -3714,7 +3780,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -3723,10 +3789,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D124" s="1">
-        <v>227.50000000000014</v>
+        <v>249.16666666666703</v>
       </c>
       <c r="E124" s="2">
-        <v>0.91243315508021849</v>
+        <v>0.9071601941747518</v>
       </c>
       <c r="F124" t="s">
         <v>45</v>
@@ -3734,7 +3800,7 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -3743,10 +3809,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D125" s="1">
-        <v>227.6666666666668</v>
+        <v>249.33333333333368</v>
       </c>
       <c r="E125" s="2">
-        <v>0.9131016042780794</v>
+        <v>0.90776699029125663</v>
       </c>
       <c r="F125" t="s">
         <v>45</v>
@@ -3754,7 +3820,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -3763,10 +3829,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D126" s="1">
-        <v>227.83333333333346</v>
+        <v>249.50000000000034</v>
       </c>
       <c r="E126" s="2">
-        <v>0.91377005347594031</v>
+        <v>0.90837378640776145</v>
       </c>
       <c r="F126" t="s">
         <v>45</v>
@@ -3774,7 +3840,7 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -3783,10 +3849,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D127" s="1">
-        <v>228.00000000000011</v>
+        <v>249.666666666667</v>
       </c>
       <c r="E127" s="2">
-        <v>0.91443850267380122</v>
+        <v>0.90898058252426617</v>
       </c>
       <c r="F127" t="s">
         <v>45</v>
@@ -3794,7 +3860,7 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>134</v>
+        <v>212</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -3803,10 +3869,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D128" s="1">
-        <v>228.16666666666677</v>
+        <v>249.83333333333366</v>
       </c>
       <c r="E128" s="2">
-        <v>0.91510695187166224</v>
+        <v>0.90958737864077099</v>
       </c>
       <c r="F128" t="s">
         <v>45</v>
@@ -3814,7 +3880,7 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>135</v>
+        <v>241</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -3823,10 +3889,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D129" s="1">
-        <v>228.33333333333343</v>
+        <v>250.00000000000031</v>
       </c>
       <c r="E129" s="2">
-        <v>0.91577540106952315</v>
+        <v>0.91019417475727582</v>
       </c>
       <c r="F129" t="s">
         <v>45</v>
@@ -3834,7 +3900,7 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -3843,10 +3909,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D130" s="1">
-        <v>228.50000000000009</v>
+        <v>250.16666666666697</v>
       </c>
       <c r="E130" s="2">
-        <v>0.91644385026738406</v>
+        <v>0.91080097087378065</v>
       </c>
       <c r="F130" t="s">
         <v>45</v>
@@ -3854,7 +3920,7 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -3863,10 +3929,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D131" s="1">
-        <v>228.66666666666674</v>
+        <v>250.33333333333363</v>
       </c>
       <c r="E131" s="2">
-        <v>0.91711229946524497</v>
+        <v>0.91140776699028547</v>
       </c>
       <c r="F131" t="s">
         <v>45</v>
@@ -3874,7 +3940,7 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>138</v>
+        <v>209</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -3883,10 +3949,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D132" s="1">
-        <v>228.8333333333334</v>
+        <v>250.50000000000028</v>
       </c>
       <c r="E132" s="2">
-        <v>0.91778074866310588</v>
+        <v>0.9120145631067903</v>
       </c>
       <c r="F132" t="s">
         <v>45</v>
@@ -3894,7 +3960,7 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -3903,10 +3969,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D133" s="1">
-        <v>229.00000000000006</v>
+        <v>250.66666666666694</v>
       </c>
       <c r="E133" s="2">
-        <v>0.91844919786096679</v>
+        <v>0.91262135922329513</v>
       </c>
       <c r="F133" t="s">
         <v>45</v>
@@ -3914,7 +3980,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>140</v>
+        <v>232</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -3923,10 +3989,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D134" s="1">
-        <v>229.16666666666671</v>
+        <v>250.8333333333336</v>
       </c>
       <c r="E134" s="2">
-        <v>0.91911764705882781</v>
+        <v>0.91322815533979995</v>
       </c>
       <c r="F134" t="s">
         <v>45</v>
@@ -3934,7 +4000,7 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>141</v>
+        <v>173</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -3943,10 +4009,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D135" s="1">
-        <v>229.33333333333337</v>
+        <v>251.00000000000026</v>
       </c>
       <c r="E135" s="2">
-        <v>0.91978609625668872</v>
+        <v>0.91383495145630478</v>
       </c>
       <c r="F135" t="s">
         <v>45</v>
@@ -3954,7 +4020,7 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -3963,10 +4029,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D136" s="1">
-        <v>229.50000000000003</v>
+        <v>251.16666666666691</v>
       </c>
       <c r="E136" s="2">
-        <v>0.92045454545454963</v>
+        <v>0.9144417475728096</v>
       </c>
       <c r="F136" t="s">
         <v>45</v>
@@ -3974,7 +4040,7 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -3983,10 +4049,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D137" s="1">
-        <v>229.66666666666669</v>
+        <v>251.33333333333357</v>
       </c>
       <c r="E137" s="2">
-        <v>0.92112299465241054</v>
+        <v>0.91504854368931432</v>
       </c>
       <c r="F137" t="s">
         <v>45</v>
@@ -3994,7 +4060,7 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>144</v>
+        <v>257</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -4003,10 +4069,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D138" s="1">
-        <v>229.83333333333334</v>
+        <v>251.50000000000023</v>
       </c>
       <c r="E138" s="2">
-        <v>0.92179144385027145</v>
+        <v>0.91565533980581915</v>
       </c>
       <c r="F138" t="s">
         <v>45</v>
@@ -4014,7 +4080,7 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -4023,10 +4089,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D139" s="1">
-        <v>230</v>
+        <v>251.66666666666688</v>
       </c>
       <c r="E139" s="2">
-        <v>0.92245989304813236</v>
+        <v>0.91626213592232397</v>
       </c>
       <c r="F139" t="s">
         <v>45</v>
@@ -4034,7 +4100,7 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -4043,10 +4109,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D140" s="1">
-        <v>230.16666666666666</v>
+        <v>251.83333333333354</v>
       </c>
       <c r="E140" s="2">
-        <v>0.92312834224599338</v>
+        <v>0.9168689320388288</v>
       </c>
       <c r="F140" t="s">
         <v>45</v>
@@ -4054,7 +4120,7 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -4063,18 +4129,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D141" s="1">
-        <v>230.33333333333331</v>
+        <v>252.0000000000002</v>
       </c>
       <c r="E141" s="2">
-        <v>0.92379679144385429</v>
+        <v>0.91747572815533363</v>
       </c>
       <c r="F141" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="3">
-        <v>77160020500</v>
+      <c r="A142" s="3" t="s">
+        <v>108</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -4083,10 +4149,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D142" s="1">
-        <v>230.49999999999997</v>
+        <v>252.16666666666686</v>
       </c>
       <c r="E142" s="2">
-        <v>0.9244652406417152</v>
+        <v>0.91808252427183845</v>
       </c>
       <c r="F142" t="s">
         <v>45</v>
@@ -4094,7 +4160,7 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -4103,10 +4169,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D143" s="1">
-        <v>230.66666666666663</v>
+        <v>252.33333333333351</v>
       </c>
       <c r="E143" s="2">
-        <v>0.92513368983957611</v>
+        <v>0.91868932038834328</v>
       </c>
       <c r="F143" t="s">
         <v>45</v>
@@ -4114,7 +4180,7 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>149</v>
+        <v>119</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -4123,10 +4189,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D144" s="1">
-        <v>230.83333333333329</v>
+        <v>252.50000000000017</v>
       </c>
       <c r="E144" s="2">
-        <v>0.92580213903743702</v>
+        <v>0.9192961165048481</v>
       </c>
       <c r="F144" t="s">
         <v>45</v>
@@ -4134,7 +4200,7 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -4143,10 +4209,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D145" s="1">
-        <v>230.99999999999994</v>
+        <v>252.66666666666683</v>
       </c>
       <c r="E145" s="2">
-        <v>0.92647058823529793</v>
+        <v>0.91990291262135293</v>
       </c>
       <c r="F145" t="s">
         <v>45</v>
@@ -4154,7 +4220,7 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -4163,10 +4229,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D146" s="1">
-        <v>231.1666666666666</v>
+        <v>252.83333333333348</v>
       </c>
       <c r="E146" s="2">
-        <v>0.92713903743315895</v>
+        <v>0.92050970873785776</v>
       </c>
       <c r="F146" t="s">
         <v>45</v>
@@ -4174,7 +4240,7 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -4183,10 +4249,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D147" s="1">
-        <v>231.33333333333326</v>
+        <v>253.00000000000014</v>
       </c>
       <c r="E147" s="2">
-        <v>0.92780748663101986</v>
+        <v>0.92111650485436247</v>
       </c>
       <c r="F147" t="s">
         <v>45</v>
@@ -4194,7 +4260,7 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -4203,10 +4269,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D148" s="1">
-        <v>231.49999999999991</v>
+        <v>253.1666666666668</v>
       </c>
       <c r="E148" s="2">
-        <v>0.92847593582888077</v>
+        <v>0.9217233009708673</v>
       </c>
       <c r="F148" t="s">
         <v>45</v>
@@ -4214,7 +4280,7 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>154</v>
+        <v>206</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -4223,10 +4289,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D149" s="1">
-        <v>231.66666666666657</v>
+        <v>253.33333333333346</v>
       </c>
       <c r="E149" s="2">
-        <v>0.92914438502674168</v>
+        <v>0.92233009708737212</v>
       </c>
       <c r="F149" t="s">
         <v>45</v>
@@ -4234,7 +4300,7 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>155</v>
+        <v>226</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -4243,10 +4309,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D150" s="1">
-        <v>231.83333333333323</v>
+        <v>253.50000000000011</v>
       </c>
       <c r="E150" s="2">
-        <v>0.92981283422460259</v>
+        <v>0.92293689320387695</v>
       </c>
       <c r="F150" t="s">
         <v>45</v>
@@ -4254,7 +4320,7 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -4263,10 +4329,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D151" s="1">
-        <v>231.99999999999989</v>
+        <v>253.66666666666677</v>
       </c>
       <c r="E151" s="2">
-        <v>0.9304812834224635</v>
+        <v>0.92354368932038178</v>
       </c>
       <c r="F151" t="s">
         <v>45</v>
@@ -4274,7 +4340,7 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>157</v>
+        <v>95</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -4283,10 +4349,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D152" s="1">
-        <v>232.16666666666654</v>
+        <v>253.83333333333343</v>
       </c>
       <c r="E152" s="2">
-        <v>0.93114973262032441</v>
+        <v>0.9241504854368866</v>
       </c>
       <c r="F152" t="s">
         <v>45</v>
@@ -4294,7 +4360,7 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -4303,10 +4369,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D153" s="1">
-        <v>232.3333333333332</v>
+        <v>254.00000000000009</v>
       </c>
       <c r="E153" s="2">
-        <v>0.93181818181818543</v>
+        <v>0.92475728155339143</v>
       </c>
       <c r="F153" t="s">
         <v>45</v>
@@ -4314,7 +4380,7 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>159</v>
+        <v>258</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -4323,10 +4389,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D154" s="1">
-        <v>232.49999999999986</v>
+        <v>254.16666666666674</v>
       </c>
       <c r="E154" s="2">
-        <v>0.93248663101604634</v>
+        <v>0.92536407766989626</v>
       </c>
       <c r="F154" t="s">
         <v>45</v>
@@ -4334,7 +4400,7 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>160</v>
+        <v>244</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -4343,10 +4409,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D155" s="1">
-        <v>232.66666666666652</v>
+        <v>254.3333333333334</v>
       </c>
       <c r="E155" s="2">
-        <v>0.93315508021390725</v>
+        <v>0.92597087378640108</v>
       </c>
       <c r="F155" t="s">
         <v>45</v>
@@ -4354,7 +4420,7 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -4363,18 +4429,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D156" s="1">
-        <v>232.83333333333317</v>
+        <v>254.50000000000006</v>
       </c>
       <c r="E156" s="2">
-        <v>0.93382352941176816</v>
+        <v>0.92657766990290591</v>
       </c>
       <c r="F156" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A157" s="3" t="s">
-        <v>162</v>
+      <c r="A157" s="3">
+        <v>77160020500</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -4383,10 +4449,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D157" s="1">
-        <v>232.99999999999983</v>
+        <v>254.66666666666671</v>
       </c>
       <c r="E157" s="2">
-        <v>0.93449197860962907</v>
+        <v>0.92718446601941062</v>
       </c>
       <c r="F157" t="s">
         <v>45</v>
@@ -4394,7 +4460,7 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>163</v>
+        <v>259</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -4403,10 +4469,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D158" s="1">
-        <v>233.16666666666649</v>
+        <v>254.83333333333337</v>
       </c>
       <c r="E158" s="2">
-        <v>0.93516042780748998</v>
+        <v>0.92779126213591545</v>
       </c>
       <c r="F158" t="s">
         <v>45</v>
@@ -4414,7 +4480,7 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>164</v>
+        <v>111</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -4423,10 +4489,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D159" s="1">
-        <v>233.33333333333314</v>
+        <v>255.00000000000003</v>
       </c>
       <c r="E159" s="2">
-        <v>0.935828877005351</v>
+        <v>0.92839805825242028</v>
       </c>
       <c r="F159" t="s">
         <v>45</v>
@@ -4434,7 +4500,7 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>165</v>
+        <v>260</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -4443,10 +4509,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D160" s="1">
-        <v>233.4999999999998</v>
+        <v>255.16666666666669</v>
       </c>
       <c r="E160" s="2">
-        <v>0.93649732620321191</v>
+        <v>0.9290048543689251</v>
       </c>
       <c r="F160" t="s">
         <v>45</v>
@@ -4454,7 +4520,7 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -4463,10 +4529,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D161" s="1">
-        <v>233.66666666666646</v>
+        <v>255.33333333333334</v>
       </c>
       <c r="E161" s="2">
-        <v>0.93716577540107282</v>
+        <v>0.92961165048542993</v>
       </c>
       <c r="F161" t="s">
         <v>45</v>
@@ -4474,7 +4540,7 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -4483,10 +4549,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D162" s="1">
-        <v>233.83333333333312</v>
+        <v>255.5</v>
       </c>
       <c r="E162" s="2">
-        <v>0.93783422459893373</v>
+        <v>0.93021844660193476</v>
       </c>
       <c r="F162" t="s">
         <v>45</v>
@@ -4494,7 +4560,7 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -4503,10 +4569,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D163" s="1">
-        <v>233.99999999999977</v>
+        <v>255.66666666666666</v>
       </c>
       <c r="E163" s="2">
-        <v>0.93850267379679464</v>
+        <v>0.93082524271843958</v>
       </c>
       <c r="F163" t="s">
         <v>45</v>
@@ -4514,7 +4580,7 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -4523,10 +4589,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D164" s="1">
-        <v>234.16666666666643</v>
+        <v>255.83333333333331</v>
       </c>
       <c r="E164" s="2">
-        <v>0.93917112299465555</v>
+        <v>0.93143203883494441</v>
       </c>
       <c r="F164" t="s">
         <v>45</v>
@@ -4534,7 +4600,7 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>170</v>
+        <v>261</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -4543,10 +4609,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D165" s="1">
-        <v>234.33333333333309</v>
+        <v>255.99999999999997</v>
       </c>
       <c r="E165" s="2">
-        <v>0.93983957219251657</v>
+        <v>0.93203883495144924</v>
       </c>
       <c r="F165" t="s">
         <v>45</v>
@@ -4554,7 +4620,7 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>171</v>
+        <v>262</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -4563,10 +4629,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D166" s="1">
-        <v>234.49999999999974</v>
+        <v>256.16666666666663</v>
       </c>
       <c r="E166" s="2">
-        <v>0.94050802139037748</v>
+        <v>0.93264563106795406</v>
       </c>
       <c r="F166" t="s">
         <v>45</v>
@@ -4574,7 +4640,7 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>172</v>
+        <v>248</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -4583,10 +4649,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D167" s="1">
-        <v>234.6666666666664</v>
+        <v>256.33333333333331</v>
       </c>
       <c r="E167" s="2">
-        <v>0.94117647058823839</v>
+        <v>0.93325242718445889</v>
       </c>
       <c r="F167" t="s">
         <v>45</v>
@@ -4594,7 +4660,7 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -4603,10 +4669,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D168" s="1">
-        <v>234.83333333333306</v>
+        <v>256.5</v>
       </c>
       <c r="E168" s="2">
-        <v>0.9418449197860993</v>
+        <v>0.93385922330096383</v>
       </c>
       <c r="F168" t="s">
         <v>45</v>
@@ -4614,7 +4680,7 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -4623,10 +4689,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D169" s="1">
-        <v>234.99999999999972</v>
+        <v>256.66666666666669</v>
       </c>
       <c r="E169" s="2">
-        <v>0.94251336898396021</v>
+        <v>0.93446601941746876</v>
       </c>
       <c r="F169" t="s">
         <v>45</v>
@@ -4634,7 +4700,7 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -4643,10 +4709,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D170" s="1">
-        <v>235.16666666666637</v>
+        <v>256.83333333333337</v>
       </c>
       <c r="E170" s="2">
-        <v>0.94318181818182112</v>
+        <v>0.9350728155339737</v>
       </c>
       <c r="F170" t="s">
         <v>45</v>
@@ -4654,7 +4720,7 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -4663,10 +4729,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D171" s="1">
-        <v>235.33333333333303</v>
+        <v>257.00000000000006</v>
       </c>
       <c r="E171" s="2">
-        <v>0.94385026737968214</v>
+        <v>0.93567961165047864</v>
       </c>
       <c r="F171" t="s">
         <v>45</v>
@@ -4674,7 +4740,7 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>177</v>
+        <v>211</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -4683,10 +4749,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D172" s="1">
-        <v>235.49999999999969</v>
+        <v>257.16666666666674</v>
       </c>
       <c r="E172" s="2">
-        <v>0.94451871657754305</v>
+        <v>0.93628640776698357</v>
       </c>
       <c r="F172" t="s">
         <v>45</v>
@@ -4694,7 +4760,7 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -4703,10 +4769,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D173" s="1">
-        <v>235.66666666666634</v>
+        <v>257.33333333333343</v>
       </c>
       <c r="E173" s="2">
-        <v>0.94518716577540396</v>
+        <v>0.9368932038834884</v>
       </c>
       <c r="F173" t="s">
         <v>45</v>
@@ -4714,7 +4780,7 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -4723,10 +4789,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D174" s="1">
-        <v>235.833333333333</v>
+        <v>257.50000000000011</v>
       </c>
       <c r="E174" s="2">
-        <v>0.94585561497326487</v>
+        <v>0.93749999999999334</v>
       </c>
       <c r="F174" t="s">
         <v>45</v>
@@ -4734,7 +4800,7 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -4743,10 +4809,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D175" s="1">
-        <v>235.99999999999966</v>
+        <v>257.6666666666668</v>
       </c>
       <c r="E175" s="2">
-        <v>0.94652406417112578</v>
+        <v>0.93810679611649828</v>
       </c>
       <c r="F175" t="s">
         <v>45</v>
@@ -4754,7 +4820,7 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -4763,10 +4829,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D176" s="1">
-        <v>236.16666666666632</v>
+        <v>257.83333333333348</v>
       </c>
       <c r="E176" s="2">
-        <v>0.94719251336898669</v>
+        <v>0.93871359223300321</v>
       </c>
       <c r="F176" t="s">
         <v>45</v>
@@ -4774,7 +4840,7 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>182</v>
+        <v>155</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -4783,10 +4849,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D177" s="1">
-        <v>236.33333333333297</v>
+        <v>258.00000000000017</v>
       </c>
       <c r="E177" s="2">
-        <v>0.94786096256684771</v>
+        <v>0.93932038834950815</v>
       </c>
       <c r="F177" t="s">
         <v>45</v>
@@ -4794,7 +4860,7 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>183</v>
+        <v>263</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -4803,10 +4869,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D178" s="1">
-        <v>236.49999999999963</v>
+        <v>258.16666666666686</v>
       </c>
       <c r="E178" s="2">
-        <v>0.94852941176470862</v>
+        <v>0.93992718446601309</v>
       </c>
       <c r="F178" t="s">
         <v>45</v>
@@ -4814,7 +4880,7 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -4823,10 +4889,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D179" s="1">
-        <v>236.66666666666629</v>
+        <v>258.33333333333354</v>
       </c>
       <c r="E179" s="2">
-        <v>0.94919786096256953</v>
+        <v>0.94053398058251791</v>
       </c>
       <c r="F179" t="s">
         <v>45</v>
@@ -4834,7 +4900,7 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>185</v>
+        <v>224</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -4843,10 +4909,10 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D180" s="1">
-        <v>236.83333333333294</v>
+        <v>258.50000000000023</v>
       </c>
       <c r="E180" s="2">
-        <v>0.94986631016043044</v>
+        <v>0.94114077669902285</v>
       </c>
       <c r="F180" t="s">
         <v>45</v>
@@ -4863,18 +4929,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D181" s="1">
-        <v>236.9999999999996</v>
+        <v>258.66666666666691</v>
       </c>
       <c r="E181" s="2">
-        <v>0.95053475935829135</v>
+        <v>0.94174757281552779</v>
       </c>
       <c r="F181" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -4883,18 +4949,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D182" s="1">
-        <v>237.16666666666626</v>
+        <v>258.8333333333336</v>
       </c>
       <c r="E182" s="2">
-        <v>0.95120320855615226</v>
+        <v>0.94235436893203273</v>
       </c>
       <c r="F182" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
-        <v>189</v>
+        <v>264</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -4903,18 +4969,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D183" s="1">
-        <v>237.33333333333292</v>
+        <v>259.00000000000028</v>
       </c>
       <c r="E183" s="2">
-        <v>0.95187165775401317</v>
+        <v>0.94296116504853766</v>
       </c>
       <c r="F183" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>190</v>
+        <v>265</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -4923,18 +4989,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D184" s="1">
-        <v>237.49999999999957</v>
+        <v>259.16666666666697</v>
       </c>
       <c r="E184" s="2">
-        <v>0.95254010695187419</v>
+        <v>0.9435679611650426</v>
       </c>
       <c r="F184" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>191</v>
+        <v>266</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -4943,18 +5009,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D185" s="1">
-        <v>237.66666666666623</v>
+        <v>259.33333333333366</v>
       </c>
       <c r="E185" s="2">
-        <v>0.9532085561497351</v>
+        <v>0.94417475728154743</v>
       </c>
       <c r="F185" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>192</v>
+        <v>149</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -4963,18 +5029,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D186" s="1">
-        <v>237.83333333333289</v>
+        <v>259.50000000000034</v>
       </c>
       <c r="E186" s="2">
-        <v>0.95387700534759601</v>
+        <v>0.94478155339805237</v>
       </c>
       <c r="F186" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -4983,18 +5049,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D187" s="1">
-        <v>237.99999999999955</v>
+        <v>259.66666666666703</v>
       </c>
       <c r="E187" s="2">
-        <v>0.95454545454545692</v>
+        <v>0.9453883495145573</v>
       </c>
       <c r="F187" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -5003,18 +5069,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D188" s="1">
-        <v>238.1666666666662</v>
+        <v>259.83333333333371</v>
       </c>
       <c r="E188" s="2">
-        <v>0.95521390374331783</v>
+        <v>0.94599514563106224</v>
       </c>
       <c r="F188" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -5023,18 +5089,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D189" s="1">
-        <v>238.33333333333286</v>
+        <v>260.0000000000004</v>
       </c>
       <c r="E189" s="2">
-        <v>0.95588235294117874</v>
+        <v>0.94660194174756718</v>
       </c>
       <c r="F189" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -5043,18 +5109,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D190" s="1">
-        <v>238.49999999999952</v>
+        <v>260.16666666666708</v>
       </c>
       <c r="E190" s="2">
-        <v>0.95655080213903976</v>
+        <v>0.94720873786407211</v>
       </c>
       <c r="F190" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -5063,18 +5129,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D191" s="1">
-        <v>238.66666666666617</v>
+        <v>260.33333333333377</v>
       </c>
       <c r="E191" s="2">
-        <v>0.95721925133690067</v>
+        <v>0.94781553398057694</v>
       </c>
       <c r="F191" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>198</v>
+        <v>127</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -5083,18 +5149,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D192" s="1">
-        <v>238.83333333333283</v>
+        <v>260.50000000000045</v>
       </c>
       <c r="E192" s="2">
-        <v>0.95788770053476158</v>
+        <v>0.94842233009708188</v>
       </c>
       <c r="F192" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
-        <v>199</v>
+        <v>160</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -5103,18 +5169,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D193" s="1">
-        <v>238.99999999999949</v>
+        <v>260.66666666666714</v>
       </c>
       <c r="E193" s="2">
-        <v>0.95855614973262249</v>
+        <v>0.94902912621358682</v>
       </c>
       <c r="F193" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -5123,18 +5189,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D194" s="1">
-        <v>239.16666666666615</v>
+        <v>260.83333333333383</v>
       </c>
       <c r="E194" s="2">
-        <v>0.9592245989304834</v>
+        <v>0.94963592233009175</v>
       </c>
       <c r="F194" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
-        <v>201</v>
+        <v>234</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -5143,18 +5209,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D195" s="1">
-        <v>239.3333333333328</v>
+        <v>261.00000000000051</v>
       </c>
       <c r="E195" s="2">
-        <v>0.95989304812834431</v>
+        <v>0.95024271844659669</v>
       </c>
       <c r="F195" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
-        <v>202</v>
+        <v>268</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -5163,18 +5229,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D196" s="1">
-        <v>239.49999999999946</v>
+        <v>261.1666666666672</v>
       </c>
       <c r="E196" s="2">
-        <v>0.96056149732620533</v>
+        <v>0.95084951456310163</v>
       </c>
       <c r="F196" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -5183,18 +5249,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D197" s="1">
-        <v>239.66666666666612</v>
+        <v>261.33333333333388</v>
       </c>
       <c r="E197" s="2">
-        <v>0.96122994652406624</v>
+        <v>0.95145631067960645</v>
       </c>
       <c r="F197" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -5203,18 +5269,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D198" s="1">
-        <v>239.83333333333277</v>
+        <v>261.50000000000057</v>
       </c>
       <c r="E198" s="2">
-        <v>0.96189839572192715</v>
+        <v>0.95206310679611139</v>
       </c>
       <c r="F198" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
-        <v>205</v>
+        <v>43</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -5223,18 +5289,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D199" s="1">
-        <v>239.99999999999943</v>
+        <v>261.66666666666725</v>
       </c>
       <c r="E199" s="2">
-        <v>0.96256684491978806</v>
+        <v>0.95266990291261633</v>
       </c>
       <c r="F199" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -5243,18 +5309,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D200" s="1">
-        <v>240.16666666666609</v>
+        <v>261.83333333333394</v>
       </c>
       <c r="E200" s="2">
-        <v>0.96323529411764897</v>
+        <v>0.95327669902912127</v>
       </c>
       <c r="F200" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -5263,18 +5329,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D201" s="1">
-        <v>240.33333333333275</v>
+        <v>262.00000000000063</v>
       </c>
       <c r="E201" s="2">
-        <v>0.96390374331550988</v>
+        <v>0.9538834951456262</v>
       </c>
       <c r="F201" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
-        <v>208</v>
+        <v>120</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -5283,18 +5349,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D202" s="1">
-        <v>240.4999999999994</v>
+        <v>262.16666666666731</v>
       </c>
       <c r="E202" s="2">
-        <v>0.9645721925133709</v>
+        <v>0.95449029126213114</v>
       </c>
       <c r="F202" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
-        <v>209</v>
+        <v>269</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -5303,18 +5369,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D203" s="1">
-        <v>240.66666666666606</v>
+        <v>262.333333333334</v>
       </c>
       <c r="E203" s="2">
-        <v>0.96524064171123181</v>
+        <v>0.95509708737863597</v>
       </c>
       <c r="F203" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -5323,18 +5389,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D204" s="1">
-        <v>240.83333333333272</v>
+        <v>262.50000000000068</v>
       </c>
       <c r="E204" s="2">
-        <v>0.96590909090909272</v>
+        <v>0.9557038834951409</v>
       </c>
       <c r="F204" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -5343,18 +5409,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D205" s="1">
-        <v>240.99999999999937</v>
+        <v>262.66666666666737</v>
       </c>
       <c r="E205" s="2">
-        <v>0.96657754010695363</v>
+        <v>0.95631067961164584</v>
       </c>
       <c r="F205" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -5363,18 +5429,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D206" s="1">
-        <v>241.16666666666603</v>
+        <v>262.83333333333405</v>
       </c>
       <c r="E206" s="2">
-        <v>0.96724598930481454</v>
+        <v>0.95691747572815078</v>
       </c>
       <c r="F206" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>213</v>
+        <v>243</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -5383,18 +5449,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D207" s="1">
-        <v>241.33333333333269</v>
+        <v>263.00000000000074</v>
       </c>
       <c r="E207" s="2">
-        <v>0.96791443850267544</v>
+        <v>0.95752427184465572</v>
       </c>
       <c r="F207" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>214</v>
+        <v>156</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -5403,18 +5469,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D208" s="1">
-        <v>241.49999999999935</v>
+        <v>263.16666666666742</v>
       </c>
       <c r="E208" s="2">
-        <v>0.96858288770053635</v>
+        <v>0.95813106796116065</v>
       </c>
       <c r="F208" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -5423,18 +5489,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D209" s="1">
-        <v>241.666666666666</v>
+        <v>263.33333333333411</v>
       </c>
       <c r="E209" s="2">
-        <v>0.96925133689839738</v>
+        <v>0.95873786407766548</v>
       </c>
       <c r="F209" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>216</v>
+        <v>126</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -5443,18 +5509,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D210" s="1">
-        <v>241.83333333333266</v>
+        <v>263.5000000000008</v>
       </c>
       <c r="E210" s="2">
-        <v>0.96991978609625829</v>
+        <v>0.95934466019417042</v>
       </c>
       <c r="F210" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -5463,18 +5529,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D211" s="1">
-        <v>241.99999999999932</v>
+        <v>263.66666666666748</v>
       </c>
       <c r="E211" s="2">
-        <v>0.97058823529411919</v>
+        <v>0.95995145631067536</v>
       </c>
       <c r="F211" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>218</v>
+        <v>124</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -5483,18 +5549,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D212" s="1">
-        <v>242.16666666666598</v>
+        <v>263.83333333333417</v>
       </c>
       <c r="E212" s="2">
-        <v>0.9712566844919801</v>
+        <v>0.96055825242718029</v>
       </c>
       <c r="F212" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -5503,18 +5569,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D213" s="1">
-        <v>242.33333333333263</v>
+        <v>264.00000000000085</v>
       </c>
       <c r="E213" s="2">
-        <v>0.97192513368984101</v>
+        <v>0.96116504854368523</v>
       </c>
       <c r="F213" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -5523,18 +5589,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D214" s="1">
-        <v>242.49999999999929</v>
+        <v>264.16666666666754</v>
       </c>
       <c r="E214" s="2">
-        <v>0.97259358288770192</v>
+        <v>0.96177184466019017</v>
       </c>
       <c r="F214" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -5543,18 +5609,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D215" s="1">
-        <v>242.66666666666595</v>
+        <v>264.33333333333422</v>
       </c>
       <c r="E215" s="2">
-        <v>0.97326203208556294</v>
+        <v>0.96237864077669499</v>
       </c>
       <c r="F215" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -5563,18 +5629,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D216" s="1">
-        <v>242.8333333333326</v>
+        <v>264.50000000000091</v>
       </c>
       <c r="E216" s="2">
-        <v>0.97393048128342385</v>
+        <v>0.96298543689319993</v>
       </c>
       <c r="F216" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -5583,18 +5649,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D217" s="1">
-        <v>242.99999999999926</v>
+        <v>264.6666666666676</v>
       </c>
       <c r="E217" s="2">
-        <v>0.97459893048128476</v>
+        <v>0.96359223300970487</v>
       </c>
       <c r="F217" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -5603,18 +5669,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D218" s="1">
-        <v>243.16666666666592</v>
+        <v>264.83333333333428</v>
       </c>
       <c r="E218" s="2">
-        <v>0.97526737967914567</v>
+        <v>0.96419902912620981</v>
       </c>
       <c r="F218" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -5623,18 +5689,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D219" s="1">
-        <v>243.33333333333258</v>
+        <v>265.00000000000097</v>
       </c>
       <c r="E219" s="2">
-        <v>0.97593582887700658</v>
+        <v>0.96480582524271474</v>
       </c>
       <c r="F219" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -5643,18 +5709,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D220" s="1">
-        <v>243.49999999999923</v>
+        <v>265.16666666666765</v>
       </c>
       <c r="E220" s="2">
-        <v>0.97660427807486749</v>
+        <v>0.96541262135921968</v>
       </c>
       <c r="F220" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -5663,18 +5729,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D221" s="1">
-        <v>243.66666666666589</v>
+        <v>265.33333333333434</v>
       </c>
       <c r="E221" s="2">
-        <v>0.97727272727272851</v>
+        <v>0.96601941747572451</v>
       </c>
       <c r="F221" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -5683,18 +5749,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D222" s="1">
-        <v>243.83333333333255</v>
+        <v>265.50000000000102</v>
       </c>
       <c r="E222" s="2">
-        <v>0.97794117647058942</v>
+        <v>0.96662621359222944</v>
       </c>
       <c r="F222" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -5703,18 +5769,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D223" s="1">
-        <v>243.9999999999992</v>
+        <v>265.66666666666771</v>
       </c>
       <c r="E223" s="2">
-        <v>0.97860962566845033</v>
+        <v>0.96723300970873438</v>
       </c>
       <c r="F223" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -5723,18 +5789,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D224" s="1">
-        <v>244.16666666666586</v>
+        <v>265.83333333333439</v>
       </c>
       <c r="E224" s="2">
-        <v>0.97927807486631124</v>
+        <v>0.96783980582523932</v>
       </c>
       <c r="F224" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -5743,18 +5809,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D225" s="1">
-        <v>244.33333333333252</v>
+        <v>266.00000000000108</v>
       </c>
       <c r="E225" s="2">
-        <v>0.97994652406417215</v>
+        <v>0.96844660194174426</v>
       </c>
       <c r="F225" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
-        <v>232</v>
+        <v>271</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -5763,18 +5829,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D226" s="1">
-        <v>244.49999999999918</v>
+        <v>266.16666666666777</v>
       </c>
       <c r="E226" s="2">
-        <v>0.98061497326203306</v>
+        <v>0.96905339805824919</v>
       </c>
       <c r="F226" t="s">
-        <v>187</v>
+        <v>79</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -5783,18 +5849,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D227" s="1">
-        <v>244.66666666666583</v>
+        <v>266.33333333333445</v>
       </c>
       <c r="E227" s="2">
-        <v>0.98128342245989408</v>
+        <v>0.96966019417475402</v>
       </c>
       <c r="F227" t="s">
-        <v>187</v>
+        <v>79</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -5803,18 +5869,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D228" s="1">
-        <v>244.83333333333249</v>
+        <v>266.50000000000114</v>
       </c>
       <c r="E228" s="2">
-        <v>0.98195187165775499</v>
+        <v>0.97026699029125896</v>
       </c>
       <c r="F228" t="s">
-        <v>187</v>
+        <v>79</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -5823,18 +5889,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D229" s="1">
-        <v>244.99999999999915</v>
+        <v>266.66666666666782</v>
       </c>
       <c r="E229" s="2">
-        <v>0.9826203208556159</v>
+        <v>0.97087378640776389</v>
       </c>
       <c r="F229" t="s">
-        <v>187</v>
+        <v>79</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
-        <v>237</v>
+        <v>273</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -5843,18 +5909,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D230" s="1">
-        <v>245.1666666666658</v>
+        <v>266.83333333333451</v>
       </c>
       <c r="E230" s="2">
-        <v>0.98328877005347681</v>
+        <v>0.97148058252426883</v>
       </c>
       <c r="F230" t="s">
-        <v>187</v>
+        <v>79</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="B231">
         <v>1</v>
@@ -5863,18 +5929,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D231" s="1">
-        <v>245.33333333333246</v>
+        <v>267.00000000000119</v>
       </c>
       <c r="E231" s="2">
-        <v>0.98395721925133772</v>
+        <v>0.97208737864077377</v>
       </c>
       <c r="F231" t="s">
-        <v>187</v>
+        <v>79</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
-        <v>239</v>
+        <v>165</v>
       </c>
       <c r="B232">
         <v>1</v>
@@ -5883,18 +5949,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D232" s="1">
-        <v>245.49999999999912</v>
+        <v>267.16666666666788</v>
       </c>
       <c r="E232" s="2">
-        <v>0.98462566844919863</v>
+        <v>0.97269417475727871</v>
       </c>
       <c r="F232" t="s">
-        <v>187</v>
+        <v>79</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="B233">
         <v>1</v>
@@ -5903,18 +5969,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D233" s="1">
-        <v>245.66666666666578</v>
+        <v>267.33333333333456</v>
       </c>
       <c r="E233" s="2">
-        <v>0.98529411764705954</v>
+        <v>0.97330097087378353</v>
       </c>
       <c r="F233" t="s">
-        <v>187</v>
+        <v>79</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
-        <v>241</v>
+        <v>141</v>
       </c>
       <c r="B234">
         <v>1</v>
@@ -5923,18 +5989,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D234" s="1">
-        <v>245.83333333333243</v>
+        <v>267.50000000000125</v>
       </c>
       <c r="E234" s="2">
-        <v>0.98596256684492056</v>
+        <v>0.97390776699028847</v>
       </c>
       <c r="F234" t="s">
-        <v>187</v>
+        <v>79</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="B235">
         <v>1</v>
@@ -5943,18 +6009,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D235" s="1">
-        <v>245.99999999999909</v>
+        <v>267.66666666666794</v>
       </c>
       <c r="E235" s="2">
-        <v>0.98663101604278147</v>
+        <v>0.97451456310679341</v>
       </c>
       <c r="F235" t="s">
-        <v>187</v>
+        <v>79</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="B236">
         <v>1</v>
@@ -5963,18 +6029,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D236" s="1">
-        <v>246.16666666666575</v>
+        <v>267.83333333333462</v>
       </c>
       <c r="E236" s="2">
-        <v>0.98729946524064238</v>
+        <v>0.97512135922329835</v>
       </c>
       <c r="F236" t="s">
-        <v>187</v>
+        <v>79</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B237">
         <v>1</v>
@@ -5983,18 +6049,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D237" s="1">
-        <v>246.3333333333324</v>
+        <v>268.00000000000131</v>
       </c>
       <c r="E237" s="2">
-        <v>0.98796791443850329</v>
+        <v>0.97572815533980328</v>
       </c>
       <c r="F237" t="s">
-        <v>187</v>
+        <v>79</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
-        <v>245</v>
+        <v>122</v>
       </c>
       <c r="B238">
         <v>1</v>
@@ -6003,18 +6069,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D238" s="1">
-        <v>246.49999999999906</v>
+        <v>268.16666666666799</v>
       </c>
       <c r="E238" s="2">
-        <v>0.9886363636363642</v>
+        <v>0.97633495145630822</v>
       </c>
       <c r="F238" t="s">
-        <v>187</v>
+        <v>79</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="B239">
         <v>1</v>
@@ -6023,18 +6089,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D239" s="1">
-        <v>246.66666666666572</v>
+        <v>268.33333333333468</v>
       </c>
       <c r="E239" s="2">
-        <v>0.98930481283422511</v>
+        <v>0.97694174757281305</v>
       </c>
       <c r="F239" t="s">
-        <v>187</v>
+        <v>79</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
-        <v>247</v>
+        <v>169</v>
       </c>
       <c r="B240">
         <v>1</v>
@@ -6043,18 +6109,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D240" s="1">
-        <v>246.83333333333238</v>
+        <v>268.50000000000136</v>
       </c>
       <c r="E240" s="2">
-        <v>0.98997326203208613</v>
+        <v>0.97754854368931798</v>
       </c>
       <c r="F240" t="s">
-        <v>187</v>
+        <v>79</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="3" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="B241">
         <v>1</v>
@@ -6063,18 +6129,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D241" s="1">
-        <v>246.99999999999903</v>
+        <v>268.66666666666805</v>
       </c>
       <c r="E241" s="2">
-        <v>0.99064171122994704</v>
+        <v>0.97815533980582292</v>
       </c>
       <c r="F241" t="s">
-        <v>233</v>
+        <v>79</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
-        <v>249</v>
+        <v>143</v>
       </c>
       <c r="B242">
         <v>1</v>
@@ -6083,18 +6149,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D242" s="1">
-        <v>247.16666666666569</v>
+        <v>268.83333333333474</v>
       </c>
       <c r="E242" s="2">
-        <v>0.99131016042780795</v>
+        <v>0.97876213592232786</v>
       </c>
       <c r="F242" t="s">
-        <v>233</v>
+        <v>79</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
-        <v>250</v>
+        <v>176</v>
       </c>
       <c r="B243">
         <v>1</v>
@@ -6103,18 +6169,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D243" s="1">
-        <v>247.33333333333235</v>
+        <v>269.00000000000142</v>
       </c>
       <c r="E243" s="2">
-        <v>0.99197860962566886</v>
+        <v>0.9793689320388328</v>
       </c>
       <c r="F243" t="s">
-        <v>233</v>
+        <v>79</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="B244">
         <v>1</v>
@@ -6123,18 +6189,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D244" s="1">
-        <v>247.49999999999901</v>
+        <v>269.16666666666811</v>
       </c>
       <c r="E244" s="2">
-        <v>0.99264705882352977</v>
+        <v>0.97997572815533773</v>
       </c>
       <c r="F244" t="s">
-        <v>233</v>
+        <v>79</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
-        <v>252</v>
+        <v>146</v>
       </c>
       <c r="B245">
         <v>1</v>
@@ -6143,18 +6209,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D245" s="1">
-        <v>247.66666666666566</v>
+        <v>269.33333333333479</v>
       </c>
       <c r="E245" s="2">
-        <v>0.99331550802139068</v>
+        <v>0.98058252427184256</v>
       </c>
       <c r="F245" t="s">
-        <v>233</v>
+        <v>181</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
-        <v>253</v>
+        <v>145</v>
       </c>
       <c r="B246">
         <v>1</v>
@@ -6163,18 +6229,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D246" s="1">
-        <v>247.83333333333232</v>
+        <v>269.50000000000148</v>
       </c>
       <c r="E246" s="2">
-        <v>0.9939839572192517</v>
+        <v>0.9811893203883475</v>
       </c>
       <c r="F246" t="s">
-        <v>233</v>
+        <v>181</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="3" t="s">
-        <v>254</v>
+        <v>178</v>
       </c>
       <c r="B247">
         <v>1</v>
@@ -6183,18 +6249,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D247" s="1">
-        <v>247.99999999999898</v>
+        <v>269.66666666666816</v>
       </c>
       <c r="E247" s="2">
-        <v>0.99465240641711261</v>
+        <v>0.98179611650485243</v>
       </c>
       <c r="F247" t="s">
-        <v>233</v>
+        <v>181</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
-        <v>255</v>
+        <v>142</v>
       </c>
       <c r="B248">
         <v>1</v>
@@ -6203,18 +6269,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D248" s="1">
-        <v>248.16666666666563</v>
+        <v>269.83333333333485</v>
       </c>
       <c r="E248" s="2">
-        <v>0.99532085561497352</v>
+        <v>0.98240291262135737</v>
       </c>
       <c r="F248" t="s">
-        <v>233</v>
+        <v>181</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="B249">
         <v>1</v>
@@ -6223,18 +6289,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D249" s="1">
-        <v>248.33333333333229</v>
+        <v>270.00000000000153</v>
       </c>
       <c r="E249" s="2">
-        <v>0.99598930481283443</v>
+        <v>0.98300970873786231</v>
       </c>
       <c r="F249" t="s">
-        <v>233</v>
+        <v>181</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
-        <v>257</v>
+        <v>130</v>
       </c>
       <c r="B250">
         <v>1</v>
@@ -6243,18 +6309,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D250" s="1">
-        <v>248.49999999999895</v>
+        <v>270.16666666666822</v>
       </c>
       <c r="E250" s="2">
-        <v>0.99665775401069534</v>
+        <v>0.98361650485436725</v>
       </c>
       <c r="F250" t="s">
-        <v>233</v>
+        <v>181</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B251">
         <v>1</v>
@@ -6263,18 +6329,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D251" s="1">
-        <v>248.66666666666561</v>
+        <v>270.33333333333491</v>
       </c>
       <c r="E251" s="2">
-        <v>0.99732620320855625</v>
+        <v>0.98422330097087207</v>
       </c>
       <c r="F251" t="s">
-        <v>233</v>
+        <v>181</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
-        <v>259</v>
+        <v>144</v>
       </c>
       <c r="B252">
         <v>1</v>
@@ -6283,18 +6349,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D252" s="1">
-        <v>248.83333333333226</v>
+        <v>270.50000000000159</v>
       </c>
       <c r="E252" s="2">
-        <v>0.99799465240641727</v>
+        <v>0.98483009708737701</v>
       </c>
       <c r="F252" t="s">
-        <v>233</v>
+        <v>181</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
-        <v>260</v>
+        <v>180</v>
       </c>
       <c r="B253">
         <v>1</v>
@@ -6303,18 +6369,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D253" s="1">
-        <v>248.99999999999892</v>
+        <v>270.66666666666828</v>
       </c>
       <c r="E253" s="2">
-        <v>0.99866310160427818</v>
+        <v>0.98543689320388195</v>
       </c>
       <c r="F253" t="s">
-        <v>233</v>
+        <v>181</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="B254">
         <v>1</v>
@@ -6323,18 +6389,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D254" s="1">
-        <v>249.16666666666558</v>
+        <v>270.83333333333496</v>
       </c>
       <c r="E254" s="2">
-        <v>0.99933155080213909</v>
+        <v>0.98604368932038688</v>
       </c>
       <c r="F254" t="s">
-        <v>233</v>
+        <v>181</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
-        <v>262</v>
+        <v>148</v>
       </c>
       <c r="B255">
         <v>1</v>
@@ -6343,13 +6409,453 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D255" s="1">
-        <v>249.33333333333223</v>
+        <v>271.00000000000165</v>
       </c>
       <c r="E255" s="2">
-        <v>1</v>
+        <v>0.98665048543689182</v>
       </c>
       <c r="F255" t="s">
-        <v>233</v>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A256" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B256">
+        <v>1</v>
+      </c>
+      <c r="C256" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D256" s="1">
+        <v>271.16666666666833</v>
+      </c>
+      <c r="E256" s="2">
+        <v>0.98725728155339676</v>
+      </c>
+      <c r="F256" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A257" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B257">
+        <v>1</v>
+      </c>
+      <c r="C257" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D257" s="1">
+        <v>271.33333333333502</v>
+      </c>
+      <c r="E257" s="2">
+        <v>0.98786407766990159</v>
+      </c>
+      <c r="F257" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A258" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B258">
+        <v>1</v>
+      </c>
+      <c r="C258" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D258" s="1">
+        <v>271.50000000000171</v>
+      </c>
+      <c r="E258" s="2">
+        <v>0.98847087378640652</v>
+      </c>
+      <c r="F258" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A259" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B259">
+        <v>1</v>
+      </c>
+      <c r="C259" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D259" s="1">
+        <v>271.66666666666839</v>
+      </c>
+      <c r="E259" s="2">
+        <v>0.98907766990291146</v>
+      </c>
+      <c r="F259" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A260" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B260">
+        <v>1</v>
+      </c>
+      <c r="C260" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D260" s="1">
+        <v>271.83333333333508</v>
+      </c>
+      <c r="E260" s="2">
+        <v>0.9896844660194164</v>
+      </c>
+      <c r="F260" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A261" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B261">
+        <v>1</v>
+      </c>
+      <c r="C261" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D261" s="1">
+        <v>272.00000000000176</v>
+      </c>
+      <c r="E261" s="2">
+        <v>0.99029126213592134</v>
+      </c>
+      <c r="F261" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A262" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B262">
+        <v>1</v>
+      </c>
+      <c r="C262" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D262" s="1">
+        <v>272.16666666666845</v>
+      </c>
+      <c r="E262" s="2">
+        <v>0.99089805825242627</v>
+      </c>
+      <c r="F262" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A263" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B263">
+        <v>1</v>
+      </c>
+      <c r="C263" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D263" s="1">
+        <v>272.33333333333513</v>
+      </c>
+      <c r="E263" s="2">
+        <v>0.9915048543689311</v>
+      </c>
+      <c r="F263" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A264" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B264">
+        <v>1</v>
+      </c>
+      <c r="C264" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D264" s="1">
+        <v>272.50000000000182</v>
+      </c>
+      <c r="E264" s="2">
+        <v>0.99211165048543604</v>
+      </c>
+      <c r="F264" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A265" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B265">
+        <v>1</v>
+      </c>
+      <c r="C265" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D265" s="1">
+        <v>272.6666666666685</v>
+      </c>
+      <c r="E265" s="2">
+        <v>0.99271844660194097</v>
+      </c>
+      <c r="F265" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A266" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B266">
+        <v>1</v>
+      </c>
+      <c r="C266" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D266" s="1">
+        <v>272.83333333333519</v>
+      </c>
+      <c r="E266" s="2">
+        <v>0.99332524271844591</v>
+      </c>
+      <c r="F266" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A267" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B267">
+        <v>1</v>
+      </c>
+      <c r="C267" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D267" s="1">
+        <v>273.00000000000188</v>
+      </c>
+      <c r="E267" s="2">
+        <v>0.99393203883495085</v>
+      </c>
+      <c r="F267" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A268" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B268">
+        <v>1</v>
+      </c>
+      <c r="C268" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D268" s="1">
+        <v>273.16666666666856</v>
+      </c>
+      <c r="E268" s="2">
+        <v>0.99453883495145579</v>
+      </c>
+      <c r="F268" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A269" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B269">
+        <v>1</v>
+      </c>
+      <c r="C269" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D269" s="1">
+        <v>273.33333333333525</v>
+      </c>
+      <c r="E269" s="2">
+        <v>0.99514563106796061</v>
+      </c>
+      <c r="F269" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A270" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B270">
+        <v>1</v>
+      </c>
+      <c r="C270" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D270" s="1">
+        <v>273.50000000000193</v>
+      </c>
+      <c r="E270" s="2">
+        <v>0.99575242718446555</v>
+      </c>
+      <c r="F270" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A271" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B271">
+        <v>1</v>
+      </c>
+      <c r="C271" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D271" s="1">
+        <v>273.66666666666862</v>
+      </c>
+      <c r="E271" s="2">
+        <v>0.99635922330097049</v>
+      </c>
+      <c r="F271" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A272" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B272">
+        <v>1</v>
+      </c>
+      <c r="C272" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D272" s="1">
+        <v>273.8333333333353</v>
+      </c>
+      <c r="E272" s="2">
+        <v>0.99696601941747542</v>
+      </c>
+      <c r="F272" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A273" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B273">
+        <v>1</v>
+      </c>
+      <c r="C273" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D273" s="1">
+        <v>274.00000000000199</v>
+      </c>
+      <c r="E273" s="2">
+        <v>0.99757281553398036</v>
+      </c>
+      <c r="F273" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A274" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B274">
+        <v>1</v>
+      </c>
+      <c r="C274" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D274" s="1">
+        <v>274.16666666666868</v>
+      </c>
+      <c r="E274" s="2">
+        <v>0.9981796116504853</v>
+      </c>
+      <c r="F274" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A275" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B275">
+        <v>1</v>
+      </c>
+      <c r="C275" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D275" s="1">
+        <v>274.33333333333536</v>
+      </c>
+      <c r="E275" s="2">
+        <v>0.99878640776699013</v>
+      </c>
+      <c r="F275" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A276" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B276">
+        <v>1</v>
+      </c>
+      <c r="C276" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D276" s="1">
+        <v>274.50000000000205</v>
+      </c>
+      <c r="E276" s="2">
+        <v>0.99939320388349506</v>
+      </c>
+      <c r="F276" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A277" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B277">
+        <v>1</v>
+      </c>
+      <c r="C277" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D277" s="1">
+        <v>274.66666666666873</v>
+      </c>
+      <c r="E277" s="2">
+        <v>1</v>
+      </c>
+      <c r="F277" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/STOK RANK/Rank Dealer/RANK BHG.xlsx
+++ b/STOK RANK/Rank Dealer/RANK BHG.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\DASHBOARD RANK STOK\data\Rank Dealer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C59A240-377A-4226-A5D1-13C971DAA4BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3AA056E-A710-4FE9-947F-08127240F148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B751393D-4C32-4D4C-AA97-AA7CC129AC75}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B751393D-4C32-4D4C-AA97-AA7CC129AC75}"/>
   </bookViews>
   <sheets>
     <sheet name="rankparts" sheetId="1" r:id="rId1"/>
+    <sheet name="avg6bulan" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="355">
   <si>
     <t>Sum of Qty</t>
   </si>
@@ -894,6 +895,213 @@
   </si>
   <si>
     <t>06455KREK01</t>
+  </si>
+  <si>
+    <t>AVG 6 Bulan</t>
+  </si>
+  <si>
+    <t>082342MBK0LZ9</t>
+  </si>
+  <si>
+    <t>08294M99K8LN9</t>
+  </si>
+  <si>
+    <t>082322MBK6LN9</t>
+  </si>
+  <si>
+    <t>81110H02BLA</t>
+  </si>
+  <si>
+    <t>082322MAK0LN9</t>
+  </si>
+  <si>
+    <t>64300K1AL00</t>
+  </si>
+  <si>
+    <t>082322MBK5LN9</t>
+  </si>
+  <si>
+    <t>082342MBK0LZ0</t>
+  </si>
+  <si>
+    <t>HBF50ML</t>
+  </si>
+  <si>
+    <t>64300K2FP00</t>
+  </si>
+  <si>
+    <t>082322MAK1LN9</t>
+  </si>
+  <si>
+    <t>082322MAK8LN9</t>
+  </si>
+  <si>
+    <t>08F88K1AL00</t>
+  </si>
+  <si>
+    <t>TBC500ML</t>
+  </si>
+  <si>
+    <t>64300K2SA00</t>
+  </si>
+  <si>
+    <t>ACG10GR</t>
+  </si>
+  <si>
+    <t>08234M99K8LN9</t>
+  </si>
+  <si>
+    <t>AHTS0201048</t>
+  </si>
+  <si>
+    <t>17200K1AL00</t>
+  </si>
+  <si>
+    <t>64300K3VA00</t>
+  </si>
+  <si>
+    <t>61304K2FP00ORG</t>
+  </si>
+  <si>
+    <t>64300K2FA00</t>
+  </si>
+  <si>
+    <t>08F44K1AA00</t>
+  </si>
+  <si>
+    <t>AHK00301014</t>
+  </si>
+  <si>
+    <t>17200K2FA00</t>
+  </si>
+  <si>
+    <t>64300K1ZV00</t>
+  </si>
+  <si>
+    <t>08F88K2FP00SLV</t>
+  </si>
+  <si>
+    <t>64300K2VG00</t>
+  </si>
+  <si>
+    <t>08F88K2FP00ORG</t>
+  </si>
+  <si>
+    <t>08F88K2FA00</t>
+  </si>
+  <si>
+    <t>08F22K3VA00</t>
+  </si>
+  <si>
+    <t>AHGL0201012</t>
+  </si>
+  <si>
+    <t>AHTS0201053</t>
+  </si>
+  <si>
+    <t>OSC70ML</t>
+  </si>
+  <si>
+    <t>03512SKRCRE</t>
+  </si>
+  <si>
+    <t>87100LXBLUL</t>
+  </si>
+  <si>
+    <t>8350AK3VA00</t>
+  </si>
+  <si>
+    <t>08F88K2SA00</t>
+  </si>
+  <si>
+    <t>08F44K2FP00SLV</t>
+  </si>
+  <si>
+    <t>87100FFBLRL</t>
+  </si>
+  <si>
+    <t>08F44K2FA00</t>
+  </si>
+  <si>
+    <t>08F88K1ZG00</t>
+  </si>
+  <si>
+    <t>07342KE2010N</t>
+  </si>
+  <si>
+    <t>87100FSSAGM</t>
+  </si>
+  <si>
+    <t>08F88K3VA00</t>
+  </si>
+  <si>
+    <t>87100PRLWHTXL</t>
+  </si>
+  <si>
+    <t>077240050002IN</t>
+  </si>
+  <si>
+    <t>08P71MCMRED</t>
+  </si>
+  <si>
+    <t>03512K1ZGBL</t>
+  </si>
+  <si>
+    <t>AHTS0301052</t>
+  </si>
+  <si>
+    <t>3311AK3VA00</t>
+  </si>
+  <si>
+    <t>08F88K2FP00LGR</t>
+  </si>
+  <si>
+    <t>07341001000N</t>
+  </si>
+  <si>
+    <t>61304K1ZV00</t>
+  </si>
+  <si>
+    <t>61304K2FP00LGR</t>
+  </si>
+  <si>
+    <t>87100FFXPTXL</t>
+  </si>
+  <si>
+    <t>87100HFCLS20L</t>
+  </si>
+  <si>
+    <t>87100LXREDXL</t>
+  </si>
+  <si>
+    <t>08R74K1ZV00</t>
+  </si>
+  <si>
+    <t>3310AK1ZV00</t>
+  </si>
+  <si>
+    <t>07GMBKT70101IN</t>
+  </si>
+  <si>
+    <t>AHK00101014</t>
+  </si>
+  <si>
+    <t>3310AK2SA00</t>
+  </si>
+  <si>
+    <t>AHTS0101048</t>
+  </si>
+  <si>
+    <t>19000K1ZG00</t>
+  </si>
+  <si>
+    <t>CC200ML</t>
+  </si>
+  <si>
+    <t>3310AK3VA00</t>
+  </si>
+  <si>
+    <t>Sum 6 Bulan</t>
   </si>
 </sst>
 </file>
@@ -986,6 +1194,18 @@
     <tableColumn id="4" xr3:uid="{A19099EB-09D4-453B-B335-8C8E31A09221}" name="Akumulasi AVG 12 Bulan" dataDxfId="0" dataCellStyle="Comma"/>
     <tableColumn id="5" xr3:uid="{47EFE725-CDB5-45AD-BDA0-B6DCB63EE85D}" name="Cont % Akumulasi" dataCellStyle="Percent"/>
     <tableColumn id="6" xr3:uid="{37C8619E-0B0F-4647-86AB-979865F93ADA}" name="Rank"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C03400FD-64EB-41AC-8C3F-E00487FB0DC0}" name="AVG6bulan" displayName="AVG6bulan" ref="A1:C344" totalsRowShown="0">
+  <autoFilter ref="A1:C344" xr:uid="{C03400FD-64EB-41AC-8C3F-E00487FB0DC0}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{EA290633-F868-4318-B60E-FE8A74ECF04D}" name="kode part"/>
+    <tableColumn id="2" xr3:uid="{53B0B34D-5627-4ECE-B3FA-95091F3CF241}" name="Sum 6 Bulan"/>
+    <tableColumn id="3" xr3:uid="{B22EC6D8-76B4-4AE7-BB5E-05B52E9A5D90}" name="AVG 6 Bulan"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6864,4 +7084,3806 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80827961-A801-4B86-A12E-303011668596}">
+  <dimension ref="A1:C344"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B2">
+        <v>2460</v>
+      </c>
+      <c r="C2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B3">
+        <v>800</v>
+      </c>
+      <c r="C3">
+        <v>133.33333333333334</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B4">
+        <v>712</v>
+      </c>
+      <c r="C4">
+        <v>118.66666666666667</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B5">
+        <v>608</v>
+      </c>
+      <c r="C5">
+        <v>101.33333333333333</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>196</v>
+      </c>
+      <c r="C6">
+        <v>32.666666666666664</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>291</v>
+      </c>
+      <c r="B7">
+        <v>134</v>
+      </c>
+      <c r="C7">
+        <v>22.333333333333332</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>292</v>
+      </c>
+      <c r="B8">
+        <v>95</v>
+      </c>
+      <c r="C8">
+        <v>15.833333333333334</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>94</v>
+      </c>
+      <c r="C9">
+        <v>15.666666666666666</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>293</v>
+      </c>
+      <c r="B10">
+        <v>85</v>
+      </c>
+      <c r="C10">
+        <v>14.166666666666666</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>294</v>
+      </c>
+      <c r="B11">
+        <v>83</v>
+      </c>
+      <c r="C11">
+        <v>13.833333333333334</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>295</v>
+      </c>
+      <c r="B12">
+        <v>79</v>
+      </c>
+      <c r="C12">
+        <v>13.166666666666666</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13">
+        <v>75</v>
+      </c>
+      <c r="C13">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14">
+        <v>75</v>
+      </c>
+      <c r="C14">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15">
+        <v>73</v>
+      </c>
+      <c r="C15">
+        <v>12.166666666666666</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16">
+        <v>68</v>
+      </c>
+      <c r="C16">
+        <v>11.333333333333334</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>61</v>
+      </c>
+      <c r="C17">
+        <v>10.166666666666666</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>296</v>
+      </c>
+      <c r="B18">
+        <v>55</v>
+      </c>
+      <c r="C18">
+        <v>9.1666666666666661</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>297</v>
+      </c>
+      <c r="B19">
+        <v>52</v>
+      </c>
+      <c r="C19">
+        <v>8.6666666666666661</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20">
+        <v>50</v>
+      </c>
+      <c r="C20">
+        <v>8.3333333333333339</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <v>49</v>
+      </c>
+      <c r="C21">
+        <v>8.1666666666666661</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22">
+        <v>44</v>
+      </c>
+      <c r="C22">
+        <v>7.333333333333333</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>298</v>
+      </c>
+      <c r="B23">
+        <v>39</v>
+      </c>
+      <c r="C23">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24">
+        <v>33</v>
+      </c>
+      <c r="C24">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>299</v>
+      </c>
+      <c r="B25">
+        <v>25</v>
+      </c>
+      <c r="C25">
+        <v>4.166666666666667</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26">
+        <v>25</v>
+      </c>
+      <c r="C26">
+        <v>4.166666666666667</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27">
+        <v>23</v>
+      </c>
+      <c r="C27">
+        <v>3.8333333333333335</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28">
+        <v>23</v>
+      </c>
+      <c r="C28">
+        <v>3.8333333333333335</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29">
+        <v>22</v>
+      </c>
+      <c r="C29">
+        <v>3.6666666666666665</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30">
+        <v>19</v>
+      </c>
+      <c r="C30">
+        <v>3.1666666666666665</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31">
+        <v>18</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32">
+        <v>18</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33">
+        <v>18</v>
+      </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34">
+        <v>18</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35">
+        <v>17</v>
+      </c>
+      <c r="C35">
+        <v>2.8333333333333335</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36">
+        <v>16</v>
+      </c>
+      <c r="C36">
+        <v>2.6666666666666665</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>16</v>
+      </c>
+      <c r="C37">
+        <v>2.6666666666666665</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>26</v>
+      </c>
+      <c r="B38">
+        <v>16</v>
+      </c>
+      <c r="C38">
+        <v>2.6666666666666665</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39">
+        <v>15</v>
+      </c>
+      <c r="C39">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>31</v>
+      </c>
+      <c r="B40">
+        <v>15</v>
+      </c>
+      <c r="C40">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41">
+        <v>14</v>
+      </c>
+      <c r="C41">
+        <v>2.3333333333333335</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42">
+        <v>14</v>
+      </c>
+      <c r="C42">
+        <v>2.3333333333333335</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>14</v>
+      </c>
+      <c r="C43">
+        <v>2.3333333333333335</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B44">
+        <v>14</v>
+      </c>
+      <c r="C44">
+        <v>2.3333333333333335</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45">
+        <v>13</v>
+      </c>
+      <c r="C45">
+        <v>2.1666666666666665</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>300</v>
+      </c>
+      <c r="B46">
+        <v>13</v>
+      </c>
+      <c r="C46">
+        <v>2.1666666666666665</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47">
+        <v>12</v>
+      </c>
+      <c r="C47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>23</v>
+      </c>
+      <c r="B48">
+        <v>12</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>32</v>
+      </c>
+      <c r="B49">
+        <v>12</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50">
+        <v>11</v>
+      </c>
+      <c r="C50">
+        <v>1.8333333333333333</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>301</v>
+      </c>
+      <c r="B51">
+        <v>10</v>
+      </c>
+      <c r="C51">
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52">
+        <v>10</v>
+      </c>
+      <c r="C52">
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>33</v>
+      </c>
+      <c r="B53">
+        <v>10</v>
+      </c>
+      <c r="C53">
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54">
+        <v>10</v>
+      </c>
+      <c r="C54">
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55">
+        <v>9</v>
+      </c>
+      <c r="C55">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>302</v>
+      </c>
+      <c r="B56">
+        <v>9</v>
+      </c>
+      <c r="C56">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>303</v>
+      </c>
+      <c r="B57">
+        <v>9</v>
+      </c>
+      <c r="C57">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>304</v>
+      </c>
+      <c r="B58">
+        <v>8</v>
+      </c>
+      <c r="C58">
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>50</v>
+      </c>
+      <c r="B59">
+        <v>8</v>
+      </c>
+      <c r="C59">
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>49</v>
+      </c>
+      <c r="B60">
+        <v>8</v>
+      </c>
+      <c r="C60">
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>48</v>
+      </c>
+      <c r="B61">
+        <v>8</v>
+      </c>
+      <c r="C61">
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>305</v>
+      </c>
+      <c r="B62">
+        <v>7</v>
+      </c>
+      <c r="C62">
+        <v>1.1666666666666667</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>47</v>
+      </c>
+      <c r="B63">
+        <v>6</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>306</v>
+      </c>
+      <c r="B64">
+        <v>6</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>58</v>
+      </c>
+      <c r="B65">
+        <v>6</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66">
+        <v>5</v>
+      </c>
+      <c r="C66">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>51</v>
+      </c>
+      <c r="B67">
+        <v>5</v>
+      </c>
+      <c r="C67">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>307</v>
+      </c>
+      <c r="B68">
+        <v>5</v>
+      </c>
+      <c r="C68">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>308</v>
+      </c>
+      <c r="B69">
+        <v>5</v>
+      </c>
+      <c r="C69">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>63</v>
+      </c>
+      <c r="B70">
+        <v>5</v>
+      </c>
+      <c r="C70">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>53</v>
+      </c>
+      <c r="B71">
+        <v>5</v>
+      </c>
+      <c r="C71">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>54</v>
+      </c>
+      <c r="B72">
+        <v>5</v>
+      </c>
+      <c r="C72">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>309</v>
+      </c>
+      <c r="B73">
+        <v>5</v>
+      </c>
+      <c r="C73">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>4</v>
+      </c>
+      <c r="C74">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>57</v>
+      </c>
+      <c r="B75">
+        <v>4</v>
+      </c>
+      <c r="C75">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>310</v>
+      </c>
+      <c r="B76">
+        <v>4</v>
+      </c>
+      <c r="C76">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>70</v>
+      </c>
+      <c r="B77">
+        <v>4</v>
+      </c>
+      <c r="C77">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B78">
+        <v>4</v>
+      </c>
+      <c r="C78">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>60</v>
+      </c>
+      <c r="B79">
+        <v>4</v>
+      </c>
+      <c r="C79">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>133</v>
+      </c>
+      <c r="B80">
+        <v>4</v>
+      </c>
+      <c r="C80">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>52</v>
+      </c>
+      <c r="B81">
+        <v>4</v>
+      </c>
+      <c r="C81">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>4</v>
+      </c>
+      <c r="C82">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>59</v>
+      </c>
+      <c r="B83">
+        <v>4</v>
+      </c>
+      <c r="C83">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>56</v>
+      </c>
+      <c r="B84">
+        <v>4</v>
+      </c>
+      <c r="C84">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>61</v>
+      </c>
+      <c r="B85">
+        <v>4</v>
+      </c>
+      <c r="C85">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>62</v>
+      </c>
+      <c r="B86">
+        <v>4</v>
+      </c>
+      <c r="C86">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>311</v>
+      </c>
+      <c r="B87">
+        <v>4</v>
+      </c>
+      <c r="C87">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88">
+        <v>3</v>
+      </c>
+      <c r="C88">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>76</v>
+      </c>
+      <c r="B89">
+        <v>3</v>
+      </c>
+      <c r="C89">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>115</v>
+      </c>
+      <c r="B90">
+        <v>3</v>
+      </c>
+      <c r="C90">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>77</v>
+      </c>
+      <c r="B91">
+        <v>3</v>
+      </c>
+      <c r="C91">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>312</v>
+      </c>
+      <c r="B92">
+        <v>3</v>
+      </c>
+      <c r="C92">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>313</v>
+      </c>
+      <c r="B93">
+        <v>3</v>
+      </c>
+      <c r="C93">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>69</v>
+      </c>
+      <c r="B94">
+        <v>3</v>
+      </c>
+      <c r="C94">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>85</v>
+      </c>
+      <c r="B95">
+        <v>3</v>
+      </c>
+      <c r="C95">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>74</v>
+      </c>
+      <c r="B96">
+        <v>3</v>
+      </c>
+      <c r="C96">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>221</v>
+      </c>
+      <c r="B97">
+        <v>3</v>
+      </c>
+      <c r="C97">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98">
+        <v>3</v>
+      </c>
+      <c r="C98">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>68</v>
+      </c>
+      <c r="B99">
+        <v>3</v>
+      </c>
+      <c r="C99">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>314</v>
+      </c>
+      <c r="B100">
+        <v>3</v>
+      </c>
+      <c r="C100">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>96</v>
+      </c>
+      <c r="B101">
+        <v>3</v>
+      </c>
+      <c r="C101">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>75</v>
+      </c>
+      <c r="B102">
+        <v>3</v>
+      </c>
+      <c r="C102">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>72</v>
+      </c>
+      <c r="B103">
+        <v>3</v>
+      </c>
+      <c r="C103">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>86</v>
+      </c>
+      <c r="B104">
+        <v>2</v>
+      </c>
+      <c r="C104">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>97</v>
+      </c>
+      <c r="B105">
+        <v>2</v>
+      </c>
+      <c r="C105">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>256</v>
+      </c>
+      <c r="B106">
+        <v>2</v>
+      </c>
+      <c r="C106">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>199</v>
+      </c>
+      <c r="B107">
+        <v>2</v>
+      </c>
+      <c r="C107">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>106</v>
+      </c>
+      <c r="B108">
+        <v>2</v>
+      </c>
+      <c r="C108">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>101</v>
+      </c>
+      <c r="B109">
+        <v>2</v>
+      </c>
+      <c r="C109">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>215</v>
+      </c>
+      <c r="B110">
+        <v>2</v>
+      </c>
+      <c r="C110">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>315</v>
+      </c>
+      <c r="B111">
+        <v>2</v>
+      </c>
+      <c r="C111">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>84</v>
+      </c>
+      <c r="B112">
+        <v>2</v>
+      </c>
+      <c r="C112">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>2</v>
+      </c>
+      <c r="C113">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>316</v>
+      </c>
+      <c r="B114">
+        <v>2</v>
+      </c>
+      <c r="C114">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>89</v>
+      </c>
+      <c r="B115">
+        <v>2</v>
+      </c>
+      <c r="C115">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>78</v>
+      </c>
+      <c r="B116">
+        <v>2</v>
+      </c>
+      <c r="C116">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>88</v>
+      </c>
+      <c r="B117">
+        <v>2</v>
+      </c>
+      <c r="C117">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>242</v>
+      </c>
+      <c r="B118">
+        <v>2</v>
+      </c>
+      <c r="C118">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>210</v>
+      </c>
+      <c r="B119">
+        <v>2</v>
+      </c>
+      <c r="C119">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>83</v>
+      </c>
+      <c r="B120">
+        <v>2</v>
+      </c>
+      <c r="C120">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>66</v>
+      </c>
+      <c r="B121">
+        <v>2</v>
+      </c>
+      <c r="C121">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>102</v>
+      </c>
+      <c r="B122">
+        <v>2</v>
+      </c>
+      <c r="C122">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>189</v>
+      </c>
+      <c r="B123">
+        <v>2</v>
+      </c>
+      <c r="C123">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>87</v>
+      </c>
+      <c r="B124">
+        <v>2</v>
+      </c>
+      <c r="C124">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>214</v>
+      </c>
+      <c r="B125">
+        <v>2</v>
+      </c>
+      <c r="C125">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>174</v>
+      </c>
+      <c r="B126">
+        <v>2</v>
+      </c>
+      <c r="C126">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>90</v>
+      </c>
+      <c r="B127">
+        <v>2</v>
+      </c>
+      <c r="C127">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>92</v>
+      </c>
+      <c r="B128">
+        <v>2</v>
+      </c>
+      <c r="C128">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>55</v>
+      </c>
+      <c r="B129">
+        <v>2</v>
+      </c>
+      <c r="C129">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>193</v>
+      </c>
+      <c r="B130">
+        <v>2</v>
+      </c>
+      <c r="C130">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>194</v>
+      </c>
+      <c r="B131">
+        <v>2</v>
+      </c>
+      <c r="C131">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>195</v>
+      </c>
+      <c r="B132">
+        <v>2</v>
+      </c>
+      <c r="C132">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>116</v>
+      </c>
+      <c r="B133">
+        <v>2</v>
+      </c>
+      <c r="C133">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>82</v>
+      </c>
+      <c r="B134">
+        <v>2</v>
+      </c>
+      <c r="C134">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>98</v>
+      </c>
+      <c r="B135">
+        <v>2</v>
+      </c>
+      <c r="C135">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>99</v>
+      </c>
+      <c r="B136">
+        <v>2</v>
+      </c>
+      <c r="C136">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>109</v>
+      </c>
+      <c r="B137">
+        <v>2</v>
+      </c>
+      <c r="C137">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>110</v>
+      </c>
+      <c r="B138">
+        <v>2</v>
+      </c>
+      <c r="C138">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>117</v>
+      </c>
+      <c r="B139">
+        <v>2</v>
+      </c>
+      <c r="C139">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>254</v>
+      </c>
+      <c r="B140">
+        <v>2</v>
+      </c>
+      <c r="C140">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>80</v>
+      </c>
+      <c r="B141">
+        <v>2</v>
+      </c>
+      <c r="C141">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>139</v>
+      </c>
+      <c r="B142">
+        <v>2</v>
+      </c>
+      <c r="C142">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>317</v>
+      </c>
+      <c r="B143">
+        <v>2</v>
+      </c>
+      <c r="C143">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>114</v>
+      </c>
+      <c r="B144">
+        <v>2</v>
+      </c>
+      <c r="C144">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>105</v>
+      </c>
+      <c r="B145">
+        <v>2</v>
+      </c>
+      <c r="C145">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>93</v>
+      </c>
+      <c r="B146">
+        <v>2</v>
+      </c>
+      <c r="C146">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>107</v>
+      </c>
+      <c r="B147">
+        <v>2</v>
+      </c>
+      <c r="C147">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>71</v>
+      </c>
+      <c r="B148">
+        <v>2</v>
+      </c>
+      <c r="C148">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>67</v>
+      </c>
+      <c r="B149">
+        <v>2</v>
+      </c>
+      <c r="C149">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>318</v>
+      </c>
+      <c r="B150">
+        <v>2</v>
+      </c>
+      <c r="C150">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>255</v>
+      </c>
+      <c r="B151">
+        <v>2</v>
+      </c>
+      <c r="C151">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>319</v>
+      </c>
+      <c r="B152">
+        <v>2</v>
+      </c>
+      <c r="C152">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>184</v>
+      </c>
+      <c r="B153">
+        <v>2</v>
+      </c>
+      <c r="C153">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>113</v>
+      </c>
+      <c r="B154">
+        <v>2</v>
+      </c>
+      <c r="C154">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>320</v>
+      </c>
+      <c r="B155">
+        <v>2</v>
+      </c>
+      <c r="C155">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>141</v>
+      </c>
+      <c r="B156">
+        <v>1</v>
+      </c>
+      <c r="C156">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>166</v>
+      </c>
+      <c r="B157">
+        <v>1</v>
+      </c>
+      <c r="C157">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>240</v>
+      </c>
+      <c r="B158">
+        <v>1</v>
+      </c>
+      <c r="C158">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>131</v>
+      </c>
+      <c r="B159">
+        <v>1</v>
+      </c>
+      <c r="C159">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>119</v>
+      </c>
+      <c r="B160">
+        <v>1</v>
+      </c>
+      <c r="C160">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>321</v>
+      </c>
+      <c r="B161">
+        <v>1</v>
+      </c>
+      <c r="C161">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>322</v>
+      </c>
+      <c r="B162">
+        <v>1</v>
+      </c>
+      <c r="C162">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>159</v>
+      </c>
+      <c r="B163">
+        <v>1</v>
+      </c>
+      <c r="C163">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>127</v>
+      </c>
+      <c r="B164">
+        <v>1</v>
+      </c>
+      <c r="C164">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>137</v>
+      </c>
+      <c r="B165">
+        <v>1</v>
+      </c>
+      <c r="C165">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>108</v>
+      </c>
+      <c r="B166">
+        <v>1</v>
+      </c>
+      <c r="C166">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>172</v>
+      </c>
+      <c r="B167">
+        <v>1</v>
+      </c>
+      <c r="C167">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>163</v>
+      </c>
+      <c r="B168">
+        <v>1</v>
+      </c>
+      <c r="C168">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>157</v>
+      </c>
+      <c r="B169">
+        <v>1</v>
+      </c>
+      <c r="C169">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>323</v>
+      </c>
+      <c r="B170">
+        <v>1</v>
+      </c>
+      <c r="C170">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>103</v>
+      </c>
+      <c r="B171">
+        <v>1</v>
+      </c>
+      <c r="C171">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>324</v>
+      </c>
+      <c r="B172">
+        <v>1</v>
+      </c>
+      <c r="C172">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>264</v>
+      </c>
+      <c r="B173">
+        <v>1</v>
+      </c>
+      <c r="C173">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>121</v>
+      </c>
+      <c r="B174">
+        <v>1</v>
+      </c>
+      <c r="C174">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>325</v>
+      </c>
+      <c r="B175">
+        <v>1</v>
+      </c>
+      <c r="C175">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>152</v>
+      </c>
+      <c r="B176">
+        <v>1</v>
+      </c>
+      <c r="C176">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>147</v>
+      </c>
+      <c r="B177">
+        <v>1</v>
+      </c>
+      <c r="C177">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>192</v>
+      </c>
+      <c r="B178">
+        <v>1</v>
+      </c>
+      <c r="C178">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>206</v>
+      </c>
+      <c r="B179">
+        <v>1</v>
+      </c>
+      <c r="C179">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>124</v>
+      </c>
+      <c r="B180">
+        <v>1</v>
+      </c>
+      <c r="C180">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>151</v>
+      </c>
+      <c r="B181">
+        <v>1</v>
+      </c>
+      <c r="C181">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>209</v>
+      </c>
+      <c r="B182">
+        <v>1</v>
+      </c>
+      <c r="C182">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>153</v>
+      </c>
+      <c r="B183">
+        <v>1</v>
+      </c>
+      <c r="C183">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>201</v>
+      </c>
+      <c r="B184">
+        <v>1</v>
+      </c>
+      <c r="C184">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>238</v>
+      </c>
+      <c r="B185">
+        <v>1</v>
+      </c>
+      <c r="C185">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>122</v>
+      </c>
+      <c r="B186">
+        <v>1</v>
+      </c>
+      <c r="C186">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>138</v>
+      </c>
+      <c r="B187">
+        <v>1</v>
+      </c>
+      <c r="C187">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>326</v>
+      </c>
+      <c r="B188">
+        <v>1</v>
+      </c>
+      <c r="C188">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>285</v>
+      </c>
+      <c r="B189">
+        <v>1</v>
+      </c>
+      <c r="C189">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>327</v>
+      </c>
+      <c r="B190">
+        <v>1</v>
+      </c>
+      <c r="C190">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>77160020500</v>
+      </c>
+      <c r="B191">
+        <v>1</v>
+      </c>
+      <c r="C191">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>236</v>
+      </c>
+      <c r="B192">
+        <v>1</v>
+      </c>
+      <c r="C192">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>328</v>
+      </c>
+      <c r="B193">
+        <v>1</v>
+      </c>
+      <c r="C193">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>241</v>
+      </c>
+      <c r="B194">
+        <v>1</v>
+      </c>
+      <c r="C194">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>244</v>
+      </c>
+      <c r="B195">
+        <v>1</v>
+      </c>
+      <c r="C195">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>162</v>
+      </c>
+      <c r="B196">
+        <v>1</v>
+      </c>
+      <c r="C196">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>111</v>
+      </c>
+      <c r="B197">
+        <v>1</v>
+      </c>
+      <c r="C197">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>134</v>
+      </c>
+      <c r="B198">
+        <v>1</v>
+      </c>
+      <c r="C198">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>168</v>
+      </c>
+      <c r="B199">
+        <v>1</v>
+      </c>
+      <c r="C199">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>260</v>
+      </c>
+      <c r="B200">
+        <v>1</v>
+      </c>
+      <c r="C200">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>171</v>
+      </c>
+      <c r="B201">
+        <v>1</v>
+      </c>
+      <c r="C201">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>91</v>
+      </c>
+      <c r="B202">
+        <v>1</v>
+      </c>
+      <c r="C202">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>261</v>
+      </c>
+      <c r="B203">
+        <v>1</v>
+      </c>
+      <c r="C203">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>197</v>
+      </c>
+      <c r="B204">
+        <v>1</v>
+      </c>
+      <c r="C204">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>160</v>
+      </c>
+      <c r="B205">
+        <v>1</v>
+      </c>
+      <c r="C205">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>262</v>
+      </c>
+      <c r="B206">
+        <v>1</v>
+      </c>
+      <c r="C206">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>175</v>
+      </c>
+      <c r="B207">
+        <v>1</v>
+      </c>
+      <c r="C207">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>150</v>
+      </c>
+      <c r="B208">
+        <v>1</v>
+      </c>
+      <c r="C208">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>177</v>
+      </c>
+      <c r="B209">
+        <v>1</v>
+      </c>
+      <c r="C209">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>161</v>
+      </c>
+      <c r="B210">
+        <v>1</v>
+      </c>
+      <c r="C210">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>179</v>
+      </c>
+      <c r="B211">
+        <v>1</v>
+      </c>
+      <c r="C211">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>1</v>
+      </c>
+      <c r="C212">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>269</v>
+      </c>
+      <c r="B213">
+        <v>1</v>
+      </c>
+      <c r="C213">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>128</v>
+      </c>
+      <c r="B214">
+        <v>1</v>
+      </c>
+      <c r="C214">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>248</v>
+      </c>
+      <c r="B215">
+        <v>1</v>
+      </c>
+      <c r="C215">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>165</v>
+      </c>
+      <c r="B216">
+        <v>1</v>
+      </c>
+      <c r="C216">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>100</v>
+      </c>
+      <c r="B217">
+        <v>1</v>
+      </c>
+      <c r="C217">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>219</v>
+      </c>
+      <c r="B218">
+        <v>1</v>
+      </c>
+      <c r="C218">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>259</v>
+      </c>
+      <c r="B219">
+        <v>1</v>
+      </c>
+      <c r="C219">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>169</v>
+      </c>
+      <c r="B220">
+        <v>1</v>
+      </c>
+      <c r="C220">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>329</v>
+      </c>
+      <c r="B221">
+        <v>1</v>
+      </c>
+      <c r="C221">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>226</v>
+      </c>
+      <c r="B222">
+        <v>1</v>
+      </c>
+      <c r="C222">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>266</v>
+      </c>
+      <c r="B223">
+        <v>1</v>
+      </c>
+      <c r="C223">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>330</v>
+      </c>
+      <c r="B224">
+        <v>1</v>
+      </c>
+      <c r="C224">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>331</v>
+      </c>
+      <c r="B225">
+        <v>1</v>
+      </c>
+      <c r="C225">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>332</v>
+      </c>
+      <c r="B226">
+        <v>1</v>
+      </c>
+      <c r="C226">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>191</v>
+      </c>
+      <c r="B227">
+        <v>1</v>
+      </c>
+      <c r="C227">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>182</v>
+      </c>
+      <c r="B228">
+        <v>1</v>
+      </c>
+      <c r="C228">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>333</v>
+      </c>
+      <c r="B229">
+        <v>1</v>
+      </c>
+      <c r="C229">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>130</v>
+      </c>
+      <c r="B230">
+        <v>1</v>
+      </c>
+      <c r="C230">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>334</v>
+      </c>
+      <c r="B231">
+        <v>1</v>
+      </c>
+      <c r="C231">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>204</v>
+      </c>
+      <c r="B232">
+        <v>1</v>
+      </c>
+      <c r="C232">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>154</v>
+      </c>
+      <c r="B233">
+        <v>1</v>
+      </c>
+      <c r="C233">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>144</v>
+      </c>
+      <c r="B234">
+        <v>1</v>
+      </c>
+      <c r="C234">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>198</v>
+      </c>
+      <c r="B235">
+        <v>1</v>
+      </c>
+      <c r="C235">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>246</v>
+      </c>
+      <c r="B236">
+        <v>1</v>
+      </c>
+      <c r="C236">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>155</v>
+      </c>
+      <c r="B237">
+        <v>1</v>
+      </c>
+      <c r="C237">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>123</v>
+      </c>
+      <c r="B238">
+        <v>1</v>
+      </c>
+      <c r="C238">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>335</v>
+      </c>
+      <c r="B239">
+        <v>1</v>
+      </c>
+      <c r="C239">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>336</v>
+      </c>
+      <c r="B240">
+        <v>1</v>
+      </c>
+      <c r="C240">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>43</v>
+      </c>
+      <c r="B241">
+        <v>1</v>
+      </c>
+      <c r="C241">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>149</v>
+      </c>
+      <c r="B242">
+        <v>1</v>
+      </c>
+      <c r="C242">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>129</v>
+      </c>
+      <c r="B243">
+        <v>1</v>
+      </c>
+      <c r="C243">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>188</v>
+      </c>
+      <c r="B244">
+        <v>1</v>
+      </c>
+      <c r="C244">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>243</v>
+      </c>
+      <c r="B245">
+        <v>1</v>
+      </c>
+      <c r="C245">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>190</v>
+      </c>
+      <c r="B246">
+        <v>1</v>
+      </c>
+      <c r="C246">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>245</v>
+      </c>
+      <c r="B247">
+        <v>1</v>
+      </c>
+      <c r="C247">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>120</v>
+      </c>
+      <c r="B248">
+        <v>1</v>
+      </c>
+      <c r="C248">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>247</v>
+      </c>
+      <c r="B249">
+        <v>1</v>
+      </c>
+      <c r="C249">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>337</v>
+      </c>
+      <c r="B250">
+        <v>1</v>
+      </c>
+      <c r="C250">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>338</v>
+      </c>
+      <c r="B251">
+        <v>1</v>
+      </c>
+      <c r="C251">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>200</v>
+      </c>
+      <c r="B252">
+        <v>1</v>
+      </c>
+      <c r="C252">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>164</v>
+      </c>
+      <c r="B253">
+        <v>1</v>
+      </c>
+      <c r="C253">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>156</v>
+      </c>
+      <c r="B254">
+        <v>1</v>
+      </c>
+      <c r="C254">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>279</v>
+      </c>
+      <c r="B255">
+        <v>1</v>
+      </c>
+      <c r="C255">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>126</v>
+      </c>
+      <c r="B256">
+        <v>1</v>
+      </c>
+      <c r="C256">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>280</v>
+      </c>
+      <c r="B257">
+        <v>1</v>
+      </c>
+      <c r="C257">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>217</v>
+      </c>
+      <c r="B258">
+        <v>1</v>
+      </c>
+      <c r="C258">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>281</v>
+      </c>
+      <c r="B259">
+        <v>1</v>
+      </c>
+      <c r="C259">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>132</v>
+      </c>
+      <c r="B260">
+        <v>1</v>
+      </c>
+      <c r="C260">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>283</v>
+      </c>
+      <c r="B261">
+        <v>1</v>
+      </c>
+      <c r="C261">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>203</v>
+      </c>
+      <c r="B262">
+        <v>1</v>
+      </c>
+      <c r="C262">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>225</v>
+      </c>
+      <c r="B263">
+        <v>1</v>
+      </c>
+      <c r="C263">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>205</v>
+      </c>
+      <c r="B264">
+        <v>1</v>
+      </c>
+      <c r="C264">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>272</v>
+      </c>
+      <c r="B265">
+        <v>1</v>
+      </c>
+      <c r="C265">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>207</v>
+      </c>
+      <c r="B266">
+        <v>1</v>
+      </c>
+      <c r="C266">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>227</v>
+      </c>
+      <c r="B267">
+        <v>1</v>
+      </c>
+      <c r="C267">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>270</v>
+      </c>
+      <c r="B268">
+        <v>1</v>
+      </c>
+      <c r="C268">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>229</v>
+      </c>
+      <c r="B269">
+        <v>1</v>
+      </c>
+      <c r="C269">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>140</v>
+      </c>
+      <c r="B270">
+        <v>1</v>
+      </c>
+      <c r="C270">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>231</v>
+      </c>
+      <c r="B271">
+        <v>1</v>
+      </c>
+      <c r="C271">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>271</v>
+      </c>
+      <c r="B272">
+        <v>1</v>
+      </c>
+      <c r="C272">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>233</v>
+      </c>
+      <c r="B273">
+        <v>1</v>
+      </c>
+      <c r="C273">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>213</v>
+      </c>
+      <c r="B274">
+        <v>1</v>
+      </c>
+      <c r="C274">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>235</v>
+      </c>
+      <c r="B275">
+        <v>1</v>
+      </c>
+      <c r="C275">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>273</v>
+      </c>
+      <c r="B276">
+        <v>1</v>
+      </c>
+      <c r="C276">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>237</v>
+      </c>
+      <c r="B277">
+        <v>1</v>
+      </c>
+      <c r="C277">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>339</v>
+      </c>
+      <c r="B278">
+        <v>1</v>
+      </c>
+      <c r="C278">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>239</v>
+      </c>
+      <c r="B279">
+        <v>1</v>
+      </c>
+      <c r="C279">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>216</v>
+      </c>
+      <c r="B280">
+        <v>1</v>
+      </c>
+      <c r="C280">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>340</v>
+      </c>
+      <c r="B281">
+        <v>1</v>
+      </c>
+      <c r="C281">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>167</v>
+      </c>
+      <c r="B282">
+        <v>1</v>
+      </c>
+      <c r="C282">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>341</v>
+      </c>
+      <c r="B283">
+        <v>1</v>
+      </c>
+      <c r="C283">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>263</v>
+      </c>
+      <c r="B284">
+        <v>1</v>
+      </c>
+      <c r="C284">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>208</v>
+      </c>
+      <c r="B285">
+        <v>1</v>
+      </c>
+      <c r="C285">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>258</v>
+      </c>
+      <c r="B286">
+        <v>1</v>
+      </c>
+      <c r="C286">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>176</v>
+      </c>
+      <c r="B287">
+        <v>1</v>
+      </c>
+      <c r="C287">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>224</v>
+      </c>
+      <c r="B288">
+        <v>1</v>
+      </c>
+      <c r="C288">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>146</v>
+      </c>
+      <c r="B289">
+        <v>1</v>
+      </c>
+      <c r="C289">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>143</v>
+      </c>
+      <c r="B290">
+        <v>1</v>
+      </c>
+      <c r="C290">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>178</v>
+      </c>
+      <c r="B291">
+        <v>1</v>
+      </c>
+      <c r="C291">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>170</v>
+      </c>
+      <c r="B292">
+        <v>1</v>
+      </c>
+      <c r="C292">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>274</v>
+      </c>
+      <c r="B293">
+        <v>1</v>
+      </c>
+      <c r="C293">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>342</v>
+      </c>
+      <c r="B294">
+        <v>1</v>
+      </c>
+      <c r="C294">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>145</v>
+      </c>
+      <c r="B295">
+        <v>1</v>
+      </c>
+      <c r="C295">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>343</v>
+      </c>
+      <c r="B296">
+        <v>1</v>
+      </c>
+      <c r="C296">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>180</v>
+      </c>
+      <c r="B297">
+        <v>1</v>
+      </c>
+      <c r="C297">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>344</v>
+      </c>
+      <c r="B298">
+        <v>1</v>
+      </c>
+      <c r="C298">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>148</v>
+      </c>
+      <c r="B299">
+        <v>1</v>
+      </c>
+      <c r="C299">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>228</v>
+      </c>
+      <c r="B300">
+        <v>1</v>
+      </c>
+      <c r="C300">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>275</v>
+      </c>
+      <c r="B301">
+        <v>1</v>
+      </c>
+      <c r="C301">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>230</v>
+      </c>
+      <c r="B302">
+        <v>1</v>
+      </c>
+      <c r="C302">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>183</v>
+      </c>
+      <c r="B303">
+        <v>1</v>
+      </c>
+      <c r="C303">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>136</v>
+      </c>
+      <c r="B304">
+        <v>1</v>
+      </c>
+      <c r="C304">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>276</v>
+      </c>
+      <c r="B305">
+        <v>1</v>
+      </c>
+      <c r="C305">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>265</v>
+      </c>
+      <c r="B306">
+        <v>1</v>
+      </c>
+      <c r="C306">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>277</v>
+      </c>
+      <c r="B307">
+        <v>1</v>
+      </c>
+      <c r="C307">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>95</v>
+      </c>
+      <c r="B308">
+        <v>1</v>
+      </c>
+      <c r="C308">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>345</v>
+      </c>
+      <c r="B309">
+        <v>1</v>
+      </c>
+      <c r="C309">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>118</v>
+      </c>
+      <c r="B310">
+        <v>1</v>
+      </c>
+      <c r="C310">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>185</v>
+      </c>
+      <c r="B311">
+        <v>1</v>
+      </c>
+      <c r="C311">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>232</v>
+      </c>
+      <c r="B312">
+        <v>1</v>
+      </c>
+      <c r="C312">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>346</v>
+      </c>
+      <c r="B313">
+        <v>1</v>
+      </c>
+      <c r="C313">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>142</v>
+      </c>
+      <c r="B314">
+        <v>1</v>
+      </c>
+      <c r="C314">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>187</v>
+      </c>
+      <c r="B315">
+        <v>1</v>
+      </c>
+      <c r="C315">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>347</v>
+      </c>
+      <c r="B316">
+        <v>1</v>
+      </c>
+      <c r="C316">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>282</v>
+      </c>
+      <c r="B317">
+        <v>1</v>
+      </c>
+      <c r="C317">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>212</v>
+      </c>
+      <c r="B318">
+        <v>1</v>
+      </c>
+      <c r="C318">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>284</v>
+      </c>
+      <c r="B319">
+        <v>1</v>
+      </c>
+      <c r="C319">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>234</v>
+      </c>
+      <c r="B320">
+        <v>1</v>
+      </c>
+      <c r="C320">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>250</v>
+      </c>
+      <c r="B321">
+        <v>1</v>
+      </c>
+      <c r="C321">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>348</v>
+      </c>
+      <c r="B322">
+        <v>1</v>
+      </c>
+      <c r="C322">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>349</v>
+      </c>
+      <c r="B323">
+        <v>1</v>
+      </c>
+      <c r="C323">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>350</v>
+      </c>
+      <c r="B324">
+        <v>1</v>
+      </c>
+      <c r="C324">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>196</v>
+      </c>
+      <c r="B325">
+        <v>1</v>
+      </c>
+      <c r="C325">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>125</v>
+      </c>
+      <c r="B326">
+        <v>1</v>
+      </c>
+      <c r="C326">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>202</v>
+      </c>
+      <c r="B327">
+        <v>1</v>
+      </c>
+      <c r="C327">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>351</v>
+      </c>
+      <c r="B328">
+        <v>1</v>
+      </c>
+      <c r="C328">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>135</v>
+      </c>
+      <c r="B329">
+        <v>1</v>
+      </c>
+      <c r="C329">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>352</v>
+      </c>
+      <c r="B330">
+        <v>1</v>
+      </c>
+      <c r="C330">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>353</v>
+      </c>
+      <c r="B331">
+        <v>1</v>
+      </c>
+      <c r="C331">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>278</v>
+      </c>
+      <c r="B332">
+        <v>1</v>
+      </c>
+      <c r="C332">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>249</v>
+      </c>
+      <c r="B333">
+        <v>1</v>
+      </c>
+      <c r="C333">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>173</v>
+      </c>
+      <c r="B334">
+        <v>1</v>
+      </c>
+      <c r="C334">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>251</v>
+      </c>
+      <c r="B335">
+        <v>1</v>
+      </c>
+      <c r="C335">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>267</v>
+      </c>
+      <c r="B336">
+        <v>1</v>
+      </c>
+      <c r="C336">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>252</v>
+      </c>
+      <c r="B337">
+        <v>1</v>
+      </c>
+      <c r="C337">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>257</v>
+      </c>
+      <c r="B338">
+        <v>1</v>
+      </c>
+      <c r="C338">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>218</v>
+      </c>
+      <c r="B339">
+        <v>1</v>
+      </c>
+      <c r="C339">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>268</v>
+      </c>
+      <c r="B340">
+        <v>1</v>
+      </c>
+      <c r="C340">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>220</v>
+      </c>
+      <c r="B341">
+        <v>1</v>
+      </c>
+      <c r="C341">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>158</v>
+      </c>
+      <c r="B342">
+        <v>1</v>
+      </c>
+      <c r="C342">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>222</v>
+      </c>
+      <c r="B343">
+        <v>1</v>
+      </c>
+      <c r="C343">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>186</v>
+      </c>
+      <c r="B344">
+        <v>1</v>
+      </c>
+      <c r="C344">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/STOK RANK/Rank Dealer/RANK BHG.xlsx
+++ b/STOK RANK/Rank Dealer/RANK BHG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\DASHBOARD RANK STOK\data\Rank Dealer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADAE2C30-8FD4-4942-A136-A28BBBEB98B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D14AEE6-89FD-497C-A925-7BA1B15FDAF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B751393D-4C32-4D4C-AA97-AA7CC129AC75}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="357">
   <si>
     <t>Sum of Qty</t>
   </si>
@@ -1105,6 +1105,9 @@
   </si>
   <si>
     <t>AHGL0001015</t>
+  </si>
+  <si>
+    <t>77160020500</t>
   </si>
 </sst>
 </file>
@@ -1164,7 +1167,10 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
@@ -1191,10 +1197,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C03BE401-9C1F-4F8C-A0F0-B1258C79C616}" name="rankparts" displayName="rankparts" ref="A1:F271" totalsRowShown="0">
   <autoFilter ref="A1:F271" xr:uid="{C03BE401-9C1F-4F8C-A0F0-B1258C79C616}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{EC489C37-CEDC-4675-8D70-1D331AA94B51}" name="kode part" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{EC489C37-CEDC-4675-8D70-1D331AA94B51}" name="kode part" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{36D6B850-0C62-4808-8CA4-A3ADDE283157}" name="Sum of Qty"/>
-    <tableColumn id="3" xr3:uid="{6AF7942C-7A8B-42A4-8893-BB3A0B0BA8DB}" name="AVG 12 Bulan" dataDxfId="1" dataCellStyle="Comma"/>
-    <tableColumn id="4" xr3:uid="{A19099EB-09D4-453B-B335-8C8E31A09221}" name="Akumulasi AVG 12 Bulan" dataDxfId="0" dataCellStyle="Comma"/>
+    <tableColumn id="3" xr3:uid="{6AF7942C-7A8B-42A4-8893-BB3A0B0BA8DB}" name="AVG 12 Bulan" dataDxfId="2" dataCellStyle="Comma"/>
+    <tableColumn id="4" xr3:uid="{A19099EB-09D4-453B-B335-8C8E31A09221}" name="Akumulasi AVG 12 Bulan" dataDxfId="1" dataCellStyle="Comma"/>
     <tableColumn id="5" xr3:uid="{47EFE725-CDB5-45AD-BDA0-B6DCB63EE85D}" name="Cont % Akumulasi" dataCellStyle="Percent"/>
     <tableColumn id="6" xr3:uid="{37C8619E-0B0F-4647-86AB-979865F93ADA}" name="Rank"/>
   </tableColumns>
@@ -1206,7 +1212,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C03400FD-64EB-41AC-8C3F-E00487FB0DC0}" name="AVG6bulan" displayName="AVG6bulan" ref="A1:C345" totalsRowShown="0">
   <autoFilter ref="A1:C345" xr:uid="{C03400FD-64EB-41AC-8C3F-E00487FB0DC0}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{EA290633-F868-4318-B60E-FE8A74ECF04D}" name="kode part"/>
+    <tableColumn id="1" xr3:uid="{EA290633-F868-4318-B60E-FE8A74ECF04D}" name="kode part" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{53B0B34D-5627-4ECE-B3FA-95091F3CF241}" name="Sum 6 Bulan"/>
     <tableColumn id="3" xr3:uid="{B22EC6D8-76B4-4AE7-BB5E-05B52E9A5D90}" name="AVG 6 Bulan"/>
   </tableColumns>
@@ -6974,13 +6980,13 @@
   <dimension ref="A1:C345"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>228</v>
       </c>
       <c r="B1" t="s">
@@ -6991,7 +6997,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>262</v>
       </c>
       <c r="B2">
@@ -7002,7 +7008,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>263</v>
       </c>
       <c r="B3">
@@ -7013,7 +7019,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>265</v>
       </c>
       <c r="B4">
@@ -7024,7 +7030,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>264</v>
       </c>
       <c r="B5">
@@ -7035,7 +7041,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>268</v>
       </c>
       <c r="B6">
@@ -7046,7 +7052,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B7">
@@ -7057,7 +7063,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>267</v>
       </c>
       <c r="B8">
@@ -7068,7 +7074,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>266</v>
       </c>
       <c r="B9">
@@ -7079,7 +7085,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="3" t="s">
         <v>269</v>
       </c>
       <c r="B10">
@@ -7090,7 +7096,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B11">
@@ -7101,7 +7107,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B12">
@@ -7112,7 +7118,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B13">
@@ -7123,7 +7129,7 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="3" t="s">
         <v>271</v>
       </c>
       <c r="B14">
@@ -7134,7 +7140,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B15">
@@ -7145,7 +7151,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B16">
@@ -7156,7 +7162,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="3" t="s">
         <v>270</v>
       </c>
       <c r="B17">
@@ -7167,7 +7173,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B18">
@@ -7178,7 +7184,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B19">
@@ -7189,7 +7195,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B20">
@@ -7200,7 +7206,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="3" t="s">
         <v>272</v>
       </c>
       <c r="B21">
@@ -7211,7 +7217,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B22">
@@ -7222,7 +7228,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23" s="3" t="s">
         <v>273</v>
       </c>
       <c r="B23">
@@ -7233,7 +7239,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="3" t="s">
         <v>274</v>
       </c>
       <c r="B24">
@@ -7244,7 +7250,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B25">
@@ -7255,7 +7261,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B26">
@@ -7266,7 +7272,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B27">
@@ -7277,7 +7283,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="A28" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B28">
@@ -7288,7 +7294,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="A29" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B29">
@@ -7299,7 +7305,7 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="A30" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B30">
@@ -7310,7 +7316,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="A31" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B31">
@@ -7321,7 +7327,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B32">
@@ -7332,7 +7338,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B33">
@@ -7343,7 +7349,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="A34" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B34">
@@ -7354,7 +7360,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="A35" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B35">
@@ -7365,7 +7371,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B36">
@@ -7376,7 +7382,7 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="A37" s="3" t="s">
         <v>276</v>
       </c>
       <c r="B37">
@@ -7387,7 +7393,7 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="A38" s="3" t="s">
         <v>279</v>
       </c>
       <c r="B38">
@@ -7398,7 +7404,7 @@
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="A39" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B39">
@@ -7409,7 +7415,7 @@
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B40">
@@ -7420,7 +7426,7 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="A41" s="3" t="s">
         <v>45</v>
       </c>
       <c r="B41">
@@ -7431,7 +7437,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="A42" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B42">
@@ -7442,7 +7448,7 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="A43" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B43">
@@ -7453,7 +7459,7 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="A44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B44">
@@ -7464,7 +7470,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="A45" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B45">
@@ -7475,7 +7481,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="A46" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B46">
@@ -7486,7 +7492,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="A47" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B47">
@@ -7497,7 +7503,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="A48" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B48">
@@ -7508,7 +7514,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="A49" s="3" t="s">
         <v>275</v>
       </c>
       <c r="B49">
@@ -7519,7 +7525,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="A50" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B50">
@@ -7530,7 +7536,7 @@
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="A51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B51">
@@ -7541,7 +7547,7 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="A52" s="3" t="s">
         <v>280</v>
       </c>
       <c r="B52">
@@ -7552,7 +7558,7 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="A53" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B53">
@@ -7563,7 +7569,7 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="A54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B54">
@@ -7574,7 +7580,7 @@
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="A55" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B55">
@@ -7585,7 +7591,7 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="A56" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B56">
@@ -7596,7 +7602,7 @@
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="A57" s="3" t="s">
         <v>281</v>
       </c>
       <c r="B57">
@@ -7607,7 +7613,7 @@
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="A58" s="3" t="s">
         <v>277</v>
       </c>
       <c r="B58">
@@ -7618,7 +7624,7 @@
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="A59" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B59">
@@ -7629,7 +7635,7 @@
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="A60" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B60">
@@ -7640,7 +7646,7 @@
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="A61" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B61">
@@ -7651,7 +7657,7 @@
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="A62" s="3" t="s">
         <v>286</v>
       </c>
       <c r="B62">
@@ -7662,7 +7668,7 @@
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="A63" s="3" t="s">
         <v>278</v>
       </c>
       <c r="B63">
@@ -7673,7 +7679,7 @@
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="A64" s="3" t="s">
         <v>296</v>
       </c>
       <c r="B64">
@@ -7684,7 +7690,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="A65" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B65">
@@ -7695,7 +7701,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="A66" s="3" t="s">
         <v>75</v>
       </c>
       <c r="B66">
@@ -7706,7 +7712,7 @@
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="A67" s="3" t="s">
         <v>57</v>
       </c>
       <c r="B67">
@@ -7717,7 +7723,7 @@
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="A68" s="3" t="s">
         <v>47</v>
       </c>
       <c r="B68">
@@ -7728,7 +7734,7 @@
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="A69" s="3" t="s">
         <v>59</v>
       </c>
       <c r="B69">
@@ -7739,7 +7745,7 @@
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="A70" s="3" t="s">
         <v>62</v>
       </c>
       <c r="B70">
@@ -7750,7 +7756,7 @@
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="A71" s="3" t="s">
         <v>283</v>
       </c>
       <c r="B71">
@@ -7761,7 +7767,7 @@
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="A72" s="3" t="s">
         <v>61</v>
       </c>
       <c r="B72">
@@ -7772,7 +7778,7 @@
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="A73" s="3" t="s">
         <v>83</v>
       </c>
       <c r="B73">
@@ -7783,7 +7789,7 @@
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="A74" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B74">
@@ -7794,7 +7800,7 @@
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="A75" s="3" t="s">
         <v>291</v>
       </c>
       <c r="B75">
@@ -7805,7 +7811,7 @@
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="A76" s="3" t="s">
         <v>71</v>
       </c>
       <c r="B76">
@@ -7816,7 +7822,7 @@
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="A77" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B77">
@@ -7827,7 +7833,7 @@
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="A78" s="3" t="s">
         <v>79</v>
       </c>
       <c r="B78">
@@ -7838,7 +7844,7 @@
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="A79" s="3" t="s">
         <v>46</v>
       </c>
       <c r="B79">
@@ -7849,7 +7855,7 @@
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="A80" s="3" t="s">
         <v>301</v>
       </c>
       <c r="B80">
@@ -7860,7 +7866,7 @@
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="A81" s="3" t="s">
         <v>53</v>
       </c>
       <c r="B81">
@@ -7871,7 +7877,7 @@
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="A82" s="3" t="s">
         <v>284</v>
       </c>
       <c r="B82">
@@ -7882,7 +7888,7 @@
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="A83" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B83">
@@ -7893,7 +7899,7 @@
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="A84" s="3" t="s">
         <v>92</v>
       </c>
       <c r="B84">
@@ -7904,7 +7910,7 @@
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="A85" s="3" t="s">
         <v>72</v>
       </c>
       <c r="B85">
@@ -7915,7 +7921,7 @@
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="A86" s="3" t="s">
         <v>125</v>
       </c>
       <c r="B86">
@@ -7926,7 +7932,7 @@
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="A87" s="3" t="s">
         <v>200</v>
       </c>
       <c r="B87">
@@ -7937,7 +7943,7 @@
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="A88" s="3" t="s">
         <v>287</v>
       </c>
       <c r="B88">
@@ -7948,7 +7954,7 @@
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="A89" s="3" t="s">
         <v>285</v>
       </c>
       <c r="B89">
@@ -7959,7 +7965,7 @@
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="A90" s="3" t="s">
         <v>66</v>
       </c>
       <c r="B90">
@@ -7970,7 +7976,7 @@
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="A91" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B91">
@@ -7981,7 +7987,7 @@
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="A92" s="3" t="s">
         <v>295</v>
       </c>
       <c r="B92">
@@ -7992,7 +7998,7 @@
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+      <c r="A93" s="3" t="s">
         <v>320</v>
       </c>
       <c r="B93">
@@ -8003,7 +8009,7 @@
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+      <c r="A94" s="3" t="s">
         <v>339</v>
       </c>
       <c r="B94">
@@ -8014,7 +8020,7 @@
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+      <c r="A95" s="3" t="s">
         <v>58</v>
       </c>
       <c r="B95">
@@ -8025,7 +8031,7 @@
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+      <c r="A96" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B96">
@@ -8036,7 +8042,7 @@
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+      <c r="A97" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B97">
@@ -8047,7 +8053,7 @@
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+      <c r="A98" s="3" t="s">
         <v>110</v>
       </c>
       <c r="B98">
@@ -8058,7 +8064,7 @@
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+      <c r="A99" s="3" t="s">
         <v>91</v>
       </c>
       <c r="B99">
@@ -8069,7 +8075,7 @@
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+      <c r="A100" s="3" t="s">
         <v>112</v>
       </c>
       <c r="B100">
@@ -8080,7 +8086,7 @@
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="A101" s="3" t="s">
         <v>129</v>
       </c>
       <c r="B101">
@@ -8091,7 +8097,7 @@
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+      <c r="A102" s="3" t="s">
         <v>74</v>
       </c>
       <c r="B102">
@@ -8102,7 +8108,7 @@
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+      <c r="A103" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B103">
@@ -8113,7 +8119,7 @@
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+      <c r="A104" s="3" t="s">
         <v>100</v>
       </c>
       <c r="B104">
@@ -8124,7 +8130,7 @@
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+      <c r="A105" s="3" t="s">
         <v>73</v>
       </c>
       <c r="B105">
@@ -8135,7 +8141,7 @@
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+      <c r="A106" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B106">
@@ -8146,7 +8152,7 @@
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+      <c r="A107" s="3" t="s">
         <v>95</v>
       </c>
       <c r="B107">
@@ -8157,7 +8163,7 @@
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+      <c r="A108" s="3" t="s">
         <v>233</v>
       </c>
       <c r="B108">
@@ -8168,7 +8174,7 @@
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+      <c r="A109" s="3" t="s">
         <v>94</v>
       </c>
       <c r="B109">
@@ -8179,7 +8185,7 @@
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="A110" s="3" t="s">
         <v>231</v>
       </c>
       <c r="B110">
@@ -8190,7 +8196,7 @@
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+      <c r="A111" s="3" t="s">
         <v>88</v>
       </c>
       <c r="B111">
@@ -8201,7 +8207,7 @@
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+      <c r="A112" s="3" t="s">
         <v>288</v>
       </c>
       <c r="B112">
@@ -8212,7 +8218,7 @@
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+      <c r="A113" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B113">
@@ -8223,7 +8229,7 @@
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+      <c r="A114" s="3" t="s">
         <v>340</v>
       </c>
       <c r="B114">
@@ -8234,7 +8240,7 @@
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+      <c r="A115" s="3" t="s">
         <v>103</v>
       </c>
       <c r="B115">
@@ -8245,7 +8251,7 @@
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+      <c r="A116" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B116">
@@ -8256,7 +8262,7 @@
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+      <c r="A117" s="3" t="s">
         <v>341</v>
       </c>
       <c r="B117">
@@ -8267,7 +8273,7 @@
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+      <c r="A118" s="3" t="s">
         <v>87</v>
       </c>
       <c r="B118">
@@ -8278,7 +8284,7 @@
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
+      <c r="A119" s="3" t="s">
         <v>308</v>
       </c>
       <c r="B119">
@@ -8289,7 +8295,7 @@
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
+      <c r="A120" s="3" t="s">
         <v>217</v>
       </c>
       <c r="B120">
@@ -8300,7 +8306,7 @@
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+      <c r="A121" s="3" t="s">
         <v>282</v>
       </c>
       <c r="B121">
@@ -8311,7 +8317,7 @@
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
+      <c r="A122" s="3" t="s">
         <v>342</v>
       </c>
       <c r="B122">
@@ -8322,7 +8328,7 @@
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+      <c r="A123" s="3" t="s">
         <v>299</v>
       </c>
       <c r="B123">
@@ -8333,7 +8339,7 @@
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+      <c r="A124" s="3" t="s">
         <v>177</v>
       </c>
       <c r="B124">
@@ -8344,7 +8350,7 @@
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+      <c r="A125" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B125">
@@ -8355,7 +8361,7 @@
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
+      <c r="A126" s="3" t="s">
         <v>67</v>
       </c>
       <c r="B126">
@@ -8366,7 +8372,7 @@
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
+      <c r="A127" s="3" t="s">
         <v>85</v>
       </c>
       <c r="B127">
@@ -8377,7 +8383,7 @@
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
+      <c r="A128" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B128">
@@ -8388,7 +8394,7 @@
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+      <c r="A129" s="3" t="s">
         <v>69</v>
       </c>
       <c r="B129">
@@ -8399,7 +8405,7 @@
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+      <c r="A130" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B130">
@@ -8410,7 +8416,7 @@
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+      <c r="A131" s="3" t="s">
         <v>182</v>
       </c>
       <c r="B131">
@@ -8421,7 +8427,7 @@
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+      <c r="A132" s="3" t="s">
         <v>107</v>
       </c>
       <c r="B132">
@@ -8432,7 +8438,7 @@
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
+      <c r="A133" s="3" t="s">
         <v>84</v>
       </c>
       <c r="B133">
@@ -8443,7 +8449,7 @@
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
+      <c r="A134" s="3" t="s">
         <v>109</v>
       </c>
       <c r="B134">
@@ -8454,7 +8460,7 @@
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
+      <c r="A135" s="3" t="s">
         <v>184</v>
       </c>
       <c r="B135">
@@ -8465,7 +8471,7 @@
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
+      <c r="A136" s="3" t="s">
         <v>64</v>
       </c>
       <c r="B136">
@@ -8476,7 +8482,7 @@
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
+      <c r="A137" s="3" t="s">
         <v>343</v>
       </c>
       <c r="B137">
@@ -8487,7 +8493,7 @@
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
+      <c r="A138" s="3" t="s">
         <v>174</v>
       </c>
       <c r="B138">
@@ -8498,7 +8504,7 @@
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
+      <c r="A139" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B139">
@@ -8509,7 +8515,7 @@
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
+      <c r="A140" s="3" t="s">
         <v>191</v>
       </c>
       <c r="B140">
@@ -8520,7 +8526,7 @@
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
+      <c r="A141" s="3" t="s">
         <v>76</v>
       </c>
       <c r="B141">
@@ -8531,7 +8537,7 @@
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
+      <c r="A142" s="3" t="s">
         <v>222</v>
       </c>
       <c r="B142">
@@ -8542,7 +8548,7 @@
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
+      <c r="A143" s="3" t="s">
         <v>178</v>
       </c>
       <c r="B143">
@@ -8553,7 +8559,7 @@
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
+      <c r="A144" s="3" t="s">
         <v>290</v>
       </c>
       <c r="B144">
@@ -8564,7 +8570,7 @@
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
+      <c r="A145" s="3" t="s">
         <v>229</v>
       </c>
       <c r="B145">
@@ -8575,7 +8581,7 @@
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
+      <c r="A146" s="3" t="s">
         <v>93</v>
       </c>
       <c r="B146">
@@ -8586,7 +8592,7 @@
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
+      <c r="A147" s="3" t="s">
         <v>78</v>
       </c>
       <c r="B147">
@@ -8597,7 +8603,7 @@
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
+      <c r="A148" s="3" t="s">
         <v>159</v>
       </c>
       <c r="B148">
@@ -8608,7 +8614,7 @@
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
+      <c r="A149" s="3" t="s">
         <v>321</v>
       </c>
       <c r="B149">
@@ -8619,7 +8625,7 @@
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
+      <c r="A150" s="3" t="s">
         <v>322</v>
       </c>
       <c r="B150">
@@ -8630,7 +8636,7 @@
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
+      <c r="A151" s="3" t="s">
         <v>167</v>
       </c>
       <c r="B151">
@@ -8641,7 +8647,7 @@
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
+      <c r="A152" s="3" t="s">
         <v>289</v>
       </c>
       <c r="B152">
@@ -8652,7 +8658,7 @@
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
+      <c r="A153" s="3" t="s">
         <v>105</v>
       </c>
       <c r="B153">
@@ -8663,7 +8669,7 @@
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
+      <c r="A154" s="3" t="s">
         <v>196</v>
       </c>
       <c r="B154">
@@ -8674,7 +8680,7 @@
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
+      <c r="A155" s="3" t="s">
         <v>344</v>
       </c>
       <c r="B155">
@@ -8685,7 +8691,7 @@
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
+      <c r="A156" s="3" t="s">
         <v>89</v>
       </c>
       <c r="B156">
@@ -8696,7 +8702,7 @@
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
+      <c r="A157" s="3" t="s">
         <v>176</v>
       </c>
       <c r="B157">
@@ -8707,7 +8713,7 @@
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
+      <c r="A158" s="3" t="s">
         <v>230</v>
       </c>
       <c r="B158">
@@ -8718,7 +8724,7 @@
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
+      <c r="A159" s="3" t="s">
         <v>297</v>
       </c>
       <c r="B159">
@@ -8729,7 +8735,7 @@
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
+      <c r="A160" s="3" t="s">
         <v>186</v>
       </c>
       <c r="B160">
@@ -8740,7 +8746,7 @@
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
+      <c r="A161" s="3" t="s">
         <v>325</v>
       </c>
       <c r="B161">
@@ -8751,7 +8757,7 @@
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
+      <c r="A162" s="3" t="s">
         <v>141</v>
       </c>
       <c r="B162">
@@ -8762,7 +8768,7 @@
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
+      <c r="A163" s="3" t="s">
         <v>326</v>
       </c>
       <c r="B163">
@@ -8773,7 +8779,7 @@
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
+      <c r="A164" s="3" t="s">
         <v>185</v>
       </c>
       <c r="B164">
@@ -8784,7 +8790,7 @@
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
+      <c r="A165" s="3" t="s">
         <v>122</v>
       </c>
       <c r="B165">
@@ -8795,7 +8801,7 @@
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
+      <c r="A166" s="3" t="s">
         <v>293</v>
       </c>
       <c r="B166">
@@ -8806,7 +8812,7 @@
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
+      <c r="A167" s="3" t="s">
         <v>345</v>
       </c>
       <c r="B167">
@@ -8817,7 +8823,7 @@
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
+      <c r="A168" s="3" t="s">
         <v>244</v>
       </c>
       <c r="B168">
@@ -8828,7 +8834,7 @@
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
+      <c r="A169" s="3" t="s">
         <v>192</v>
       </c>
       <c r="B169">
@@ -8839,7 +8845,7 @@
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
+      <c r="A170" s="3" t="s">
         <v>190</v>
       </c>
       <c r="B170">
@@ -8850,7 +8856,7 @@
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
+      <c r="A171" s="3" t="s">
         <v>156</v>
       </c>
       <c r="B171">
@@ -8861,7 +8867,7 @@
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
+      <c r="A172" s="3" t="s">
         <v>172</v>
       </c>
       <c r="B172">
@@ -8872,7 +8878,7 @@
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
+      <c r="A173" s="3" t="s">
         <v>311</v>
       </c>
       <c r="B173">
@@ -8883,7 +8889,7 @@
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
+      <c r="A174" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B174">
@@ -8894,7 +8900,7 @@
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
+      <c r="A175" s="3" t="s">
         <v>331</v>
       </c>
       <c r="B175">
@@ -8905,7 +8911,7 @@
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
+      <c r="A176" s="3" t="s">
         <v>155</v>
       </c>
       <c r="B176">
@@ -8916,7 +8922,7 @@
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
+      <c r="A177" s="3" t="s">
         <v>242</v>
       </c>
       <c r="B177">
@@ -8927,7 +8933,7 @@
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
+      <c r="A178" s="3" t="s">
         <v>236</v>
       </c>
       <c r="B178">
@@ -8938,7 +8944,7 @@
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
+      <c r="A179" s="3" t="s">
         <v>346</v>
       </c>
       <c r="B179">
@@ -8949,7 +8955,7 @@
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
+      <c r="A180" s="3" t="s">
         <v>226</v>
       </c>
       <c r="B180">
@@ -8960,7 +8966,7 @@
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
+      <c r="A181" s="3" t="s">
         <v>189</v>
       </c>
       <c r="B181">
@@ -8971,7 +8977,7 @@
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
+      <c r="A182" s="3" t="s">
         <v>160</v>
       </c>
       <c r="B182">
@@ -8982,7 +8988,7 @@
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
+      <c r="A183" s="3" t="s">
         <v>121</v>
       </c>
       <c r="B183">
@@ -8993,7 +8999,7 @@
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
+      <c r="A184" s="3" t="s">
         <v>162</v>
       </c>
       <c r="B184">
@@ -9004,7 +9010,7 @@
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
+      <c r="A185" s="3" t="s">
         <v>199</v>
       </c>
       <c r="B185">
@@ -9015,7 +9021,7 @@
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
+      <c r="A186" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B186">
@@ -9026,7 +9032,7 @@
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
+      <c r="A187" s="3" t="s">
         <v>133</v>
       </c>
       <c r="B187">
@@ -9037,8 +9043,8 @@
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188">
-        <v>77160020500</v>
+      <c r="A188" s="3" t="s">
+        <v>356</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -9048,7 +9054,7 @@
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
+      <c r="A189" s="3" t="s">
         <v>302</v>
       </c>
       <c r="B189">
@@ -9059,7 +9065,7 @@
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
+      <c r="A190" s="3" t="s">
         <v>179</v>
       </c>
       <c r="B190">
@@ -9070,7 +9076,7 @@
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
+      <c r="A191" s="3" t="s">
         <v>148</v>
       </c>
       <c r="B191">
@@ -9081,7 +9087,7 @@
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
+      <c r="A192" s="3" t="s">
         <v>126</v>
       </c>
       <c r="B192">
@@ -9092,7 +9098,7 @@
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
+      <c r="A193" s="3" t="s">
         <v>215</v>
       </c>
       <c r="B193">
@@ -9103,7 +9109,7 @@
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
+      <c r="A194" s="3" t="s">
         <v>169</v>
       </c>
       <c r="B194">
@@ -9114,7 +9120,7 @@
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
+      <c r="A195" s="3" t="s">
         <v>313</v>
       </c>
       <c r="B195">
@@ -9125,7 +9131,7 @@
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
+      <c r="A196" s="3" t="s">
         <v>108</v>
       </c>
       <c r="B196">
@@ -9136,7 +9142,7 @@
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
+      <c r="A197" s="3" t="s">
         <v>292</v>
       </c>
       <c r="B197">
@@ -9147,7 +9153,7 @@
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
+      <c r="A198" s="3" t="s">
         <v>241</v>
       </c>
       <c r="B198">
@@ -9158,7 +9164,7 @@
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
+      <c r="A199" s="3" t="s">
         <v>243</v>
       </c>
       <c r="B199">
@@ -9169,7 +9175,7 @@
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
+      <c r="A200" s="3" t="s">
         <v>260</v>
       </c>
       <c r="B200">
@@ -9180,7 +9186,7 @@
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
+      <c r="A201" s="3" t="s">
         <v>137</v>
       </c>
       <c r="B201">
@@ -9191,7 +9197,7 @@
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
+      <c r="A202" s="3" t="s">
         <v>209</v>
       </c>
       <c r="B202">
@@ -9202,7 +9208,7 @@
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
+      <c r="A203" s="3" t="s">
         <v>135</v>
       </c>
       <c r="B203">
@@ -9213,7 +9219,7 @@
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
+      <c r="A204" s="3" t="s">
         <v>158</v>
       </c>
       <c r="B204">
@@ -9224,7 +9230,7 @@
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
+      <c r="A205" s="3" t="s">
         <v>188</v>
       </c>
       <c r="B205">
@@ -9235,7 +9241,7 @@
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
+      <c r="A206" s="3" t="s">
         <v>132</v>
       </c>
       <c r="B206">
@@ -9246,7 +9252,7 @@
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
+      <c r="A207" s="3" t="s">
         <v>245</v>
       </c>
       <c r="B207">
@@ -9257,7 +9263,7 @@
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
+      <c r="A208" s="3" t="s">
         <v>90</v>
       </c>
       <c r="B208">
@@ -9268,7 +9274,7 @@
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
+      <c r="A209" s="3" t="s">
         <v>151</v>
       </c>
       <c r="B209">
@@ -9279,7 +9285,7 @@
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
+      <c r="A210" s="3" t="s">
         <v>181</v>
       </c>
       <c r="B210">
@@ -9290,7 +9296,7 @@
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
+      <c r="A211" s="3" t="s">
         <v>198</v>
       </c>
       <c r="B211">
@@ -9301,7 +9307,7 @@
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
+      <c r="A212" s="3" t="s">
         <v>221</v>
       </c>
       <c r="B212">
@@ -9312,7 +9318,7 @@
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
+      <c r="A213" s="3" t="s">
         <v>197</v>
       </c>
       <c r="B213">
@@ -9323,7 +9329,7 @@
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
+      <c r="A214" s="3" t="s">
         <v>224</v>
       </c>
       <c r="B214">
@@ -9334,7 +9340,7 @@
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
+      <c r="A215" s="3" t="s">
         <v>116</v>
       </c>
       <c r="B215">
@@ -9345,7 +9351,7 @@
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
+      <c r="A216" s="3" t="s">
         <v>96</v>
       </c>
       <c r="B216">
@@ -9356,7 +9362,7 @@
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
+      <c r="A217" s="3" t="s">
         <v>328</v>
       </c>
       <c r="B217">
@@ -9367,7 +9373,7 @@
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
+      <c r="A218" s="3" t="s">
         <v>144</v>
       </c>
       <c r="B218">
@@ -9378,7 +9384,7 @@
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
+      <c r="A219" s="3" t="s">
         <v>329</v>
       </c>
       <c r="B219">
@@ -9389,7 +9395,7 @@
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
+      <c r="A220" s="3" t="s">
         <v>220</v>
       </c>
       <c r="B220">
@@ -9400,7 +9406,7 @@
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
+      <c r="A221" s="3" t="s">
         <v>294</v>
       </c>
       <c r="B221">
@@ -9411,7 +9417,7 @@
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
+      <c r="A222" s="3" t="s">
         <v>333</v>
       </c>
       <c r="B222">
@@ -9422,7 +9428,7 @@
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
+      <c r="A223" s="3" t="s">
         <v>140</v>
       </c>
       <c r="B223">
@@ -9433,7 +9439,7 @@
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
+      <c r="A224" s="3" t="s">
         <v>223</v>
       </c>
       <c r="B224">
@@ -9444,7 +9450,7 @@
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
+      <c r="A225" s="3" t="s">
         <v>303</v>
       </c>
       <c r="B225">
@@ -9455,7 +9461,7 @@
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
+      <c r="A226" s="3" t="s">
         <v>225</v>
       </c>
       <c r="B226">
@@ -9466,7 +9472,7 @@
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
+      <c r="A227" s="3" t="s">
         <v>187</v>
       </c>
       <c r="B227">
@@ -9477,7 +9483,7 @@
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
+      <c r="A228" s="3" t="s">
         <v>334</v>
       </c>
       <c r="B228">
@@ -9488,7 +9494,7 @@
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
+      <c r="A229" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B229">
@@ -9499,7 +9505,7 @@
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
+      <c r="A230" s="3" t="s">
         <v>227</v>
       </c>
       <c r="B230">
@@ -9510,7 +9516,7 @@
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
+      <c r="A231" s="3" t="s">
         <v>115</v>
       </c>
       <c r="B231">
@@ -9521,7 +9527,7 @@
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
+      <c r="A232" s="3" t="s">
         <v>201</v>
       </c>
       <c r="B232">
@@ -9532,7 +9538,7 @@
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
+      <c r="A233" s="3" t="s">
         <v>315</v>
       </c>
       <c r="B233">
@@ -9543,7 +9549,7 @@
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
+      <c r="A234" s="3" t="s">
         <v>204</v>
       </c>
       <c r="B234">
@@ -9554,7 +9560,7 @@
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
+      <c r="A235" s="3" t="s">
         <v>306</v>
       </c>
       <c r="B235">
@@ -9565,7 +9571,7 @@
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
+      <c r="A236" s="3" t="s">
         <v>335</v>
       </c>
       <c r="B236">
@@ -9576,7 +9582,7 @@
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
+      <c r="A237" s="3" t="s">
         <v>127</v>
       </c>
       <c r="B237">
@@ -9587,7 +9593,7 @@
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A238" t="s">
+      <c r="A238" s="3" t="s">
         <v>247</v>
       </c>
       <c r="B238">
@@ -9598,7 +9604,7 @@
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A239" t="s">
+      <c r="A239" s="3" t="s">
         <v>298</v>
       </c>
       <c r="B239">
@@ -9609,7 +9615,7 @@
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A240" t="s">
+      <c r="A240" s="3" t="s">
         <v>206</v>
       </c>
       <c r="B240">
@@ -9620,7 +9626,7 @@
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
+      <c r="A241" s="3" t="s">
         <v>232</v>
       </c>
       <c r="B241">
@@ -9631,7 +9637,7 @@
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
+      <c r="A242" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B242">
@@ -9642,7 +9648,7 @@
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
+      <c r="A243" s="3" t="s">
         <v>234</v>
       </c>
       <c r="B243">
@@ -9653,7 +9659,7 @@
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
+      <c r="A244" s="3" t="s">
         <v>208</v>
       </c>
       <c r="B244">
@@ -9664,7 +9670,7 @@
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A245" t="s">
+      <c r="A245" s="3" t="s">
         <v>347</v>
       </c>
       <c r="B245">
@@ -9675,7 +9681,7 @@
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
+      <c r="A246" s="3" t="s">
         <v>210</v>
       </c>
       <c r="B246">
@@ -9686,7 +9692,7 @@
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A247" t="s">
+      <c r="A247" s="3" t="s">
         <v>348</v>
       </c>
       <c r="B247">
@@ -9697,7 +9703,7 @@
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
+      <c r="A248" s="3" t="s">
         <v>212</v>
       </c>
       <c r="B248">
@@ -9708,7 +9714,7 @@
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A249" t="s">
+      <c r="A249" s="3" t="s">
         <v>349</v>
       </c>
       <c r="B249">
@@ -9719,7 +9725,7 @@
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A250" t="s">
+      <c r="A250" s="3" t="s">
         <v>214</v>
       </c>
       <c r="B250">
@@ -9730,7 +9736,7 @@
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
+      <c r="A251" s="3" t="s">
         <v>195</v>
       </c>
       <c r="B251">
@@ -9741,7 +9747,7 @@
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A252" t="s">
+      <c r="A252" s="3" t="s">
         <v>216</v>
       </c>
       <c r="B252">
@@ -9752,7 +9758,7 @@
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
+      <c r="A253" s="3" t="s">
         <v>324</v>
       </c>
       <c r="B253">
@@ -9763,7 +9769,7 @@
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
+      <c r="A254" s="3" t="s">
         <v>146</v>
       </c>
       <c r="B254">
@@ -9774,7 +9780,7 @@
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
+      <c r="A255" s="3" t="s">
         <v>113</v>
       </c>
       <c r="B255">
@@ -9785,7 +9791,7 @@
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
+      <c r="A256" s="3" t="s">
         <v>150</v>
       </c>
       <c r="B256">
@@ -9796,7 +9802,7 @@
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
+      <c r="A257" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B257">
@@ -9807,7 +9813,7 @@
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A258" t="s">
+      <c r="A258" s="3" t="s">
         <v>316</v>
       </c>
       <c r="B258">
@@ -9818,7 +9824,7 @@
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A259" t="s">
+      <c r="A259" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B259">
@@ -9829,7 +9835,7 @@
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A260" t="s">
+      <c r="A260" s="3" t="s">
         <v>161</v>
       </c>
       <c r="B260">
@@ -9840,7 +9846,7 @@
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
+      <c r="A261" s="3" t="s">
         <v>246</v>
       </c>
       <c r="B261">
@@ -9851,7 +9857,7 @@
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A262" t="s">
+      <c r="A262" s="3" t="s">
         <v>136</v>
       </c>
       <c r="B262">
@@ -9862,7 +9868,7 @@
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A263" t="s">
+      <c r="A263" s="3" t="s">
         <v>194</v>
       </c>
       <c r="B263">
@@ -9873,7 +9879,7 @@
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A264" t="s">
+      <c r="A264" s="3" t="s">
         <v>163</v>
       </c>
       <c r="B264">
@@ -9884,7 +9890,7 @@
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
+      <c r="A265" s="3" t="s">
         <v>248</v>
       </c>
       <c r="B265">
@@ -9895,7 +9901,7 @@
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
+      <c r="A266" s="3" t="s">
         <v>249</v>
       </c>
       <c r="B266">
@@ -9906,7 +9912,7 @@
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A267" t="s">
+      <c r="A267" s="3" t="s">
         <v>124</v>
       </c>
       <c r="B267">
@@ -9917,7 +9923,7 @@
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A268" t="s">
+      <c r="A268" s="3" t="s">
         <v>98</v>
       </c>
       <c r="B268">
@@ -9928,7 +9934,7 @@
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A269" t="s">
+      <c r="A269" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B269">
@@ -9939,7 +9945,7 @@
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A270" t="s">
+      <c r="A270" s="3" t="s">
         <v>164</v>
       </c>
       <c r="B270">
@@ -9950,7 +9956,7 @@
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A271" t="s">
+      <c r="A271" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B271">
@@ -9961,7 +9967,7 @@
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A272" t="s">
+      <c r="A272" s="3" t="s">
         <v>138</v>
       </c>
       <c r="B272">
@@ -9972,7 +9978,7 @@
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
+      <c r="A273" s="3" t="s">
         <v>238</v>
       </c>
       <c r="B273">
@@ -9983,7 +9989,7 @@
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A274" t="s">
+      <c r="A274" s="3" t="s">
         <v>250</v>
       </c>
       <c r="B274">
@@ -9994,7 +10000,7 @@
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A275" t="s">
+      <c r="A275" s="3" t="s">
         <v>106</v>
       </c>
       <c r="B275">
@@ -10005,7 +10011,7 @@
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
+      <c r="A276" s="3" t="s">
         <v>337</v>
       </c>
       <c r="B276">
@@ -10016,7 +10022,7 @@
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A277" t="s">
+      <c r="A277" s="3" t="s">
         <v>336</v>
       </c>
       <c r="B277">
@@ -10027,7 +10033,7 @@
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A278" t="s">
+      <c r="A278" s="3" t="s">
         <v>166</v>
       </c>
       <c r="B278">
@@ -10038,7 +10044,7 @@
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A279" t="s">
+      <c r="A279" s="3" t="s">
         <v>203</v>
       </c>
       <c r="B279">
@@ -10049,7 +10055,7 @@
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A280" t="s">
+      <c r="A280" s="3" t="s">
         <v>251</v>
       </c>
       <c r="B280">
@@ -10060,7 +10066,7 @@
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A281" t="s">
+      <c r="A281" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B281">
@@ -10071,7 +10077,7 @@
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A282" t="s">
+      <c r="A282" s="3" t="s">
         <v>252</v>
       </c>
       <c r="B282">
@@ -10082,7 +10088,7 @@
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A283" t="s">
+      <c r="A283" s="3" t="s">
         <v>157</v>
       </c>
       <c r="B283">
@@ -10093,7 +10099,7 @@
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A284" t="s">
+      <c r="A284" s="3" t="s">
         <v>82</v>
       </c>
       <c r="B284">
@@ -10104,7 +10110,7 @@
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A285" t="s">
+      <c r="A285" s="3" t="s">
         <v>309</v>
       </c>
       <c r="B285">
@@ -10115,7 +10121,7 @@
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A286" t="s">
+      <c r="A286" s="3" t="s">
         <v>168</v>
       </c>
       <c r="B286">
@@ -10126,7 +10132,7 @@
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A287" t="s">
+      <c r="A287" s="3" t="s">
         <v>310</v>
       </c>
       <c r="B287">
@@ -10137,7 +10143,7 @@
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A288" t="s">
+      <c r="A288" s="3" t="s">
         <v>152</v>
       </c>
       <c r="B288">
@@ -10148,7 +10154,7 @@
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A289" t="s">
+      <c r="A289" s="3" t="s">
         <v>118</v>
       </c>
       <c r="B289">
@@ -10159,7 +10165,7 @@
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A290" t="s">
+      <c r="A290" s="3" t="s">
         <v>170</v>
       </c>
       <c r="B290">
@@ -10170,7 +10176,7 @@
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A291" t="s">
+      <c r="A291" s="3" t="s">
         <v>330</v>
       </c>
       <c r="B291">
@@ -10181,7 +10187,7 @@
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A292" t="s">
+      <c r="A292" s="3" t="s">
         <v>257</v>
       </c>
       <c r="B292">
@@ -10192,7 +10198,7 @@
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A293" t="s">
+      <c r="A293" s="3" t="s">
         <v>175</v>
       </c>
       <c r="B293">
@@ -10203,7 +10209,7 @@
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A294" t="s">
+      <c r="A294" s="3" t="s">
         <v>259</v>
       </c>
       <c r="B294">
@@ -10214,7 +10220,7 @@
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A295" t="s">
+      <c r="A295" s="3" t="s">
         <v>139</v>
       </c>
       <c r="B295">
@@ -10225,7 +10231,7 @@
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A296" t="s">
+      <c r="A296" s="3" t="s">
         <v>147</v>
       </c>
       <c r="B296">
@@ -10236,7 +10242,7 @@
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
+      <c r="A297" s="3" t="s">
         <v>213</v>
       </c>
       <c r="B297">
@@ -10247,7 +10253,7 @@
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A298" t="s">
+      <c r="A298" s="3" t="s">
         <v>128</v>
       </c>
       <c r="B298">
@@ -10258,7 +10264,7 @@
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A299" t="s">
+      <c r="A299" s="3" t="s">
         <v>240</v>
       </c>
       <c r="B299">
@@ -10269,7 +10275,7 @@
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A300" t="s">
+      <c r="A300" s="3" t="s">
         <v>307</v>
       </c>
       <c r="B300">
@@ -10280,7 +10286,7 @@
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A301" t="s">
+      <c r="A301" s="3" t="s">
         <v>134</v>
       </c>
       <c r="B301">
@@ -10291,7 +10297,7 @@
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A302" t="s">
+      <c r="A302" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B302">
@@ -10302,7 +10308,7 @@
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
+      <c r="A303" s="3" t="s">
         <v>211</v>
       </c>
       <c r="B303">
@@ -10313,7 +10319,7 @@
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A304" t="s">
+      <c r="A304" s="3" t="s">
         <v>300</v>
       </c>
       <c r="B304">
@@ -10324,7 +10330,7 @@
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A305" t="s">
+      <c r="A305" s="3" t="s">
         <v>193</v>
       </c>
       <c r="B305">
@@ -10335,7 +10341,7 @@
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
+      <c r="A306" s="3" t="s">
         <v>304</v>
       </c>
       <c r="B306">
@@ -10346,7 +10352,7 @@
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
+      <c r="A307" s="3" t="s">
         <v>117</v>
       </c>
       <c r="B307">
@@ -10357,7 +10363,7 @@
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
+      <c r="A308" s="3" t="s">
         <v>171</v>
       </c>
       <c r="B308">
@@ -10368,7 +10374,7 @@
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A309" t="s">
+      <c r="A309" s="3" t="s">
         <v>338</v>
       </c>
       <c r="B309">
@@ -10379,7 +10385,7 @@
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A310" t="s">
+      <c r="A310" s="3" t="s">
         <v>142</v>
       </c>
       <c r="B310">
@@ -10390,7 +10396,7 @@
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A311" t="s">
+      <c r="A311" s="3" t="s">
         <v>120</v>
       </c>
       <c r="B311">
@@ -10401,7 +10407,7 @@
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A312" t="s">
+      <c r="A312" s="3" t="s">
         <v>173</v>
       </c>
       <c r="B312">
@@ -10412,7 +10418,7 @@
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A313" t="s">
+      <c r="A313" s="3" t="s">
         <v>123</v>
       </c>
       <c r="B313">
@@ -10423,7 +10429,7 @@
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A314" t="s">
+      <c r="A314" s="3" t="s">
         <v>235</v>
       </c>
       <c r="B314">
@@ -10434,7 +10440,7 @@
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A315" t="s">
+      <c r="A315" s="3" t="s">
         <v>143</v>
       </c>
       <c r="B315">
@@ -10445,7 +10451,7 @@
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A316" t="s">
+      <c r="A316" s="3" t="s">
         <v>114</v>
       </c>
       <c r="B316">
@@ -10456,7 +10462,7 @@
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A317" t="s">
+      <c r="A317" s="3" t="s">
         <v>317</v>
       </c>
       <c r="B317">
@@ -10467,7 +10473,7 @@
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A318" t="s">
+      <c r="A318" s="3" t="s">
         <v>332</v>
       </c>
       <c r="B318">
@@ -10478,7 +10484,7 @@
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A319" t="s">
+      <c r="A319" s="3" t="s">
         <v>239</v>
       </c>
       <c r="B319">
@@ -10489,7 +10495,7 @@
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A320" t="s">
+      <c r="A320" s="3" t="s">
         <v>312</v>
       </c>
       <c r="B320">
@@ -10500,7 +10506,7 @@
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A321" t="s">
+      <c r="A321" s="3" t="s">
         <v>99</v>
       </c>
       <c r="B321">
@@ -10511,7 +10517,7 @@
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A322" t="s">
+      <c r="A322" s="3" t="s">
         <v>102</v>
       </c>
       <c r="B322">
@@ -10522,7 +10528,7 @@
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A323" t="s">
+      <c r="A323" s="3" t="s">
         <v>254</v>
       </c>
       <c r="B323">
@@ -10533,7 +10539,7 @@
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A324" t="s">
+      <c r="A324" s="3" t="s">
         <v>323</v>
       </c>
       <c r="B324">
@@ -10544,7 +10550,7 @@
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A325" t="s">
+      <c r="A325" s="3" t="s">
         <v>255</v>
       </c>
       <c r="B325">
@@ -10555,7 +10561,7 @@
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A326" t="s">
+      <c r="A326" s="3" t="s">
         <v>314</v>
       </c>
       <c r="B326">
@@ -10566,7 +10572,7 @@
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A327" t="s">
+      <c r="A327" s="3" t="s">
         <v>256</v>
       </c>
       <c r="B327">
@@ -10577,7 +10583,7 @@
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A328" t="s">
+      <c r="A328" s="3" t="s">
         <v>327</v>
       </c>
       <c r="B328">
@@ -10588,7 +10594,7 @@
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A329" t="s">
+      <c r="A329" s="3" t="s">
         <v>258</v>
       </c>
       <c r="B329">
@@ -10599,7 +10605,7 @@
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A330" t="s">
+      <c r="A330" s="3" t="s">
         <v>318</v>
       </c>
       <c r="B330">
@@ -10610,7 +10616,7 @@
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A331" t="s">
+      <c r="A331" s="3" t="s">
         <v>350</v>
       </c>
       <c r="B331">
@@ -10621,7 +10627,7 @@
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A332" t="s">
+      <c r="A332" s="3" t="s">
         <v>253</v>
       </c>
       <c r="B332">
@@ -10632,7 +10638,7 @@
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A333" t="s">
+      <c r="A333" s="3" t="s">
         <v>305</v>
       </c>
       <c r="B333">
@@ -10643,7 +10649,7 @@
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A334" t="s">
+      <c r="A334" s="3" t="s">
         <v>145</v>
       </c>
       <c r="B334">
@@ -10654,7 +10660,7 @@
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A335" t="s">
+      <c r="A335" s="3" t="s">
         <v>351</v>
       </c>
       <c r="B335">
@@ -10665,7 +10671,7 @@
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A336" t="s">
+      <c r="A336" s="3" t="s">
         <v>180</v>
       </c>
       <c r="B336">
@@ -10676,7 +10682,7 @@
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A337" t="s">
+      <c r="A337" s="3" t="s">
         <v>352</v>
       </c>
       <c r="B337">
@@ -10687,7 +10693,7 @@
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A338" t="s">
+      <c r="A338" s="3" t="s">
         <v>119</v>
       </c>
       <c r="B338">
@@ -10698,7 +10704,7 @@
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A339" t="s">
+      <c r="A339" s="3" t="s">
         <v>353</v>
       </c>
       <c r="B339">
@@ -10709,7 +10715,7 @@
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A340" t="s">
+      <c r="A340" s="3" t="s">
         <v>104</v>
       </c>
       <c r="B340">
@@ -10720,7 +10726,7 @@
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A341" t="s">
+      <c r="A341" s="3" t="s">
         <v>354</v>
       </c>
       <c r="B341">
@@ -10731,7 +10737,7 @@
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A342" t="s">
+      <c r="A342" s="3" t="s">
         <v>154</v>
       </c>
       <c r="B342">
@@ -10742,7 +10748,7 @@
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A343" t="s">
+      <c r="A343" s="3" t="s">
         <v>355</v>
       </c>
       <c r="B343">
@@ -10753,7 +10759,7 @@
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A344" t="s">
+      <c r="A344" s="3" t="s">
         <v>237</v>
       </c>
       <c r="B344">
@@ -10764,7 +10770,7 @@
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A345" t="s">
+      <c r="A345" s="3" t="s">
         <v>183</v>
       </c>
       <c r="B345">

--- a/STOK RANK/Rank Dealer/RANK BHG.xlsx
+++ b/STOK RANK/Rank Dealer/RANK BHG.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\DASHBOARD RANK STOK\data\Rank Dealer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D14AEE6-89FD-497C-A925-7BA1B15FDAF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B3E175-67B0-473B-864B-92B9F80A1350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B751393D-4C32-4D4C-AA97-AA7CC129AC75}"/>
   </bookViews>
@@ -1575,7 +1575,7 @@
         <v>173</v>
       </c>
       <c r="C2" s="1">
-        <v>28.833333333333332</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1">
         <v>28.833333333333332</v>
@@ -1595,7 +1595,7 @@
         <v>88</v>
       </c>
       <c r="C3" s="1">
-        <v>14.666666666666666</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1">
         <v>43.5</v>
@@ -1635,7 +1635,7 @@
         <v>83</v>
       </c>
       <c r="C5" s="1">
-        <v>13.833333333333334</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1">
         <v>71.333333333333329</v>
@@ -1655,7 +1655,7 @@
         <v>70</v>
       </c>
       <c r="C6" s="1">
-        <v>11.666666666666666</v>
+        <v>12</v>
       </c>
       <c r="D6" s="1">
         <v>83</v>
@@ -1675,7 +1675,7 @@
         <v>68</v>
       </c>
       <c r="C7" s="1">
-        <v>11.333333333333334</v>
+        <v>12</v>
       </c>
       <c r="D7" s="1">
         <v>94.333333333333329</v>
@@ -1695,7 +1695,7 @@
         <v>61</v>
       </c>
       <c r="C8" s="1">
-        <v>10.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="D8" s="1">
         <v>104.5</v>
@@ -1735,7 +1735,7 @@
         <v>53</v>
       </c>
       <c r="C10" s="1">
-        <v>8.8333333333333339</v>
+        <v>9</v>
       </c>
       <c r="D10" s="1">
         <v>122.33333333333333</v>
@@ -1755,7 +1755,7 @@
         <v>50</v>
       </c>
       <c r="C11" s="1">
-        <v>8.3333333333333339</v>
+        <v>9</v>
       </c>
       <c r="D11" s="1">
         <v>130.66666666666666</v>
@@ -1775,7 +1775,7 @@
         <v>37</v>
       </c>
       <c r="C12" s="1">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="D12" s="1">
         <v>136.83333333333331</v>
@@ -1795,7 +1795,7 @@
         <v>28</v>
       </c>
       <c r="C13" s="1">
-        <v>4.666666666666667</v>
+        <v>5</v>
       </c>
       <c r="D13" s="1">
         <v>141.49999999999997</v>
@@ -1815,7 +1815,7 @@
         <v>27</v>
       </c>
       <c r="C14" s="1">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="D14" s="1">
         <v>145.99999999999997</v>
@@ -1835,7 +1835,7 @@
         <v>25</v>
       </c>
       <c r="C15" s="1">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="D15" s="1">
         <v>150.16666666666663</v>
@@ -1855,7 +1855,7 @@
         <v>23</v>
       </c>
       <c r="C16" s="1">
-        <v>3.8333333333333335</v>
+        <v>4</v>
       </c>
       <c r="D16" s="1">
         <v>153.99999999999997</v>
@@ -1875,7 +1875,7 @@
         <v>23</v>
       </c>
       <c r="C17" s="1">
-        <v>3.8333333333333335</v>
+        <v>4</v>
       </c>
       <c r="D17" s="1">
         <v>157.83333333333331</v>
@@ -1895,7 +1895,7 @@
         <v>23</v>
       </c>
       <c r="C18" s="1">
-        <v>3.8333333333333335</v>
+        <v>4</v>
       </c>
       <c r="D18" s="1">
         <v>161.66666666666666</v>
@@ -1915,7 +1915,7 @@
         <v>22</v>
       </c>
       <c r="C19" s="1">
-        <v>3.6666666666666665</v>
+        <v>4</v>
       </c>
       <c r="D19" s="1">
         <v>165.33333333333331</v>
@@ -1935,7 +1935,7 @@
         <v>22</v>
       </c>
       <c r="C20" s="1">
-        <v>3.6666666666666665</v>
+        <v>4</v>
       </c>
       <c r="D20" s="1">
         <v>168.99999999999997</v>
@@ -1955,7 +1955,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="1">
-        <v>3.3333333333333335</v>
+        <v>4</v>
       </c>
       <c r="D21" s="1">
         <v>172.33333333333331</v>
@@ -1975,7 +1975,7 @@
         <v>19</v>
       </c>
       <c r="C22" s="1">
-        <v>3.1666666666666665</v>
+        <v>4</v>
       </c>
       <c r="D22" s="1">
         <v>175.49999999999997</v>
@@ -2015,7 +2015,7 @@
         <v>16</v>
       </c>
       <c r="C24" s="1">
-        <v>2.6666666666666665</v>
+        <v>3</v>
       </c>
       <c r="D24" s="1">
         <v>181.16666666666663</v>
@@ -2035,7 +2035,7 @@
         <v>16</v>
       </c>
       <c r="C25" s="1">
-        <v>2.6666666666666665</v>
+        <v>3</v>
       </c>
       <c r="D25" s="1">
         <v>183.83333333333329</v>
@@ -2055,7 +2055,7 @@
         <v>16</v>
       </c>
       <c r="C26" s="1">
-        <v>2.6666666666666665</v>
+        <v>3</v>
       </c>
       <c r="D26" s="1">
         <v>186.49999999999994</v>
@@ -2075,7 +2075,7 @@
         <v>15</v>
       </c>
       <c r="C27" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D27" s="1">
         <v>188.99999999999994</v>
@@ -2095,7 +2095,7 @@
         <v>15</v>
       </c>
       <c r="C28" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D28" s="1">
         <v>191.49999999999994</v>
@@ -2115,7 +2115,7 @@
         <v>15</v>
       </c>
       <c r="C29" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D29" s="1">
         <v>193.99999999999994</v>
@@ -2135,7 +2135,7 @@
         <v>15</v>
       </c>
       <c r="C30" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D30" s="1">
         <v>196.49999999999994</v>
@@ -2155,7 +2155,7 @@
         <v>15</v>
       </c>
       <c r="C31" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D31" s="1">
         <v>198.99999999999994</v>
@@ -2175,7 +2175,7 @@
         <v>15</v>
       </c>
       <c r="C32" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D32" s="1">
         <v>201.49999999999994</v>
@@ -2195,7 +2195,7 @@
         <v>13</v>
       </c>
       <c r="C33" s="1">
-        <v>2.1666666666666665</v>
+        <v>3</v>
       </c>
       <c r="D33" s="1">
         <v>203.6666666666666</v>
@@ -2215,7 +2215,7 @@
         <v>13</v>
       </c>
       <c r="C34" s="1">
-        <v>2.1666666666666665</v>
+        <v>3</v>
       </c>
       <c r="D34" s="1">
         <v>205.83333333333326</v>
@@ -2275,7 +2275,7 @@
         <v>11</v>
       </c>
       <c r="C37" s="1">
-        <v>1.8333333333333333</v>
+        <v>2</v>
       </c>
       <c r="D37" s="1">
         <v>211.6666666666666</v>
@@ -2295,7 +2295,7 @@
         <v>11</v>
       </c>
       <c r="C38" s="1">
-        <v>1.8333333333333333</v>
+        <v>2</v>
       </c>
       <c r="D38" s="1">
         <v>213.49999999999994</v>
@@ -2315,7 +2315,7 @@
         <v>10</v>
       </c>
       <c r="C39" s="1">
-        <v>1.6666666666666667</v>
+        <v>2</v>
       </c>
       <c r="D39" s="1">
         <v>215.1666666666666</v>
@@ -2335,7 +2335,7 @@
         <v>8</v>
       </c>
       <c r="C40" s="1">
-        <v>1.3333333333333333</v>
+        <v>2</v>
       </c>
       <c r="D40" s="1">
         <v>216.49999999999994</v>
@@ -2355,7 +2355,7 @@
         <v>8</v>
       </c>
       <c r="C41" s="1">
-        <v>1.3333333333333333</v>
+        <v>2</v>
       </c>
       <c r="D41" s="1">
         <v>217.83333333333329</v>
@@ -2375,7 +2375,7 @@
         <v>8</v>
       </c>
       <c r="C42" s="1">
-        <v>1.3333333333333333</v>
+        <v>2</v>
       </c>
       <c r="D42" s="1">
         <v>219.16666666666663</v>
@@ -2395,7 +2395,7 @@
         <v>7</v>
       </c>
       <c r="C43" s="1">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
       <c r="D43" s="1">
         <v>220.33333333333329</v>
@@ -2475,7 +2475,7 @@
         <v>5</v>
       </c>
       <c r="C47" s="1">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="D47" s="1">
         <v>224.16666666666663</v>
@@ -2495,7 +2495,7 @@
         <v>5</v>
       </c>
       <c r="C48" s="1">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="D48" s="1">
         <v>224.99999999999997</v>
@@ -2515,7 +2515,7 @@
         <v>5</v>
       </c>
       <c r="C49" s="1">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="D49" s="1">
         <v>225.83333333333331</v>
@@ -2535,7 +2535,7 @@
         <v>5</v>
       </c>
       <c r="C50" s="1">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="D50" s="1">
         <v>226.66666666666666</v>
@@ -2555,7 +2555,7 @@
         <v>5</v>
       </c>
       <c r="C51" s="1">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="D51" s="1">
         <v>227.5</v>
@@ -2575,7 +2575,7 @@
         <v>4</v>
       </c>
       <c r="C52" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D52" s="1">
         <v>228.16666666666666</v>
@@ -2595,7 +2595,7 @@
         <v>4</v>
       </c>
       <c r="C53" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D53" s="1">
         <v>228.83333333333331</v>
@@ -2615,7 +2615,7 @@
         <v>4</v>
       </c>
       <c r="C54" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D54" s="1">
         <v>229.49999999999997</v>
@@ -2635,7 +2635,7 @@
         <v>4</v>
       </c>
       <c r="C55" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D55" s="1">
         <v>230.16666666666663</v>
@@ -2655,7 +2655,7 @@
         <v>4</v>
       </c>
       <c r="C56" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D56" s="1">
         <v>230.83333333333329</v>
@@ -2675,7 +2675,7 @@
         <v>4</v>
       </c>
       <c r="C57" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D57" s="1">
         <v>231.49999999999994</v>
@@ -2695,7 +2695,7 @@
         <v>4</v>
       </c>
       <c r="C58" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D58" s="1">
         <v>232.1666666666666</v>
@@ -2715,7 +2715,7 @@
         <v>4</v>
       </c>
       <c r="C59" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D59" s="1">
         <v>232.83333333333326</v>
@@ -2735,7 +2735,7 @@
         <v>4</v>
       </c>
       <c r="C60" s="1">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D60" s="1">
         <v>233.49999999999991</v>
@@ -2755,7 +2755,7 @@
         <v>3</v>
       </c>
       <c r="C61" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D61" s="1">
         <v>233.99999999999991</v>
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C62" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D62" s="1">
         <v>234.49999999999991</v>
@@ -2795,7 +2795,7 @@
         <v>3</v>
       </c>
       <c r="C63" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D63" s="1">
         <v>234.99999999999991</v>
@@ -2815,7 +2815,7 @@
         <v>3</v>
       </c>
       <c r="C64" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D64" s="1">
         <v>235.49999999999991</v>
@@ -2835,7 +2835,7 @@
         <v>3</v>
       </c>
       <c r="C65" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D65" s="1">
         <v>235.99999999999991</v>
@@ -2855,7 +2855,7 @@
         <v>3</v>
       </c>
       <c r="C66" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D66" s="1">
         <v>236.49999999999991</v>
@@ -2875,7 +2875,7 @@
         <v>3</v>
       </c>
       <c r="C67" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D67" s="1">
         <v>236.99999999999991</v>
@@ -2895,7 +2895,7 @@
         <v>3</v>
       </c>
       <c r="C68" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D68" s="1">
         <v>237.49999999999991</v>
@@ -2915,7 +2915,7 @@
         <v>3</v>
       </c>
       <c r="C69" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D69" s="1">
         <v>237.99999999999991</v>
@@ -2935,7 +2935,7 @@
         <v>3</v>
       </c>
       <c r="C70" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D70" s="1">
         <v>238.49999999999991</v>
@@ -2955,7 +2955,7 @@
         <v>3</v>
       </c>
       <c r="C71" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D71" s="1">
         <v>238.99999999999991</v>
@@ -2975,7 +2975,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D72" s="1">
         <v>239.49999999999991</v>
@@ -2995,7 +2995,7 @@
         <v>3</v>
       </c>
       <c r="C73" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D73" s="1">
         <v>239.99999999999991</v>
@@ -3015,7 +3015,7 @@
         <v>3</v>
       </c>
       <c r="C74" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D74" s="1">
         <v>240.49999999999991</v>
@@ -3035,7 +3035,7 @@
         <v>3</v>
       </c>
       <c r="C75" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D75" s="1">
         <v>240.99999999999991</v>
@@ -3055,7 +3055,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D76" s="1">
         <v>241.33333333333326</v>
@@ -3075,7 +3075,7 @@
         <v>2</v>
       </c>
       <c r="C77" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D77" s="1">
         <v>241.6666666666666</v>
@@ -3095,7 +3095,7 @@
         <v>2</v>
       </c>
       <c r="C78" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D78" s="1">
         <v>241.99999999999994</v>
@@ -3115,7 +3115,7 @@
         <v>2</v>
       </c>
       <c r="C79" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D79" s="1">
         <v>242.33333333333329</v>
@@ -3135,7 +3135,7 @@
         <v>2</v>
       </c>
       <c r="C80" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D80" s="1">
         <v>242.66666666666663</v>
@@ -3155,7 +3155,7 @@
         <v>2</v>
       </c>
       <c r="C81" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D81" s="1">
         <v>242.99999999999997</v>
@@ -3175,7 +3175,7 @@
         <v>2</v>
       </c>
       <c r="C82" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D82" s="1">
         <v>243.33333333333331</v>
@@ -3195,7 +3195,7 @@
         <v>2</v>
       </c>
       <c r="C83" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D83" s="1">
         <v>243.66666666666666</v>
@@ -3215,7 +3215,7 @@
         <v>2</v>
       </c>
       <c r="C84" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D84" s="1">
         <v>244</v>
@@ -3235,7 +3235,7 @@
         <v>2</v>
       </c>
       <c r="C85" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D85" s="1">
         <v>244.33333333333334</v>
@@ -3255,7 +3255,7 @@
         <v>2</v>
       </c>
       <c r="C86" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D86" s="1">
         <v>244.66666666666669</v>
@@ -3275,7 +3275,7 @@
         <v>2</v>
       </c>
       <c r="C87" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D87" s="1">
         <v>245.00000000000003</v>
@@ -3295,7 +3295,7 @@
         <v>2</v>
       </c>
       <c r="C88" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D88" s="1">
         <v>245.33333333333337</v>
@@ -3315,7 +3315,7 @@
         <v>2</v>
       </c>
       <c r="C89" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D89" s="1">
         <v>245.66666666666671</v>
@@ -3335,7 +3335,7 @@
         <v>2</v>
       </c>
       <c r="C90" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D90" s="1">
         <v>246.00000000000006</v>
@@ -3355,7 +3355,7 @@
         <v>2</v>
       </c>
       <c r="C91" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D91" s="1">
         <v>246.3333333333334</v>
@@ -3375,7 +3375,7 @@
         <v>2</v>
       </c>
       <c r="C92" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D92" s="1">
         <v>246.66666666666674</v>
@@ -3395,7 +3395,7 @@
         <v>2</v>
       </c>
       <c r="C93" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D93" s="1">
         <v>247.00000000000009</v>
@@ -3415,7 +3415,7 @@
         <v>2</v>
       </c>
       <c r="C94" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D94" s="1">
         <v>247.33333333333343</v>
@@ -3435,7 +3435,7 @@
         <v>2</v>
       </c>
       <c r="C95" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D95" s="1">
         <v>247.66666666666677</v>
@@ -3455,7 +3455,7 @@
         <v>2</v>
       </c>
       <c r="C96" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D96" s="1">
         <v>248.00000000000011</v>
@@ -3475,7 +3475,7 @@
         <v>2</v>
       </c>
       <c r="C97" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D97" s="1">
         <v>248.33333333333346</v>
@@ -3495,7 +3495,7 @@
         <v>2</v>
       </c>
       <c r="C98" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D98" s="1">
         <v>248.6666666666668</v>
@@ -3515,7 +3515,7 @@
         <v>2</v>
       </c>
       <c r="C99" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D99" s="1">
         <v>249.00000000000014</v>
@@ -3535,7 +3535,7 @@
         <v>2</v>
       </c>
       <c r="C100" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D100" s="1">
         <v>249.33333333333348</v>
@@ -3555,7 +3555,7 @@
         <v>2</v>
       </c>
       <c r="C101" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D101" s="1">
         <v>249.66666666666683</v>
@@ -3575,7 +3575,7 @@
         <v>2</v>
       </c>
       <c r="C102" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D102" s="1">
         <v>250.00000000000017</v>
@@ -3595,7 +3595,7 @@
         <v>2</v>
       </c>
       <c r="C103" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D103" s="1">
         <v>250.33333333333351</v>
@@ -3615,7 +3615,7 @@
         <v>2</v>
       </c>
       <c r="C104" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D104" s="1">
         <v>250.66666666666686</v>
@@ -3635,7 +3635,7 @@
         <v>2</v>
       </c>
       <c r="C105" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D105" s="1">
         <v>251.0000000000002</v>
@@ -3655,7 +3655,7 @@
         <v>2</v>
       </c>
       <c r="C106" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D106" s="1">
         <v>251.33333333333354</v>
@@ -3675,7 +3675,7 @@
         <v>2</v>
       </c>
       <c r="C107" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D107" s="1">
         <v>251.66666666666688</v>
@@ -3695,7 +3695,7 @@
         <v>2</v>
       </c>
       <c r="C108" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D108" s="1">
         <v>252.00000000000023</v>
@@ -3715,7 +3715,7 @@
         <v>2</v>
       </c>
       <c r="C109" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D109" s="1">
         <v>252.33333333333357</v>
@@ -3735,7 +3735,7 @@
         <v>2</v>
       </c>
       <c r="C110" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D110" s="1">
         <v>252.66666666666691</v>
@@ -3755,7 +3755,7 @@
         <v>2</v>
       </c>
       <c r="C111" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D111" s="1">
         <v>253.00000000000026</v>
@@ -3775,7 +3775,7 @@
         <v>2</v>
       </c>
       <c r="C112" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D112" s="1">
         <v>253.3333333333336</v>
@@ -3795,7 +3795,7 @@
         <v>2</v>
       </c>
       <c r="C113" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D113" s="1">
         <v>253.66666666666694</v>
@@ -3815,7 +3815,7 @@
         <v>2</v>
       </c>
       <c r="C114" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D114" s="1">
         <v>254.00000000000028</v>
@@ -3835,7 +3835,7 @@
         <v>2</v>
       </c>
       <c r="C115" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D115" s="1">
         <v>254.33333333333363</v>
@@ -3855,7 +3855,7 @@
         <v>2</v>
       </c>
       <c r="C116" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D116" s="1">
         <v>254.66666666666697</v>
@@ -3875,7 +3875,7 @@
         <v>2</v>
       </c>
       <c r="C117" s="1">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D117" s="1">
         <v>255.00000000000031</v>
@@ -3895,7 +3895,7 @@
         <v>1</v>
       </c>
       <c r="C118" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D118" s="1">
         <v>255.16666666666697</v>
@@ -3915,7 +3915,7 @@
         <v>1</v>
       </c>
       <c r="C119" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D119" s="1">
         <v>255.33333333333363</v>
@@ -3935,7 +3935,7 @@
         <v>1</v>
       </c>
       <c r="C120" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D120" s="1">
         <v>255.50000000000028</v>
@@ -3955,7 +3955,7 @@
         <v>1</v>
       </c>
       <c r="C121" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D121" s="1">
         <v>255.66666666666694</v>
@@ -3975,7 +3975,7 @@
         <v>1</v>
       </c>
       <c r="C122" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D122" s="1">
         <v>255.8333333333336</v>
@@ -3995,7 +3995,7 @@
         <v>1</v>
       </c>
       <c r="C123" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D123" s="1">
         <v>256.00000000000028</v>
@@ -4015,7 +4015,7 @@
         <v>1</v>
       </c>
       <c r="C124" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D124" s="1">
         <v>256.16666666666697</v>
@@ -4035,7 +4035,7 @@
         <v>1</v>
       </c>
       <c r="C125" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D125" s="1">
         <v>256.33333333333366</v>
@@ -4055,7 +4055,7 @@
         <v>1</v>
       </c>
       <c r="C126" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D126" s="1">
         <v>256.50000000000034</v>
@@ -4075,7 +4075,7 @@
         <v>1</v>
       </c>
       <c r="C127" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D127" s="1">
         <v>256.66666666666703</v>
@@ -4095,7 +4095,7 @@
         <v>1</v>
       </c>
       <c r="C128" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D128" s="1">
         <v>256.83333333333371</v>
@@ -4115,7 +4115,7 @@
         <v>1</v>
       </c>
       <c r="C129" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D129" s="1">
         <v>257.0000000000004</v>
@@ -4135,7 +4135,7 @@
         <v>1</v>
       </c>
       <c r="C130" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D130" s="1">
         <v>257.16666666666708</v>
@@ -4155,7 +4155,7 @@
         <v>1</v>
       </c>
       <c r="C131" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D131" s="1">
         <v>257.33333333333377</v>
@@ -4175,7 +4175,7 @@
         <v>1</v>
       </c>
       <c r="C132" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D132" s="1">
         <v>257.50000000000045</v>
@@ -4195,7 +4195,7 @@
         <v>1</v>
       </c>
       <c r="C133" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D133" s="1">
         <v>257.66666666666714</v>
@@ -4215,7 +4215,7 @@
         <v>1</v>
       </c>
       <c r="C134" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D134" s="1">
         <v>257.83333333333383</v>
@@ -4235,7 +4235,7 @@
         <v>1</v>
       </c>
       <c r="C135" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D135" s="1">
         <v>258.00000000000051</v>
@@ -4255,7 +4255,7 @@
         <v>1</v>
       </c>
       <c r="C136" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D136" s="1">
         <v>258.1666666666672</v>
@@ -4275,7 +4275,7 @@
         <v>1</v>
       </c>
       <c r="C137" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D137" s="1">
         <v>258.33333333333388</v>
@@ -4295,7 +4295,7 @@
         <v>1</v>
       </c>
       <c r="C138" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D138" s="1">
         <v>258.50000000000057</v>
@@ -4315,7 +4315,7 @@
         <v>1</v>
       </c>
       <c r="C139" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D139" s="1">
         <v>258.66666666666725</v>
@@ -4335,7 +4335,7 @@
         <v>1</v>
       </c>
       <c r="C140" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D140" s="1">
         <v>258.83333333333394</v>
@@ -4355,7 +4355,7 @@
         <v>1</v>
       </c>
       <c r="C141" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D141" s="1">
         <v>259.00000000000063</v>
@@ -4375,7 +4375,7 @@
         <v>1</v>
       </c>
       <c r="C142" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D142" s="1">
         <v>259.16666666666731</v>
@@ -4395,7 +4395,7 @@
         <v>1</v>
       </c>
       <c r="C143" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D143" s="1">
         <v>259.333333333334</v>
@@ -4415,7 +4415,7 @@
         <v>1</v>
       </c>
       <c r="C144" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D144" s="1">
         <v>259.50000000000068</v>
@@ -4435,7 +4435,7 @@
         <v>1</v>
       </c>
       <c r="C145" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D145" s="1">
         <v>259.66666666666737</v>
@@ -4455,7 +4455,7 @@
         <v>1</v>
       </c>
       <c r="C146" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D146" s="1">
         <v>259.83333333333405</v>
@@ -4475,7 +4475,7 @@
         <v>1</v>
       </c>
       <c r="C147" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D147" s="1">
         <v>260.00000000000074</v>
@@ -4495,7 +4495,7 @@
         <v>1</v>
       </c>
       <c r="C148" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D148" s="1">
         <v>260.16666666666742</v>
@@ -4515,7 +4515,7 @@
         <v>1</v>
       </c>
       <c r="C149" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D149" s="1">
         <v>260.33333333333411</v>
@@ -4535,7 +4535,7 @@
         <v>1</v>
       </c>
       <c r="C150" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D150" s="1">
         <v>260.5000000000008</v>
@@ -4555,7 +4555,7 @@
         <v>1</v>
       </c>
       <c r="C151" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D151" s="1">
         <v>260.66666666666748</v>
@@ -4575,7 +4575,7 @@
         <v>1</v>
       </c>
       <c r="C152" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D152" s="1">
         <v>260.83333333333417</v>
@@ -4595,7 +4595,7 @@
         <v>1</v>
       </c>
       <c r="C153" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D153" s="1">
         <v>261.00000000000085</v>
@@ -4615,7 +4615,7 @@
         <v>1</v>
       </c>
       <c r="C154" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D154" s="1">
         <v>261.16666666666754</v>
@@ -4635,7 +4635,7 @@
         <v>1</v>
       </c>
       <c r="C155" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D155" s="1">
         <v>261.33333333333422</v>
@@ -4655,7 +4655,7 @@
         <v>1</v>
       </c>
       <c r="C156" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D156" s="1">
         <v>261.50000000000091</v>
@@ -4675,7 +4675,7 @@
         <v>1</v>
       </c>
       <c r="C157" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D157" s="1">
         <v>261.6666666666676</v>
@@ -4695,7 +4695,7 @@
         <v>1</v>
       </c>
       <c r="C158" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D158" s="1">
         <v>261.83333333333428</v>
@@ -4715,7 +4715,7 @@
         <v>1</v>
       </c>
       <c r="C159" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D159" s="1">
         <v>262.00000000000097</v>
@@ -4735,7 +4735,7 @@
         <v>1</v>
       </c>
       <c r="C160" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D160" s="1">
         <v>262.16666666666765</v>
@@ -4755,7 +4755,7 @@
         <v>1</v>
       </c>
       <c r="C161" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D161" s="1">
         <v>262.33333333333434</v>
@@ -4775,7 +4775,7 @@
         <v>1</v>
       </c>
       <c r="C162" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D162" s="1">
         <v>262.50000000000102</v>
@@ -4795,7 +4795,7 @@
         <v>1</v>
       </c>
       <c r="C163" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D163" s="1">
         <v>262.66666666666771</v>
@@ -4815,7 +4815,7 @@
         <v>1</v>
       </c>
       <c r="C164" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D164" s="1">
         <v>262.83333333333439</v>
@@ -4835,7 +4835,7 @@
         <v>1</v>
       </c>
       <c r="C165" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D165" s="1">
         <v>263.00000000000108</v>
@@ -4855,7 +4855,7 @@
         <v>1</v>
       </c>
       <c r="C166" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D166" s="1">
         <v>263.16666666666777</v>
@@ -4875,7 +4875,7 @@
         <v>1</v>
       </c>
       <c r="C167" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D167" s="1">
         <v>263.33333333333445</v>
@@ -4895,7 +4895,7 @@
         <v>1</v>
       </c>
       <c r="C168" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D168" s="1">
         <v>263.50000000000114</v>
@@ -4915,7 +4915,7 @@
         <v>1</v>
       </c>
       <c r="C169" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D169" s="1">
         <v>263.66666666666782</v>
@@ -4935,7 +4935,7 @@
         <v>1</v>
       </c>
       <c r="C170" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D170" s="1">
         <v>263.83333333333451</v>
@@ -4955,7 +4955,7 @@
         <v>1</v>
       </c>
       <c r="C171" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D171" s="1">
         <v>264.00000000000119</v>
@@ -4975,7 +4975,7 @@
         <v>1</v>
       </c>
       <c r="C172" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D172" s="1">
         <v>264.16666666666788</v>
@@ -4995,7 +4995,7 @@
         <v>1</v>
       </c>
       <c r="C173" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D173" s="1">
         <v>264.33333333333456</v>
@@ -5015,7 +5015,7 @@
         <v>1</v>
       </c>
       <c r="C174" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D174" s="1">
         <v>264.50000000000125</v>
@@ -5035,7 +5035,7 @@
         <v>1</v>
       </c>
       <c r="C175" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D175" s="1">
         <v>264.66666666666794</v>
@@ -5055,7 +5055,7 @@
         <v>1</v>
       </c>
       <c r="C176" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D176" s="1">
         <v>264.83333333333462</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="C177" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D177" s="1">
         <v>265.00000000000131</v>
@@ -5095,7 +5095,7 @@
         <v>1</v>
       </c>
       <c r="C178" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D178" s="1">
         <v>265.16666666666799</v>
@@ -5115,7 +5115,7 @@
         <v>1</v>
       </c>
       <c r="C179" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D179" s="1">
         <v>265.33333333333468</v>
@@ -5135,7 +5135,7 @@
         <v>1</v>
       </c>
       <c r="C180" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D180" s="1">
         <v>265.50000000000136</v>
@@ -5155,7 +5155,7 @@
         <v>1</v>
       </c>
       <c r="C181" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D181" s="1">
         <v>265.66666666666805</v>
@@ -5175,7 +5175,7 @@
         <v>1</v>
       </c>
       <c r="C182" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D182" s="1">
         <v>265.83333333333474</v>
@@ -5195,7 +5195,7 @@
         <v>1</v>
       </c>
       <c r="C183" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D183" s="1">
         <v>266.00000000000142</v>
@@ -5215,7 +5215,7 @@
         <v>1</v>
       </c>
       <c r="C184" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D184" s="1">
         <v>266.16666666666811</v>
@@ -5235,7 +5235,7 @@
         <v>1</v>
       </c>
       <c r="C185" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D185" s="1">
         <v>266.33333333333479</v>
@@ -5255,7 +5255,7 @@
         <v>1</v>
       </c>
       <c r="C186" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D186" s="1">
         <v>266.50000000000148</v>
@@ -5275,7 +5275,7 @@
         <v>1</v>
       </c>
       <c r="C187" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D187" s="1">
         <v>266.66666666666816</v>
@@ -5295,7 +5295,7 @@
         <v>1</v>
       </c>
       <c r="C188" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D188" s="1">
         <v>266.83333333333485</v>
@@ -5315,7 +5315,7 @@
         <v>1</v>
       </c>
       <c r="C189" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D189" s="1">
         <v>267.00000000000153</v>
@@ -5335,7 +5335,7 @@
         <v>1</v>
       </c>
       <c r="C190" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D190" s="1">
         <v>267.16666666666822</v>
@@ -5355,7 +5355,7 @@
         <v>1</v>
       </c>
       <c r="C191" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D191" s="1">
         <v>267.33333333333491</v>
@@ -5375,7 +5375,7 @@
         <v>1</v>
       </c>
       <c r="C192" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D192" s="1">
         <v>267.50000000000159</v>
@@ -5395,7 +5395,7 @@
         <v>1</v>
       </c>
       <c r="C193" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D193" s="1">
         <v>267.66666666666828</v>
@@ -5415,7 +5415,7 @@
         <v>1</v>
       </c>
       <c r="C194" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D194" s="1">
         <v>267.83333333333496</v>
@@ -5435,7 +5435,7 @@
         <v>1</v>
       </c>
       <c r="C195" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D195" s="1">
         <v>268.00000000000165</v>
@@ -5455,7 +5455,7 @@
         <v>1</v>
       </c>
       <c r="C196" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D196" s="1">
         <v>268.16666666666833</v>
@@ -5475,7 +5475,7 @@
         <v>1</v>
       </c>
       <c r="C197" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D197" s="1">
         <v>268.33333333333502</v>
@@ -5495,7 +5495,7 @@
         <v>1</v>
       </c>
       <c r="C198" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D198" s="1">
         <v>268.50000000000171</v>
@@ -5515,7 +5515,7 @@
         <v>1</v>
       </c>
       <c r="C199" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D199" s="1">
         <v>268.66666666666839</v>
@@ -5535,7 +5535,7 @@
         <v>1</v>
       </c>
       <c r="C200" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D200" s="1">
         <v>268.83333333333508</v>
@@ -5555,7 +5555,7 @@
         <v>1</v>
       </c>
       <c r="C201" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D201" s="1">
         <v>269.00000000000176</v>
@@ -5575,7 +5575,7 @@
         <v>1</v>
       </c>
       <c r="C202" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D202" s="1">
         <v>269.16666666666845</v>
@@ -5595,7 +5595,7 @@
         <v>1</v>
       </c>
       <c r="C203" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D203" s="1">
         <v>269.33333333333513</v>
@@ -5615,7 +5615,7 @@
         <v>1</v>
       </c>
       <c r="C204" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D204" s="1">
         <v>269.50000000000182</v>
@@ -5635,7 +5635,7 @@
         <v>1</v>
       </c>
       <c r="C205" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D205" s="1">
         <v>269.6666666666685</v>
@@ -5655,7 +5655,7 @@
         <v>1</v>
       </c>
       <c r="C206" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D206" s="1">
         <v>269.83333333333519</v>
@@ -5675,7 +5675,7 @@
         <v>1</v>
       </c>
       <c r="C207" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D207" s="1">
         <v>270.00000000000188</v>
@@ -5695,7 +5695,7 @@
         <v>1</v>
       </c>
       <c r="C208" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D208" s="1">
         <v>270.16666666666856</v>
@@ -5715,7 +5715,7 @@
         <v>1</v>
       </c>
       <c r="C209" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D209" s="1">
         <v>270.33333333333525</v>
@@ -5735,7 +5735,7 @@
         <v>1</v>
       </c>
       <c r="C210" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D210" s="1">
         <v>270.50000000000193</v>
@@ -5755,7 +5755,7 @@
         <v>1</v>
       </c>
       <c r="C211" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D211" s="1">
         <v>270.66666666666862</v>
@@ -5775,7 +5775,7 @@
         <v>1</v>
       </c>
       <c r="C212" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D212" s="1">
         <v>270.8333333333353</v>
@@ -5795,7 +5795,7 @@
         <v>1</v>
       </c>
       <c r="C213" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D213" s="1">
         <v>271.00000000000199</v>
@@ -5815,7 +5815,7 @@
         <v>1</v>
       </c>
       <c r="C214" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D214" s="1">
         <v>271.16666666666868</v>
@@ -5835,7 +5835,7 @@
         <v>1</v>
       </c>
       <c r="C215" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D215" s="1">
         <v>271.33333333333536</v>
@@ -5855,7 +5855,7 @@
         <v>1</v>
       </c>
       <c r="C216" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D216" s="1">
         <v>271.50000000000205</v>
@@ -5875,7 +5875,7 @@
         <v>1</v>
       </c>
       <c r="C217" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D217" s="1">
         <v>271.66666666666873</v>
@@ -5895,7 +5895,7 @@
         <v>1</v>
       </c>
       <c r="C218" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D218" s="1">
         <v>271.83333333333542</v>
@@ -5915,7 +5915,7 @@
         <v>1</v>
       </c>
       <c r="C219" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D219" s="1">
         <v>272.0000000000021</v>
@@ -5935,7 +5935,7 @@
         <v>1</v>
       </c>
       <c r="C220" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D220" s="1">
         <v>272.16666666666879</v>
@@ -5955,7 +5955,7 @@
         <v>1</v>
       </c>
       <c r="C221" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D221" s="1">
         <v>272.33333333333547</v>
@@ -5975,7 +5975,7 @@
         <v>1</v>
       </c>
       <c r="C222" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D222" s="1">
         <v>272.50000000000216</v>
@@ -5995,7 +5995,7 @@
         <v>1</v>
       </c>
       <c r="C223" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D223" s="1">
         <v>272.66666666666885</v>
@@ -6015,7 +6015,7 @@
         <v>1</v>
       </c>
       <c r="C224" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D224" s="1">
         <v>272.83333333333553</v>
@@ -6035,7 +6035,7 @@
         <v>1</v>
       </c>
       <c r="C225" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D225" s="1">
         <v>273.00000000000222</v>
@@ -6055,7 +6055,7 @@
         <v>1</v>
       </c>
       <c r="C226" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D226" s="1">
         <v>273.1666666666689</v>
@@ -6075,7 +6075,7 @@
         <v>1</v>
       </c>
       <c r="C227" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D227" s="1">
         <v>273.33333333333559</v>
@@ -6095,7 +6095,7 @@
         <v>1</v>
       </c>
       <c r="C228" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D228" s="1">
         <v>273.50000000000227</v>
@@ -6115,7 +6115,7 @@
         <v>1</v>
       </c>
       <c r="C229" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D229" s="1">
         <v>273.66666666666896</v>
@@ -6135,7 +6135,7 @@
         <v>1</v>
       </c>
       <c r="C230" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D230" s="1">
         <v>273.83333333333564</v>
@@ -6155,7 +6155,7 @@
         <v>1</v>
       </c>
       <c r="C231" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D231" s="1">
         <v>274.00000000000233</v>
@@ -6175,7 +6175,7 @@
         <v>1</v>
       </c>
       <c r="C232" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D232" s="1">
         <v>274.16666666666902</v>
@@ -6195,7 +6195,7 @@
         <v>1</v>
       </c>
       <c r="C233" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D233" s="1">
         <v>274.3333333333357</v>
@@ -6215,7 +6215,7 @@
         <v>1</v>
       </c>
       <c r="C234" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D234" s="1">
         <v>274.50000000000239</v>
@@ -6235,7 +6235,7 @@
         <v>1</v>
       </c>
       <c r="C235" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D235" s="1">
         <v>274.66666666666907</v>
@@ -6255,7 +6255,7 @@
         <v>1</v>
       </c>
       <c r="C236" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D236" s="1">
         <v>274.83333333333576</v>
@@ -6275,7 +6275,7 @@
         <v>1</v>
       </c>
       <c r="C237" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D237" s="1">
         <v>275.00000000000244</v>
@@ -6295,7 +6295,7 @@
         <v>1</v>
       </c>
       <c r="C238" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D238" s="1">
         <v>275.16666666666913</v>
@@ -6315,7 +6315,7 @@
         <v>1</v>
       </c>
       <c r="C239" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D239" s="1">
         <v>275.33333333333582</v>
@@ -6335,7 +6335,7 @@
         <v>1</v>
       </c>
       <c r="C240" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D240" s="1">
         <v>275.5000000000025</v>
@@ -6355,7 +6355,7 @@
         <v>1</v>
       </c>
       <c r="C241" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D241" s="1">
         <v>275.66666666666919</v>
@@ -6375,7 +6375,7 @@
         <v>1</v>
       </c>
       <c r="C242" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D242" s="1">
         <v>275.83333333333587</v>
@@ -6395,7 +6395,7 @@
         <v>1</v>
       </c>
       <c r="C243" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D243" s="1">
         <v>276.00000000000256</v>
@@ -6415,7 +6415,7 @@
         <v>1</v>
       </c>
       <c r="C244" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D244" s="1">
         <v>276.16666666666924</v>
@@ -6435,7 +6435,7 @@
         <v>1</v>
       </c>
       <c r="C245" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D245" s="1">
         <v>276.33333333333593</v>
@@ -6455,7 +6455,7 @@
         <v>1</v>
       </c>
       <c r="C246" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D246" s="1">
         <v>276.50000000000261</v>
@@ -6475,7 +6475,7 @@
         <v>1</v>
       </c>
       <c r="C247" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D247" s="1">
         <v>276.6666666666693</v>
@@ -6495,7 +6495,7 @@
         <v>1</v>
       </c>
       <c r="C248" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D248" s="1">
         <v>276.83333333333599</v>
@@ -6515,7 +6515,7 @@
         <v>1</v>
       </c>
       <c r="C249" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D249" s="1">
         <v>277.00000000000267</v>
@@ -6535,7 +6535,7 @@
         <v>1</v>
       </c>
       <c r="C250" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D250" s="1">
         <v>277.16666666666936</v>
@@ -6555,7 +6555,7 @@
         <v>1</v>
       </c>
       <c r="C251" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D251" s="1">
         <v>277.33333333333604</v>
@@ -6575,7 +6575,7 @@
         <v>1</v>
       </c>
       <c r="C252" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D252" s="1">
         <v>277.50000000000273</v>
@@ -6595,7 +6595,7 @@
         <v>1</v>
       </c>
       <c r="C253" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D253" s="1">
         <v>277.66666666666941</v>
@@ -6615,7 +6615,7 @@
         <v>1</v>
       </c>
       <c r="C254" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D254" s="1">
         <v>277.8333333333361</v>
@@ -6635,7 +6635,7 @@
         <v>1</v>
       </c>
       <c r="C255" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D255" s="1">
         <v>278.00000000000279</v>
@@ -6655,7 +6655,7 @@
         <v>1</v>
       </c>
       <c r="C256" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D256" s="1">
         <v>278.16666666666947</v>
@@ -6675,7 +6675,7 @@
         <v>1</v>
       </c>
       <c r="C257" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D257" s="1">
         <v>278.33333333333616</v>
@@ -6695,7 +6695,7 @@
         <v>1</v>
       </c>
       <c r="C258" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D258" s="1">
         <v>278.50000000000284</v>
@@ -6715,7 +6715,7 @@
         <v>1</v>
       </c>
       <c r="C259" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D259" s="1">
         <v>278.66666666666953</v>
@@ -6735,7 +6735,7 @@
         <v>1</v>
       </c>
       <c r="C260" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D260" s="1">
         <v>278.83333333333621</v>
@@ -6755,7 +6755,7 @@
         <v>1</v>
       </c>
       <c r="C261" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D261" s="1">
         <v>279.0000000000029</v>
@@ -6775,7 +6775,7 @@
         <v>1</v>
       </c>
       <c r="C262" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D262" s="1">
         <v>279.16666666666958</v>
@@ -6795,7 +6795,7 @@
         <v>1</v>
       </c>
       <c r="C263" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D263" s="1">
         <v>279.33333333333627</v>
@@ -6815,7 +6815,7 @@
         <v>1</v>
       </c>
       <c r="C264" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D264" s="1">
         <v>279.50000000000296</v>
@@ -6835,7 +6835,7 @@
         <v>1</v>
       </c>
       <c r="C265" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D265" s="1">
         <v>279.66666666666964</v>
@@ -6855,7 +6855,7 @@
         <v>1</v>
       </c>
       <c r="C266" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D266" s="1">
         <v>279.83333333333633</v>
@@ -6875,7 +6875,7 @@
         <v>1</v>
       </c>
       <c r="C267" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D267" s="1">
         <v>280.00000000000301</v>
@@ -6895,7 +6895,7 @@
         <v>1</v>
       </c>
       <c r="C268" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D268" s="1">
         <v>280.1666666666697</v>
@@ -6915,7 +6915,7 @@
         <v>1</v>
       </c>
       <c r="C269" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D269" s="1">
         <v>280.33333333333638</v>
@@ -6935,7 +6935,7 @@
         <v>1</v>
       </c>
       <c r="C270" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D270" s="1">
         <v>280.50000000000307</v>
@@ -6955,7 +6955,7 @@
         <v>1</v>
       </c>
       <c r="C271" s="1">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D271" s="1">
         <v>280.66666666666976</v>
@@ -7004,7 +7004,7 @@
         <v>2356</v>
       </c>
       <c r="C2">
-        <v>392.66666666666669</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -7015,7 +7015,7 @@
         <v>776</v>
       </c>
       <c r="C3">
-        <v>129.33333333333334</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -7026,7 +7026,7 @@
         <v>677</v>
       </c>
       <c r="C4">
-        <v>112.83333333333333</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -7037,7 +7037,7 @@
         <v>607</v>
       </c>
       <c r="C5">
-        <v>101.16666666666667</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -7059,7 +7059,7 @@
         <v>173</v>
       </c>
       <c r="C7">
-        <v>28.833333333333332</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -7070,7 +7070,7 @@
         <v>137</v>
       </c>
       <c r="C8">
-        <v>22.833333333333332</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -7081,7 +7081,7 @@
         <v>124</v>
       </c>
       <c r="C9">
-        <v>20.666666666666668</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -7092,7 +7092,7 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>16.666666666666668</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -7103,7 +7103,7 @@
         <v>88</v>
       </c>
       <c r="C11">
-        <v>14.666666666666666</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -7125,7 +7125,7 @@
         <v>83</v>
       </c>
       <c r="C13">
-        <v>13.833333333333334</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -7136,7 +7136,7 @@
         <v>71</v>
       </c>
       <c r="C14">
-        <v>11.833333333333334</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -7147,7 +7147,7 @@
         <v>70</v>
       </c>
       <c r="C15">
-        <v>11.666666666666666</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -7158,7 +7158,7 @@
         <v>68</v>
       </c>
       <c r="C16">
-        <v>11.333333333333334</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -7169,7 +7169,7 @@
         <v>62</v>
       </c>
       <c r="C17">
-        <v>10.333333333333334</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -7180,7 +7180,7 @@
         <v>61</v>
       </c>
       <c r="C18">
-        <v>10.166666666666666</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -7202,7 +7202,7 @@
         <v>53</v>
       </c>
       <c r="C20">
-        <v>8.8333333333333339</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -7213,7 +7213,7 @@
         <v>50</v>
       </c>
       <c r="C21">
-        <v>8.3333333333333339</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -7224,7 +7224,7 @@
         <v>50</v>
       </c>
       <c r="C22">
-        <v>8.3333333333333339</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -7246,7 +7246,7 @@
         <v>40</v>
       </c>
       <c r="C24">
-        <v>6.666666666666667</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -7257,7 +7257,7 @@
         <v>37</v>
       </c>
       <c r="C25">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -7268,7 +7268,7 @@
         <v>28</v>
       </c>
       <c r="C26">
-        <v>4.666666666666667</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -7279,7 +7279,7 @@
         <v>27</v>
       </c>
       <c r="C27">
-        <v>4.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -7290,7 +7290,7 @@
         <v>25</v>
       </c>
       <c r="C28">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -7301,7 +7301,7 @@
         <v>23</v>
       </c>
       <c r="C29">
-        <v>3.8333333333333335</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -7312,7 +7312,7 @@
         <v>23</v>
       </c>
       <c r="C30">
-        <v>3.8333333333333335</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -7323,7 +7323,7 @@
         <v>23</v>
       </c>
       <c r="C31">
-        <v>3.8333333333333335</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -7334,7 +7334,7 @@
         <v>22</v>
       </c>
       <c r="C32">
-        <v>3.6666666666666665</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -7345,7 +7345,7 @@
         <v>22</v>
       </c>
       <c r="C33">
-        <v>3.6666666666666665</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -7356,7 +7356,7 @@
         <v>20</v>
       </c>
       <c r="C34">
-        <v>3.3333333333333335</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -7367,7 +7367,7 @@
         <v>19</v>
       </c>
       <c r="C35">
-        <v>3.1666666666666665</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -7389,7 +7389,7 @@
         <v>17</v>
       </c>
       <c r="C37">
-        <v>2.8333333333333335</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -7400,7 +7400,7 @@
         <v>16</v>
       </c>
       <c r="C38">
-        <v>2.6666666666666665</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -7411,7 +7411,7 @@
         <v>16</v>
       </c>
       <c r="C39">
-        <v>2.6666666666666665</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -7422,7 +7422,7 @@
         <v>16</v>
       </c>
       <c r="C40">
-        <v>2.6666666666666665</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -7433,7 +7433,7 @@
         <v>16</v>
       </c>
       <c r="C41">
-        <v>2.6666666666666665</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -7444,7 +7444,7 @@
         <v>15</v>
       </c>
       <c r="C42">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -7455,7 +7455,7 @@
         <v>15</v>
       </c>
       <c r="C43">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -7466,7 +7466,7 @@
         <v>15</v>
       </c>
       <c r="C44">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -7477,7 +7477,7 @@
         <v>15</v>
       </c>
       <c r="C45">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -7488,7 +7488,7 @@
         <v>15</v>
       </c>
       <c r="C46">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -7499,7 +7499,7 @@
         <v>15</v>
       </c>
       <c r="C47">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -7510,7 +7510,7 @@
         <v>13</v>
       </c>
       <c r="C48">
-        <v>2.1666666666666665</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -7521,7 +7521,7 @@
         <v>13</v>
       </c>
       <c r="C49">
-        <v>2.1666666666666665</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -7532,7 +7532,7 @@
         <v>13</v>
       </c>
       <c r="C50">
-        <v>2.1666666666666665</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -7576,7 +7576,7 @@
         <v>11</v>
       </c>
       <c r="C54">
-        <v>1.8333333333333333</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -7587,7 +7587,7 @@
         <v>11</v>
       </c>
       <c r="C55">
-        <v>1.8333333333333333</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -7598,7 +7598,7 @@
         <v>10</v>
       </c>
       <c r="C56">
-        <v>1.6666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -7609,7 +7609,7 @@
         <v>10</v>
       </c>
       <c r="C57">
-        <v>1.6666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -7620,7 +7620,7 @@
         <v>9</v>
       </c>
       <c r="C58">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -7631,7 +7631,7 @@
         <v>8</v>
       </c>
       <c r="C59">
-        <v>1.3333333333333333</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -7642,7 +7642,7 @@
         <v>8</v>
       </c>
       <c r="C60">
-        <v>1.3333333333333333</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -7653,7 +7653,7 @@
         <v>8</v>
       </c>
       <c r="C61">
-        <v>1.3333333333333333</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -7664,7 +7664,7 @@
         <v>7</v>
       </c>
       <c r="C62">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -7675,7 +7675,7 @@
         <v>7</v>
       </c>
       <c r="C63">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -7686,7 +7686,7 @@
         <v>7</v>
       </c>
       <c r="C64">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -7697,7 +7697,7 @@
         <v>7</v>
       </c>
       <c r="C65">
-        <v>1.1666666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -7741,7 +7741,7 @@
         <v>5</v>
       </c>
       <c r="C69">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -7752,7 +7752,7 @@
         <v>5</v>
       </c>
       <c r="C70">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -7763,7 +7763,7 @@
         <v>5</v>
       </c>
       <c r="C71">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -7774,7 +7774,7 @@
         <v>5</v>
       </c>
       <c r="C72">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -7785,7 +7785,7 @@
         <v>5</v>
       </c>
       <c r="C73">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -7796,7 +7796,7 @@
         <v>5</v>
       </c>
       <c r="C74">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -7807,7 +7807,7 @@
         <v>4</v>
       </c>
       <c r="C75">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -7818,7 +7818,7 @@
         <v>4</v>
       </c>
       <c r="C76">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -7829,7 +7829,7 @@
         <v>4</v>
       </c>
       <c r="C77">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -7840,7 +7840,7 @@
         <v>4</v>
       </c>
       <c r="C78">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -7851,7 +7851,7 @@
         <v>4</v>
       </c>
       <c r="C79">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -7862,7 +7862,7 @@
         <v>4</v>
       </c>
       <c r="C80">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -7873,7 +7873,7 @@
         <v>4</v>
       </c>
       <c r="C81">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -7884,7 +7884,7 @@
         <v>4</v>
       </c>
       <c r="C82">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -7895,7 +7895,7 @@
         <v>4</v>
       </c>
       <c r="C83">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -7906,7 +7906,7 @@
         <v>4</v>
       </c>
       <c r="C84">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -7917,7 +7917,7 @@
         <v>4</v>
       </c>
       <c r="C85">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -7928,7 +7928,7 @@
         <v>4</v>
       </c>
       <c r="C86">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -7939,7 +7939,7 @@
         <v>3</v>
       </c>
       <c r="C87">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -7950,7 +7950,7 @@
         <v>3</v>
       </c>
       <c r="C88">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -7961,7 +7961,7 @@
         <v>3</v>
       </c>
       <c r="C89">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -7972,7 +7972,7 @@
         <v>3</v>
       </c>
       <c r="C90">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -7983,7 +7983,7 @@
         <v>3</v>
       </c>
       <c r="C91">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -7994,7 +7994,7 @@
         <v>3</v>
       </c>
       <c r="C92">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -8005,7 +8005,7 @@
         <v>3</v>
       </c>
       <c r="C93">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -8016,7 +8016,7 @@
         <v>3</v>
       </c>
       <c r="C94">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -8027,7 +8027,7 @@
         <v>3</v>
       </c>
       <c r="C95">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -8038,7 +8038,7 @@
         <v>3</v>
       </c>
       <c r="C96">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -8049,7 +8049,7 @@
         <v>3</v>
       </c>
       <c r="C97">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -8060,7 +8060,7 @@
         <v>3</v>
       </c>
       <c r="C98">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -8071,7 +8071,7 @@
         <v>3</v>
       </c>
       <c r="C99">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -8082,7 +8082,7 @@
         <v>3</v>
       </c>
       <c r="C100">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -8093,7 +8093,7 @@
         <v>3</v>
       </c>
       <c r="C101">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -8104,7 +8104,7 @@
         <v>3</v>
       </c>
       <c r="C102">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -8115,7 +8115,7 @@
         <v>3</v>
       </c>
       <c r="C103">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -8126,7 +8126,7 @@
         <v>3</v>
       </c>
       <c r="C104">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -8137,7 +8137,7 @@
         <v>3</v>
       </c>
       <c r="C105">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -8148,7 +8148,7 @@
         <v>2</v>
       </c>
       <c r="C106">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -8159,7 +8159,7 @@
         <v>2</v>
       </c>
       <c r="C107">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -8170,7 +8170,7 @@
         <v>2</v>
       </c>
       <c r="C108">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -8181,7 +8181,7 @@
         <v>2</v>
       </c>
       <c r="C109">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -8192,7 +8192,7 @@
         <v>2</v>
       </c>
       <c r="C110">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -8203,7 +8203,7 @@
         <v>2</v>
       </c>
       <c r="C111">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -8214,7 +8214,7 @@
         <v>2</v>
       </c>
       <c r="C112">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -8225,7 +8225,7 @@
         <v>2</v>
       </c>
       <c r="C113">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -8236,7 +8236,7 @@
         <v>2</v>
       </c>
       <c r="C114">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -8247,7 +8247,7 @@
         <v>2</v>
       </c>
       <c r="C115">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -8258,7 +8258,7 @@
         <v>2</v>
       </c>
       <c r="C116">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -8269,7 +8269,7 @@
         <v>2</v>
       </c>
       <c r="C117">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -8280,7 +8280,7 @@
         <v>2</v>
       </c>
       <c r="C118">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -8291,7 +8291,7 @@
         <v>2</v>
       </c>
       <c r="C119">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -8302,7 +8302,7 @@
         <v>2</v>
       </c>
       <c r="C120">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -8313,7 +8313,7 @@
         <v>2</v>
       </c>
       <c r="C121">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -8324,7 +8324,7 @@
         <v>2</v>
       </c>
       <c r="C122">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -8335,7 +8335,7 @@
         <v>2</v>
       </c>
       <c r="C123">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -8346,7 +8346,7 @@
         <v>2</v>
       </c>
       <c r="C124">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -8357,7 +8357,7 @@
         <v>2</v>
       </c>
       <c r="C125">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -8368,7 +8368,7 @@
         <v>2</v>
       </c>
       <c r="C126">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -8379,7 +8379,7 @@
         <v>2</v>
       </c>
       <c r="C127">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -8390,7 +8390,7 @@
         <v>2</v>
       </c>
       <c r="C128">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -8401,7 +8401,7 @@
         <v>2</v>
       </c>
       <c r="C129">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -8412,7 +8412,7 @@
         <v>2</v>
       </c>
       <c r="C130">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -8423,7 +8423,7 @@
         <v>2</v>
       </c>
       <c r="C131">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -8434,7 +8434,7 @@
         <v>2</v>
       </c>
       <c r="C132">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -8445,7 +8445,7 @@
         <v>2</v>
       </c>
       <c r="C133">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -8456,7 +8456,7 @@
         <v>2</v>
       </c>
       <c r="C134">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -8467,7 +8467,7 @@
         <v>2</v>
       </c>
       <c r="C135">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -8478,7 +8478,7 @@
         <v>2</v>
       </c>
       <c r="C136">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -8489,7 +8489,7 @@
         <v>2</v>
       </c>
       <c r="C137">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -8500,7 +8500,7 @@
         <v>2</v>
       </c>
       <c r="C138">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -8511,7 +8511,7 @@
         <v>2</v>
       </c>
       <c r="C139">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -8522,7 +8522,7 @@
         <v>2</v>
       </c>
       <c r="C140">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -8533,7 +8533,7 @@
         <v>2</v>
       </c>
       <c r="C141">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -8544,7 +8544,7 @@
         <v>2</v>
       </c>
       <c r="C142">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -8555,7 +8555,7 @@
         <v>2</v>
       </c>
       <c r="C143">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -8566,7 +8566,7 @@
         <v>2</v>
       </c>
       <c r="C144">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -8577,7 +8577,7 @@
         <v>2</v>
       </c>
       <c r="C145">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -8588,7 +8588,7 @@
         <v>2</v>
       </c>
       <c r="C146">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -8599,7 +8599,7 @@
         <v>2</v>
       </c>
       <c r="C147">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -8610,7 +8610,7 @@
         <v>2</v>
       </c>
       <c r="C148">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -8621,7 +8621,7 @@
         <v>2</v>
       </c>
       <c r="C149">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -8632,7 +8632,7 @@
         <v>2</v>
       </c>
       <c r="C150">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -8643,7 +8643,7 @@
         <v>2</v>
       </c>
       <c r="C151">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -8654,7 +8654,7 @@
         <v>2</v>
       </c>
       <c r="C152">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -8665,7 +8665,7 @@
         <v>2</v>
       </c>
       <c r="C153">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -8676,7 +8676,7 @@
         <v>2</v>
       </c>
       <c r="C154">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -8687,7 +8687,7 @@
         <v>2</v>
       </c>
       <c r="C155">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -8698,7 +8698,7 @@
         <v>2</v>
       </c>
       <c r="C156">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -8709,7 +8709,7 @@
         <v>2</v>
       </c>
       <c r="C157">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -8720,7 +8720,7 @@
         <v>2</v>
       </c>
       <c r="C158">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -8731,7 +8731,7 @@
         <v>1</v>
       </c>
       <c r="C159">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -8742,7 +8742,7 @@
         <v>1</v>
       </c>
       <c r="C160">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -8753,7 +8753,7 @@
         <v>1</v>
       </c>
       <c r="C161">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -8764,7 +8764,7 @@
         <v>1</v>
       </c>
       <c r="C162">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -8775,7 +8775,7 @@
         <v>1</v>
       </c>
       <c r="C163">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -8786,7 +8786,7 @@
         <v>1</v>
       </c>
       <c r="C164">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -8797,7 +8797,7 @@
         <v>1</v>
       </c>
       <c r="C165">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -8808,7 +8808,7 @@
         <v>1</v>
       </c>
       <c r="C166">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -8819,7 +8819,7 @@
         <v>1</v>
       </c>
       <c r="C167">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -8830,7 +8830,7 @@
         <v>1</v>
       </c>
       <c r="C168">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -8841,7 +8841,7 @@
         <v>1</v>
       </c>
       <c r="C169">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -8852,7 +8852,7 @@
         <v>1</v>
       </c>
       <c r="C170">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -8863,7 +8863,7 @@
         <v>1</v>
       </c>
       <c r="C171">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -8874,7 +8874,7 @@
         <v>1</v>
       </c>
       <c r="C172">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -8885,7 +8885,7 @@
         <v>1</v>
       </c>
       <c r="C173">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -8896,7 +8896,7 @@
         <v>1</v>
       </c>
       <c r="C174">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -8907,7 +8907,7 @@
         <v>1</v>
       </c>
       <c r="C175">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -8918,7 +8918,7 @@
         <v>1</v>
       </c>
       <c r="C176">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -8929,7 +8929,7 @@
         <v>1</v>
       </c>
       <c r="C177">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -8940,7 +8940,7 @@
         <v>1</v>
       </c>
       <c r="C178">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -8951,7 +8951,7 @@
         <v>1</v>
       </c>
       <c r="C179">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -8962,7 +8962,7 @@
         <v>1</v>
       </c>
       <c r="C180">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -8973,7 +8973,7 @@
         <v>1</v>
       </c>
       <c r="C181">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -8984,7 +8984,7 @@
         <v>1</v>
       </c>
       <c r="C182">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -8995,7 +8995,7 @@
         <v>1</v>
       </c>
       <c r="C183">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -9006,7 +9006,7 @@
         <v>1</v>
       </c>
       <c r="C184">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -9017,7 +9017,7 @@
         <v>1</v>
       </c>
       <c r="C185">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -9028,7 +9028,7 @@
         <v>1</v>
       </c>
       <c r="C186">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -9039,7 +9039,7 @@
         <v>1</v>
       </c>
       <c r="C187">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -9050,7 +9050,7 @@
         <v>1</v>
       </c>
       <c r="C188">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -9061,7 +9061,7 @@
         <v>1</v>
       </c>
       <c r="C189">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -9072,7 +9072,7 @@
         <v>1</v>
       </c>
       <c r="C190">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -9083,7 +9083,7 @@
         <v>1</v>
       </c>
       <c r="C191">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -9094,7 +9094,7 @@
         <v>1</v>
       </c>
       <c r="C192">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -9105,7 +9105,7 @@
         <v>1</v>
       </c>
       <c r="C193">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -9116,7 +9116,7 @@
         <v>1</v>
       </c>
       <c r="C194">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -9127,7 +9127,7 @@
         <v>1</v>
       </c>
       <c r="C195">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -9138,7 +9138,7 @@
         <v>1</v>
       </c>
       <c r="C196">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -9149,7 +9149,7 @@
         <v>1</v>
       </c>
       <c r="C197">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -9160,7 +9160,7 @@
         <v>1</v>
       </c>
       <c r="C198">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -9171,7 +9171,7 @@
         <v>1</v>
       </c>
       <c r="C199">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -9182,7 +9182,7 @@
         <v>1</v>
       </c>
       <c r="C200">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -9193,7 +9193,7 @@
         <v>1</v>
       </c>
       <c r="C201">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -9204,7 +9204,7 @@
         <v>1</v>
       </c>
       <c r="C202">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -9215,7 +9215,7 @@
         <v>1</v>
       </c>
       <c r="C203">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -9226,7 +9226,7 @@
         <v>1</v>
       </c>
       <c r="C204">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -9237,7 +9237,7 @@
         <v>1</v>
       </c>
       <c r="C205">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -9248,7 +9248,7 @@
         <v>1</v>
       </c>
       <c r="C206">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -9259,7 +9259,7 @@
         <v>1</v>
       </c>
       <c r="C207">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -9270,7 +9270,7 @@
         <v>1</v>
       </c>
       <c r="C208">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -9281,7 +9281,7 @@
         <v>1</v>
       </c>
       <c r="C209">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -9292,7 +9292,7 @@
         <v>1</v>
       </c>
       <c r="C210">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -9303,7 +9303,7 @@
         <v>1</v>
       </c>
       <c r="C211">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -9314,7 +9314,7 @@
         <v>1</v>
       </c>
       <c r="C212">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -9325,7 +9325,7 @@
         <v>1</v>
       </c>
       <c r="C213">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -9336,7 +9336,7 @@
         <v>1</v>
       </c>
       <c r="C214">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -9347,7 +9347,7 @@
         <v>1</v>
       </c>
       <c r="C215">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -9358,7 +9358,7 @@
         <v>1</v>
       </c>
       <c r="C216">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -9369,7 +9369,7 @@
         <v>1</v>
       </c>
       <c r="C217">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -9380,7 +9380,7 @@
         <v>1</v>
       </c>
       <c r="C218">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -9391,7 +9391,7 @@
         <v>1</v>
       </c>
       <c r="C219">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -9402,7 +9402,7 @@
         <v>1</v>
       </c>
       <c r="C220">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="C221">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -9424,7 +9424,7 @@
         <v>1</v>
       </c>
       <c r="C222">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -9435,7 +9435,7 @@
         <v>1</v>
       </c>
       <c r="C223">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -9446,7 +9446,7 @@
         <v>1</v>
       </c>
       <c r="C224">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -9457,7 +9457,7 @@
         <v>1</v>
       </c>
       <c r="C225">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -9468,7 +9468,7 @@
         <v>1</v>
       </c>
       <c r="C226">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -9479,7 +9479,7 @@
         <v>1</v>
       </c>
       <c r="C227">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -9490,7 +9490,7 @@
         <v>1</v>
       </c>
       <c r="C228">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -9501,7 +9501,7 @@
         <v>1</v>
       </c>
       <c r="C229">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -9512,7 +9512,7 @@
         <v>1</v>
       </c>
       <c r="C230">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -9523,7 +9523,7 @@
         <v>1</v>
       </c>
       <c r="C231">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -9534,7 +9534,7 @@
         <v>1</v>
       </c>
       <c r="C232">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -9545,7 +9545,7 @@
         <v>1</v>
       </c>
       <c r="C233">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -9556,7 +9556,7 @@
         <v>1</v>
       </c>
       <c r="C234">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -9567,7 +9567,7 @@
         <v>1</v>
       </c>
       <c r="C235">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -9578,7 +9578,7 @@
         <v>1</v>
       </c>
       <c r="C236">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -9589,7 +9589,7 @@
         <v>1</v>
       </c>
       <c r="C237">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -9600,7 +9600,7 @@
         <v>1</v>
       </c>
       <c r="C238">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -9611,7 +9611,7 @@
         <v>1</v>
       </c>
       <c r="C239">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -9622,7 +9622,7 @@
         <v>1</v>
       </c>
       <c r="C240">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -9633,7 +9633,7 @@
         <v>1</v>
       </c>
       <c r="C241">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -9644,7 +9644,7 @@
         <v>1</v>
       </c>
       <c r="C242">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -9655,7 +9655,7 @@
         <v>1</v>
       </c>
       <c r="C243">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -9666,7 +9666,7 @@
         <v>1</v>
       </c>
       <c r="C244">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -9677,7 +9677,7 @@
         <v>1</v>
       </c>
       <c r="C245">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -9688,7 +9688,7 @@
         <v>1</v>
       </c>
       <c r="C246">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -9699,7 +9699,7 @@
         <v>1</v>
       </c>
       <c r="C247">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -9710,7 +9710,7 @@
         <v>1</v>
       </c>
       <c r="C248">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -9721,7 +9721,7 @@
         <v>1</v>
       </c>
       <c r="C249">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -9732,7 +9732,7 @@
         <v>1</v>
       </c>
       <c r="C250">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -9743,7 +9743,7 @@
         <v>1</v>
       </c>
       <c r="C251">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -9754,7 +9754,7 @@
         <v>1</v>
       </c>
       <c r="C252">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -9765,7 +9765,7 @@
         <v>1</v>
       </c>
       <c r="C253">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -9776,7 +9776,7 @@
         <v>1</v>
       </c>
       <c r="C254">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -9787,7 +9787,7 @@
         <v>1</v>
       </c>
       <c r="C255">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -9798,7 +9798,7 @@
         <v>1</v>
       </c>
       <c r="C256">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -9809,7 +9809,7 @@
         <v>1</v>
       </c>
       <c r="C257">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -9820,7 +9820,7 @@
         <v>1</v>
       </c>
       <c r="C258">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -9831,7 +9831,7 @@
         <v>1</v>
       </c>
       <c r="C259">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -9842,7 +9842,7 @@
         <v>1</v>
       </c>
       <c r="C260">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -9853,7 +9853,7 @@
         <v>1</v>
       </c>
       <c r="C261">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -9864,7 +9864,7 @@
         <v>1</v>
       </c>
       <c r="C262">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -9875,7 +9875,7 @@
         <v>1</v>
       </c>
       <c r="C263">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -9886,7 +9886,7 @@
         <v>1</v>
       </c>
       <c r="C264">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -9897,7 +9897,7 @@
         <v>1</v>
       </c>
       <c r="C265">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -9908,7 +9908,7 @@
         <v>1</v>
       </c>
       <c r="C266">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -9919,7 +9919,7 @@
         <v>1</v>
       </c>
       <c r="C267">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -9930,7 +9930,7 @@
         <v>1</v>
       </c>
       <c r="C268">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -9941,7 +9941,7 @@
         <v>1</v>
       </c>
       <c r="C269">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -9952,7 +9952,7 @@
         <v>1</v>
       </c>
       <c r="C270">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -9963,7 +9963,7 @@
         <v>1</v>
       </c>
       <c r="C271">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -9974,7 +9974,7 @@
         <v>1</v>
       </c>
       <c r="C272">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -9985,7 +9985,7 @@
         <v>1</v>
       </c>
       <c r="C273">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -9996,7 +9996,7 @@
         <v>1</v>
       </c>
       <c r="C274">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -10007,7 +10007,7 @@
         <v>1</v>
       </c>
       <c r="C275">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -10018,7 +10018,7 @@
         <v>1</v>
       </c>
       <c r="C276">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -10029,7 +10029,7 @@
         <v>1</v>
       </c>
       <c r="C277">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -10040,7 +10040,7 @@
         <v>1</v>
       </c>
       <c r="C278">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -10051,7 +10051,7 @@
         <v>1</v>
       </c>
       <c r="C279">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -10062,7 +10062,7 @@
         <v>1</v>
       </c>
       <c r="C280">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -10073,7 +10073,7 @@
         <v>1</v>
       </c>
       <c r="C281">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -10084,7 +10084,7 @@
         <v>1</v>
       </c>
       <c r="C282">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -10095,7 +10095,7 @@
         <v>1</v>
       </c>
       <c r="C283">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -10106,7 +10106,7 @@
         <v>1</v>
       </c>
       <c r="C284">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -10117,7 +10117,7 @@
         <v>1</v>
       </c>
       <c r="C285">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -10128,7 +10128,7 @@
         <v>1</v>
       </c>
       <c r="C286">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -10139,7 +10139,7 @@
         <v>1</v>
       </c>
       <c r="C287">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -10150,7 +10150,7 @@
         <v>1</v>
       </c>
       <c r="C288">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -10161,7 +10161,7 @@
         <v>1</v>
       </c>
       <c r="C289">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -10172,7 +10172,7 @@
         <v>1</v>
       </c>
       <c r="C290">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -10183,7 +10183,7 @@
         <v>1</v>
       </c>
       <c r="C291">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -10194,7 +10194,7 @@
         <v>1</v>
       </c>
       <c r="C292">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -10205,7 +10205,7 @@
         <v>1</v>
       </c>
       <c r="C293">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -10216,7 +10216,7 @@
         <v>1</v>
       </c>
       <c r="C294">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -10227,7 +10227,7 @@
         <v>1</v>
       </c>
       <c r="C295">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -10238,7 +10238,7 @@
         <v>1</v>
       </c>
       <c r="C296">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -10249,7 +10249,7 @@
         <v>1</v>
       </c>
       <c r="C297">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -10260,7 +10260,7 @@
         <v>1</v>
       </c>
       <c r="C298">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -10271,7 +10271,7 @@
         <v>1</v>
       </c>
       <c r="C299">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -10282,7 +10282,7 @@
         <v>1</v>
       </c>
       <c r="C300">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -10293,7 +10293,7 @@
         <v>1</v>
       </c>
       <c r="C301">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -10304,7 +10304,7 @@
         <v>1</v>
       </c>
       <c r="C302">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -10315,7 +10315,7 @@
         <v>1</v>
       </c>
       <c r="C303">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -10326,7 +10326,7 @@
         <v>1</v>
       </c>
       <c r="C304">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -10337,7 +10337,7 @@
         <v>1</v>
       </c>
       <c r="C305">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -10348,7 +10348,7 @@
         <v>1</v>
       </c>
       <c r="C306">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -10359,7 +10359,7 @@
         <v>1</v>
       </c>
       <c r="C307">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -10370,7 +10370,7 @@
         <v>1</v>
       </c>
       <c r="C308">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -10381,7 +10381,7 @@
         <v>1</v>
       </c>
       <c r="C309">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -10392,7 +10392,7 @@
         <v>1</v>
       </c>
       <c r="C310">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -10403,7 +10403,7 @@
         <v>1</v>
       </c>
       <c r="C311">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -10414,7 +10414,7 @@
         <v>1</v>
       </c>
       <c r="C312">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -10425,7 +10425,7 @@
         <v>1</v>
       </c>
       <c r="C313">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -10436,7 +10436,7 @@
         <v>1</v>
       </c>
       <c r="C314">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -10447,7 +10447,7 @@
         <v>1</v>
       </c>
       <c r="C315">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -10458,7 +10458,7 @@
         <v>1</v>
       </c>
       <c r="C316">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -10469,7 +10469,7 @@
         <v>1</v>
       </c>
       <c r="C317">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -10480,7 +10480,7 @@
         <v>1</v>
       </c>
       <c r="C318">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -10491,7 +10491,7 @@
         <v>1</v>
       </c>
       <c r="C319">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -10502,7 +10502,7 @@
         <v>1</v>
       </c>
       <c r="C320">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -10513,7 +10513,7 @@
         <v>1</v>
       </c>
       <c r="C321">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -10524,7 +10524,7 @@
         <v>1</v>
       </c>
       <c r="C322">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -10535,7 +10535,7 @@
         <v>1</v>
       </c>
       <c r="C323">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -10546,7 +10546,7 @@
         <v>1</v>
       </c>
       <c r="C324">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
@@ -10557,7 +10557,7 @@
         <v>1</v>
       </c>
       <c r="C325">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -10568,7 +10568,7 @@
         <v>1</v>
       </c>
       <c r="C326">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -10579,7 +10579,7 @@
         <v>1</v>
       </c>
       <c r="C327">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -10590,7 +10590,7 @@
         <v>1</v>
       </c>
       <c r="C328">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -10601,7 +10601,7 @@
         <v>1</v>
       </c>
       <c r="C329">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -10612,7 +10612,7 @@
         <v>1</v>
       </c>
       <c r="C330">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
@@ -10623,7 +10623,7 @@
         <v>1</v>
       </c>
       <c r="C331">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -10634,7 +10634,7 @@
         <v>1</v>
       </c>
       <c r="C332">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -10645,7 +10645,7 @@
         <v>1</v>
       </c>
       <c r="C333">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
@@ -10656,7 +10656,7 @@
         <v>1</v>
       </c>
       <c r="C334">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
@@ -10667,7 +10667,7 @@
         <v>1</v>
       </c>
       <c r="C335">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -10678,7 +10678,7 @@
         <v>1</v>
       </c>
       <c r="C336">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
@@ -10689,7 +10689,7 @@
         <v>1</v>
       </c>
       <c r="C337">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -10700,7 +10700,7 @@
         <v>1</v>
       </c>
       <c r="C338">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -10711,7 +10711,7 @@
         <v>1</v>
       </c>
       <c r="C339">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -10722,7 +10722,7 @@
         <v>1</v>
       </c>
       <c r="C340">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
@@ -10733,7 +10733,7 @@
         <v>1</v>
       </c>
       <c r="C341">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
@@ -10744,7 +10744,7 @@
         <v>1</v>
       </c>
       <c r="C342">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
@@ -10755,7 +10755,7 @@
         <v>1</v>
       </c>
       <c r="C343">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
@@ -10766,7 +10766,7 @@
         <v>1</v>
       </c>
       <c r="C344">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -10777,7 +10777,7 @@
         <v>1</v>
       </c>
       <c r="C345">
-        <v>0.16666666666666666</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
